--- a/data/ams_weekly_data/White_Mulberry/ads_report_week22.xlsx
+++ b/data/ams_weekly_data/White_Mulberry/ads_report_week22.xlsx
@@ -1655,7 +1655,7 @@
         <v>69</v>
       </c>
       <c r="F44" t="n">
-        <v>12371</v>
+        <v>12369</v>
       </c>
       <c r="G44" t="n">
         <v>0</v>
@@ -1795,7 +1795,7 @@
         <v>19</v>
       </c>
       <c r="F49" t="n">
-        <v>2774</v>
+        <v>2773</v>
       </c>
       <c r="G49" t="n">
         <v>0</v>
@@ -1935,7 +1935,7 @@
         <v>153</v>
       </c>
       <c r="F54" t="n">
-        <v>19170</v>
+        <v>19168</v>
       </c>
       <c r="G54" t="n">
         <v>14405.08</v>
@@ -2489,13 +2489,13 @@
         </is>
       </c>
       <c r="D74" t="n">
-        <v>3619.94</v>
+        <v>3602.95</v>
       </c>
       <c r="E74" t="n">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="F74" t="n">
-        <v>25250</v>
+        <v>25249</v>
       </c>
       <c r="G74" t="n">
         <v>5082.2</v>
@@ -2722,10 +2722,10 @@
         <v>5450</v>
       </c>
       <c r="G82" t="n">
-        <v>5422.030000000001</v>
+        <v>8205.93</v>
       </c>
       <c r="H82" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="83">
@@ -2943,7 +2943,7 @@
         <v>21</v>
       </c>
       <c r="F90" t="n">
-        <v>3973</v>
+        <v>3972</v>
       </c>
       <c r="G90" t="n">
         <v>0</v>
@@ -4794,10 +4794,10 @@
         <v>25323</v>
       </c>
       <c r="G15" t="n">
-        <v>2626.27</v>
+        <v>5252.54</v>
       </c>
       <c r="H15" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="16">

--- a/data/ams_weekly_data/White_Mulberry/ads_report_week22.xlsx
+++ b/data/ams_weekly_data/White_Mulberry/ads_report_week22.xlsx
@@ -1039,7 +1039,7 @@
         <v>196</v>
       </c>
       <c r="F22" t="n">
-        <v>32062</v>
+        <v>32059</v>
       </c>
       <c r="G22" t="n">
         <v>0</v>
@@ -1151,7 +1151,7 @@
         <v>64</v>
       </c>
       <c r="F26" t="n">
-        <v>6712</v>
+        <v>6711</v>
       </c>
       <c r="G26" t="n">
         <v>7075.42</v>
@@ -1487,13 +1487,13 @@
         <v>34</v>
       </c>
       <c r="F38" t="n">
-        <v>6461</v>
+        <v>6460</v>
       </c>
       <c r="G38" t="n">
-        <v>12712.71</v>
+        <v>19915.25</v>
       </c>
       <c r="H38" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="39">
@@ -1599,7 +1599,7 @@
         <v>31</v>
       </c>
       <c r="F42" t="n">
-        <v>13230</v>
+        <v>13229</v>
       </c>
       <c r="G42" t="n">
         <v>0</v>
@@ -1683,7 +1683,7 @@
         <v>51</v>
       </c>
       <c r="F45" t="n">
-        <v>2641</v>
+        <v>2640</v>
       </c>
       <c r="G45" t="n">
         <v>0</v>
@@ -2495,7 +2495,7 @@
         <v>193</v>
       </c>
       <c r="F74" t="n">
-        <v>25249</v>
+        <v>25247</v>
       </c>
       <c r="G74" t="n">
         <v>5082.2</v>
@@ -2722,10 +2722,10 @@
         <v>5450</v>
       </c>
       <c r="G82" t="n">
-        <v>8205.93</v>
+        <v>13773.73</v>
       </c>
       <c r="H82" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="83">
@@ -2769,13 +2769,13 @@
         </is>
       </c>
       <c r="D84" t="n">
-        <v>1656.76</v>
+        <v>1628.61</v>
       </c>
       <c r="E84" t="n">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="F84" t="n">
-        <v>24901</v>
+        <v>24899</v>
       </c>
       <c r="G84" t="n">
         <v>2626.27</v>
@@ -3223,7 +3223,7 @@
         <v>51</v>
       </c>
       <c r="F100" t="n">
-        <v>35447</v>
+        <v>35442</v>
       </c>
       <c r="G100" t="n">
         <v>1355.08</v>
@@ -3251,7 +3251,7 @@
         <v>111</v>
       </c>
       <c r="F101" t="n">
-        <v>47805</v>
+        <v>47802</v>
       </c>
       <c r="G101" t="n">
         <v>5252.54</v>
@@ -3335,7 +3335,7 @@
         <v>124</v>
       </c>
       <c r="F104" t="n">
-        <v>67250</v>
+        <v>67246</v>
       </c>
       <c r="G104" t="n">
         <v>9532.200000000001</v>
@@ -3845,7 +3845,7 @@
         <v>7543.219999999999</v>
       </c>
       <c r="H122" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="123">
@@ -4343,7 +4343,7 @@
         <v>89</v>
       </c>
       <c r="F140" t="n">
-        <v>54480</v>
+        <v>54479</v>
       </c>
       <c r="G140" t="n">
         <v>0</v>
@@ -4651,7 +4651,7 @@
         <v>67</v>
       </c>
       <c r="F10" t="n">
-        <v>31217</v>
+        <v>31215</v>
       </c>
       <c r="G10" t="n">
         <v>0</v>
@@ -4679,7 +4679,7 @@
         <v>96</v>
       </c>
       <c r="F11" t="n">
-        <v>29741</v>
+        <v>29740</v>
       </c>
       <c r="G11" t="n">
         <v>2989.83</v>
@@ -4763,7 +4763,7 @@
         <v>53</v>
       </c>
       <c r="F14" t="n">
-        <v>22726</v>
+        <v>22725</v>
       </c>
       <c r="G14" t="n">
         <v>0</v>
@@ -4791,13 +4791,13 @@
         <v>99</v>
       </c>
       <c r="F15" t="n">
-        <v>25323</v>
+        <v>25322</v>
       </c>
       <c r="G15" t="n">
-        <v>5252.54</v>
+        <v>7878.82</v>
       </c>
       <c r="H15" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="16">
@@ -4895,7 +4895,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I28"/>
+  <dimension ref="A1:I27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5354,19 +5354,19 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>4542</v>
+        <v>7917</v>
       </c>
       <c r="E14" t="n">
-        <v>195</v>
+        <v>340</v>
       </c>
       <c r="F14" t="n">
-        <v>421.0197143358128</v>
+        <v>733.86</v>
       </c>
       <c r="G14" t="n">
-        <v>22054.36554985014</v>
+        <v>38441.945</v>
       </c>
       <c r="H14" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
@@ -5383,23 +5383,23 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>B0BFVNS8HS</t>
+          <t>B0CPFS24ML</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>4815</v>
+        <v>7917</v>
       </c>
       <c r="E15" t="n">
-        <v>207</v>
+        <v>340</v>
       </c>
       <c r="F15" t="n">
-        <v>446.2841580455429</v>
+        <v>733.86</v>
       </c>
       <c r="G15" t="n">
-        <v>23377.79829662071</v>
+        <v>38441.945</v>
       </c>
       <c r="H15" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
@@ -5411,25 +5411,25 @@
       <c r="A16" t="inlineStr"/>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Camb-SB-Multiple Asin- Product collection- exact /Reach</t>
+          <t>Camb-SB-Multiple Asin- product collection- Reach</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>B0BFWD6SNF</t>
+          <t>B0CPT3Q25C</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>2285</v>
+        <v>4039</v>
       </c>
       <c r="E16" t="n">
-        <v>98</v>
+        <v>78</v>
       </c>
       <c r="F16" t="n">
-        <v>211.7707586757711</v>
+        <v>561.6066666666667</v>
       </c>
       <c r="G16" t="n">
-        <v>11093.23284771246</v>
+        <v>15845.76333333333</v>
       </c>
       <c r="H16" t="n">
         <v>2</v>
@@ -5444,25 +5444,25 @@
       <c r="A17" t="inlineStr"/>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Camb-SB-Multiple Asin- Product collection- exact /Reach</t>
+          <t>Camb-SB-Multiple Asin- product collection- Reach</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>B0CPFS24ML</t>
+          <t>B0DQ1NV8D2</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>2257</v>
+        <v>4039</v>
       </c>
       <c r="E17" t="n">
-        <v>97</v>
+        <v>78</v>
       </c>
       <c r="F17" t="n">
-        <v>209.2492531828137</v>
+        <v>561.6066666666667</v>
       </c>
       <c r="G17" t="n">
-        <v>10961.14828733655</v>
+        <v>15845.76333333333</v>
       </c>
       <c r="H17" t="n">
         <v>2</v>
@@ -5477,28 +5477,28 @@
       <c r="A18" t="inlineStr"/>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Camb-SB-Multiple Asin- Product collection- exact /Reach</t>
+          <t>Camb-SB-Multiple Asin- product collection- Reach</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>B0DQPK7MFH</t>
+          <t>B0DQ4YWSMC</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>1935</v>
+        <v>4039</v>
       </c>
       <c r="E18" t="n">
-        <v>83</v>
+        <v>78</v>
       </c>
       <c r="F18" t="n">
-        <v>179.3961157600592</v>
+        <v>561.6066666666667</v>
       </c>
       <c r="G18" t="n">
-        <v>9397.345018480133</v>
+        <v>15845.76333333333</v>
       </c>
       <c r="H18" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
@@ -5510,28 +5510,28 @@
       <c r="A19" t="inlineStr"/>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Camb-SB-Multiple Asin- product collection- Reach</t>
+          <t>WM- SBV- Wooden Arm- B0DP32F346- Phrase</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>B0CPFS24ML</t>
+          <t>B0DP32F346</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>12118</v>
+        <v>9282</v>
       </c>
       <c r="E19" t="n">
-        <v>234</v>
+        <v>116</v>
       </c>
       <c r="F19" t="n">
-        <v>1684.82</v>
+        <v>1354.82</v>
       </c>
       <c r="G19" t="n">
-        <v>47537.29</v>
+        <v>0</v>
       </c>
       <c r="H19" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
@@ -5543,28 +5543,28 @@
       <c r="A20" t="inlineStr"/>
       <c r="B20" t="inlineStr">
         <is>
-          <t>WM- SBV- Wooden Arm- B0DP32F346- Phrase</t>
+          <t>WM- SBV-Wall Mounted Stand- B0DP2WC5VW- Phrase &amp; exact</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>B0DP32F346</t>
+          <t>B0DP2WC5VW</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>9282</v>
+        <v>17945</v>
       </c>
       <c r="E20" t="n">
-        <v>116</v>
+        <v>201</v>
       </c>
       <c r="F20" t="n">
-        <v>1354.82</v>
+        <v>2724.67</v>
       </c>
       <c r="G20" t="n">
-        <v>0</v>
+        <v>5422.030000000001</v>
       </c>
       <c r="H20" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
@@ -5576,28 +5576,28 @@
       <c r="A21" t="inlineStr"/>
       <c r="B21" t="inlineStr">
         <is>
-          <t>WM- SBV-Wall Mounted Stand- B0DP2WC5VW- Phrase &amp; exact</t>
+          <t>WM-SB-Monitor Arms-Defensive</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>B0DP2WC5VW</t>
+          <t>B0DB5VG39T</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>17945</v>
+        <v>409</v>
       </c>
       <c r="E21" t="n">
-        <v>201</v>
+        <v>7</v>
       </c>
       <c r="F21" t="n">
-        <v>2724.67</v>
+        <v>74.98833333333332</v>
       </c>
       <c r="G21" t="n">
-        <v>5422.030000000001</v>
+        <v>0</v>
       </c>
       <c r="H21" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
@@ -5614,7 +5614,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>B0DB5VG39T</t>
+          <t>B0DB5VVPSB</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -5647,7 +5647,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>B0DB5VVPSB</t>
+          <t>B0DB5W4TCP</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -5680,7 +5680,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>B0DB5W4TCP</t>
+          <t>B0DB5YTQZV</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -5713,7 +5713,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>B0DB5YTQZV</t>
+          <t>B0DP2Z5DQ9</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -5746,7 +5746,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>B0DP2Z5DQ9</t>
+          <t>B0DP32F346</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -5774,22 +5774,22 @@
       <c r="A27" t="inlineStr"/>
       <c r="B27" t="inlineStr">
         <is>
-          <t>WM-SB-Monitor Arms-Defensive</t>
+          <t>WM-SBV-Gas Spring MA- B0DB5VG39T- Phrase</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>B0DP32F346</t>
+          <t>B0DB5VG39T</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>409</v>
+        <v>16265</v>
       </c>
       <c r="E27" t="n">
-        <v>7</v>
+        <v>129</v>
       </c>
       <c r="F27" t="n">
-        <v>74.98833333333332</v>
+        <v>2247.89</v>
       </c>
       <c r="G27" t="n">
         <v>0</v>
@@ -5798,39 +5798,6 @@
         <v>0</v>
       </c>
       <c r="I27" t="inlineStr">
-        <is>
-          <t>White Mulberry</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr"/>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>WM-SBV-Gas Spring MA- B0DB5VG39T- Phrase</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>B0DB5VG39T</t>
-        </is>
-      </c>
-      <c r="D28" t="n">
-        <v>16265</v>
-      </c>
-      <c r="E28" t="n">
-        <v>129</v>
-      </c>
-      <c r="F28" t="n">
-        <v>2247.89</v>
-      </c>
-      <c r="G28" t="n">
-        <v>0</v>
-      </c>
-      <c r="H28" t="n">
-        <v>0</v>
-      </c>
-      <c r="I28" t="inlineStr">
         <is>
           <t>White Mulberry</t>
         </is>

--- a/data/ams_weekly_data/White_Mulberry/ads_report_week22.xlsx
+++ b/data/ams_weekly_data/White_Mulberry/ads_report_week22.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H140"/>
+  <dimension ref="A1:H139"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -529,13 +529,13 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>755.02</v>
+        <v>419.75</v>
       </c>
       <c r="E4" t="n">
-        <v>25</v>
+        <v>14</v>
       </c>
       <c r="F4" t="n">
-        <v>4293</v>
+        <v>2399</v>
       </c>
       <c r="G4" t="n">
         <v>0</v>
@@ -613,13 +613,13 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>1686.64</v>
+        <v>1453.69</v>
       </c>
       <c r="E7" t="n">
-        <v>46</v>
+        <v>38</v>
       </c>
       <c r="F7" t="n">
-        <v>4613</v>
+        <v>3511</v>
       </c>
       <c r="G7" t="n">
         <v>12712.72</v>
@@ -815,7 +815,7 @@
         <v>14</v>
       </c>
       <c r="F14" t="n">
-        <v>1395</v>
+        <v>1264</v>
       </c>
       <c r="G14" t="n">
         <v>0</v>
@@ -1033,13 +1033,13 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>4360.23</v>
+        <v>3717.25</v>
       </c>
       <c r="E22" t="n">
-        <v>196</v>
+        <v>164</v>
       </c>
       <c r="F22" t="n">
-        <v>32059</v>
+        <v>27844</v>
       </c>
       <c r="G22" t="n">
         <v>0</v>
@@ -1061,13 +1061,13 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>617.98</v>
+        <v>545.05</v>
       </c>
       <c r="E23" t="n">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="F23" t="n">
-        <v>6749</v>
+        <v>6020</v>
       </c>
       <c r="G23" t="n">
         <v>0</v>
@@ -1089,13 +1089,13 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>483.13</v>
+        <v>396.88</v>
       </c>
       <c r="E24" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="F24" t="n">
-        <v>2235</v>
+        <v>2169</v>
       </c>
       <c r="G24" t="n">
         <v>7202.54</v>
@@ -1117,13 +1117,13 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>76.38</v>
+        <v>0</v>
       </c>
       <c r="E25" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F25" t="n">
-        <v>448</v>
+        <v>242</v>
       </c>
       <c r="G25" t="n">
         <v>0</v>
@@ -1145,19 +1145,19 @@
         </is>
       </c>
       <c r="D26" t="n">
-        <v>1541.99</v>
+        <v>1342.88</v>
       </c>
       <c r="E26" t="n">
-        <v>64</v>
+        <v>54</v>
       </c>
       <c r="F26" t="n">
-        <v>6711</v>
+        <v>5231</v>
       </c>
       <c r="G26" t="n">
-        <v>7075.42</v>
+        <v>0</v>
       </c>
       <c r="H26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="27">
@@ -1179,7 +1179,7 @@
         <v>9</v>
       </c>
       <c r="F27" t="n">
-        <v>1469</v>
+        <v>1382</v>
       </c>
       <c r="G27" t="n">
         <v>0</v>
@@ -1201,13 +1201,13 @@
         </is>
       </c>
       <c r="D28" t="n">
-        <v>133.16</v>
+        <v>117.55</v>
       </c>
       <c r="E28" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F28" t="n">
-        <v>831</v>
+        <v>799</v>
       </c>
       <c r="G28" t="n">
         <v>0</v>
@@ -1229,13 +1229,13 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>771.41</v>
+        <v>667.89</v>
       </c>
       <c r="E29" t="n">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="F29" t="n">
-        <v>6303</v>
+        <v>5417</v>
       </c>
       <c r="G29" t="n">
         <v>0</v>
@@ -1257,13 +1257,13 @@
         </is>
       </c>
       <c r="D30" t="n">
-        <v>4472.37</v>
+        <v>3831.96</v>
       </c>
       <c r="E30" t="n">
-        <v>165</v>
+        <v>141</v>
       </c>
       <c r="F30" t="n">
-        <v>46188</v>
+        <v>38433</v>
       </c>
       <c r="G30" t="n">
         <v>0</v>
@@ -1285,13 +1285,13 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>303.31</v>
+        <v>171.19</v>
       </c>
       <c r="E31" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="F31" t="n">
-        <v>3291</v>
+        <v>2979</v>
       </c>
       <c r="G31" t="n">
         <v>0</v>
@@ -1313,19 +1313,19 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>138.13</v>
+        <v>118.49</v>
       </c>
       <c r="E32" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F32" t="n">
-        <v>1625</v>
+        <v>1496</v>
       </c>
       <c r="G32" t="n">
-        <v>0</v>
+        <v>7075.42</v>
       </c>
       <c r="H32" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="33">
@@ -1341,13 +1341,13 @@
         </is>
       </c>
       <c r="D33" t="n">
-        <v>3062.51</v>
+        <v>2636.23</v>
       </c>
       <c r="E33" t="n">
-        <v>127</v>
+        <v>112</v>
       </c>
       <c r="F33" t="n">
-        <v>40004</v>
+        <v>36803</v>
       </c>
       <c r="G33" t="n">
         <v>0</v>
@@ -1369,13 +1369,13 @@
         </is>
       </c>
       <c r="D34" t="n">
-        <v>184</v>
+        <v>170.35</v>
       </c>
       <c r="E34" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F34" t="n">
-        <v>3868</v>
+        <v>3541</v>
       </c>
       <c r="G34" t="n">
         <v>0</v>
@@ -1481,16 +1481,16 @@
         </is>
       </c>
       <c r="D38" t="n">
-        <v>1107.41</v>
+        <v>987.98</v>
       </c>
       <c r="E38" t="n">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="F38" t="n">
-        <v>6460</v>
+        <v>5854</v>
       </c>
       <c r="G38" t="n">
-        <v>19915.25</v>
+        <v>7202.54</v>
       </c>
       <c r="H38" t="n">
         <v>2</v>
@@ -1509,13 +1509,13 @@
         </is>
       </c>
       <c r="D39" t="n">
-        <v>543.76</v>
+        <v>516.85</v>
       </c>
       <c r="E39" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F39" t="n">
-        <v>4854</v>
+        <v>4128</v>
       </c>
       <c r="G39" t="n">
         <v>0</v>
@@ -1537,19 +1537,19 @@
         </is>
       </c>
       <c r="D40" t="n">
-        <v>1179.48</v>
+        <v>1004.43</v>
       </c>
       <c r="E40" t="n">
-        <v>54</v>
+        <v>47</v>
       </c>
       <c r="F40" t="n">
-        <v>7559</v>
+        <v>4831</v>
       </c>
       <c r="G40" t="n">
-        <v>12712.71</v>
+        <v>0</v>
       </c>
       <c r="H40" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="41">
@@ -1593,13 +1593,13 @@
         </is>
       </c>
       <c r="D42" t="n">
-        <v>545.9300000000001</v>
+        <v>415.17</v>
       </c>
       <c r="E42" t="n">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="F42" t="n">
-        <v>13229</v>
+        <v>10827</v>
       </c>
       <c r="G42" t="n">
         <v>0</v>
@@ -1621,19 +1621,19 @@
         </is>
       </c>
       <c r="D43" t="n">
-        <v>261.6</v>
+        <v>202.5</v>
       </c>
       <c r="E43" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F43" t="n">
-        <v>1363</v>
+        <v>863</v>
       </c>
       <c r="G43" t="n">
-        <v>11677.12</v>
+        <v>0</v>
       </c>
       <c r="H43" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="44">
@@ -1649,13 +1649,13 @@
         </is>
       </c>
       <c r="D44" t="n">
-        <v>943.2</v>
+        <v>479.15</v>
       </c>
       <c r="E44" t="n">
-        <v>69</v>
+        <v>37</v>
       </c>
       <c r="F44" t="n">
-        <v>12369</v>
+        <v>9929</v>
       </c>
       <c r="G44" t="n">
         <v>0</v>
@@ -1677,13 +1677,13 @@
         </is>
       </c>
       <c r="D45" t="n">
-        <v>688.99</v>
+        <v>330.6</v>
       </c>
       <c r="E45" t="n">
-        <v>51</v>
+        <v>26</v>
       </c>
       <c r="F45" t="n">
-        <v>2640</v>
+        <v>1434</v>
       </c>
       <c r="G45" t="n">
         <v>0</v>
@@ -1705,19 +1705,19 @@
         </is>
       </c>
       <c r="D46" t="n">
-        <v>792.47</v>
+        <v>440.12</v>
       </c>
       <c r="E46" t="n">
-        <v>74</v>
+        <v>40</v>
       </c>
       <c r="F46" t="n">
-        <v>4607</v>
+        <v>2686</v>
       </c>
       <c r="G46" t="n">
-        <v>14066.1</v>
+        <v>0</v>
       </c>
       <c r="H46" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="47">
@@ -1733,13 +1733,13 @@
         </is>
       </c>
       <c r="D47" t="n">
-        <v>488.48</v>
+        <v>280.14</v>
       </c>
       <c r="E47" t="n">
-        <v>30</v>
+        <v>18</v>
       </c>
       <c r="F47" t="n">
-        <v>2279</v>
+        <v>1377</v>
       </c>
       <c r="G47" t="n">
         <v>0</v>
@@ -1761,13 +1761,13 @@
         </is>
       </c>
       <c r="D48" t="n">
-        <v>2183.64</v>
+        <v>2073.13</v>
       </c>
       <c r="E48" t="n">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="F48" t="n">
-        <v>8371</v>
+        <v>7620</v>
       </c>
       <c r="G48" t="n">
         <v>12712.72</v>
@@ -1789,13 +1789,13 @@
         </is>
       </c>
       <c r="D49" t="n">
-        <v>553.2</v>
+        <v>403.12</v>
       </c>
       <c r="E49" t="n">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="F49" t="n">
-        <v>2773</v>
+        <v>1589</v>
       </c>
       <c r="G49" t="n">
         <v>0</v>
@@ -1817,13 +1817,13 @@
         </is>
       </c>
       <c r="D50" t="n">
-        <v>351.92</v>
+        <v>308.95</v>
       </c>
       <c r="E50" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="F50" t="n">
-        <v>1882</v>
+        <v>1086</v>
       </c>
       <c r="G50" t="n">
         <v>0</v>
@@ -1851,7 +1851,7 @@
         <v>3</v>
       </c>
       <c r="F51" t="n">
-        <v>269</v>
+        <v>236</v>
       </c>
       <c r="G51" t="n">
         <v>0</v>
@@ -1873,13 +1873,13 @@
         </is>
       </c>
       <c r="D52" t="n">
-        <v>1006.94</v>
+        <v>658.6600000000001</v>
       </c>
       <c r="E52" t="n">
-        <v>38</v>
+        <v>25</v>
       </c>
       <c r="F52" t="n">
-        <v>33958</v>
+        <v>20309</v>
       </c>
       <c r="G52" t="n">
         <v>0</v>
@@ -1907,7 +1907,7 @@
         <v>8</v>
       </c>
       <c r="F53" t="n">
-        <v>2724</v>
+        <v>2164</v>
       </c>
       <c r="G53" t="n">
         <v>0</v>
@@ -1929,19 +1929,19 @@
         </is>
       </c>
       <c r="D54" t="n">
-        <v>1926.05</v>
+        <v>1216.53</v>
       </c>
       <c r="E54" t="n">
-        <v>153</v>
+        <v>102</v>
       </c>
       <c r="F54" t="n">
-        <v>19168</v>
+        <v>12088</v>
       </c>
       <c r="G54" t="n">
-        <v>14405.08</v>
+        <v>7202.54</v>
       </c>
       <c r="H54" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="55">
@@ -2013,13 +2013,13 @@
         </is>
       </c>
       <c r="D57" t="n">
-        <v>217.11</v>
+        <v>139.94</v>
       </c>
       <c r="E57" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="F57" t="n">
-        <v>2520</v>
+        <v>2149</v>
       </c>
       <c r="G57" t="n">
         <v>0</v>
@@ -2047,7 +2047,7 @@
         <v>0</v>
       </c>
       <c r="F58" t="n">
-        <v>566</v>
+        <v>506</v>
       </c>
       <c r="G58" t="n">
         <v>0</v>
@@ -2069,13 +2069,13 @@
         </is>
       </c>
       <c r="D59" t="n">
-        <v>123.9</v>
+        <v>118.88</v>
       </c>
       <c r="E59" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F59" t="n">
-        <v>1390</v>
+        <v>1017</v>
       </c>
       <c r="G59" t="n">
         <v>0</v>
@@ -2097,13 +2097,13 @@
         </is>
       </c>
       <c r="D60" t="n">
-        <v>1085.58</v>
+        <v>860</v>
       </c>
       <c r="E60" t="n">
-        <v>48</v>
+        <v>36</v>
       </c>
       <c r="F60" t="n">
-        <v>3026</v>
+        <v>2254</v>
       </c>
       <c r="G60" t="n">
         <v>0</v>
@@ -2125,13 +2125,13 @@
         </is>
       </c>
       <c r="D61" t="n">
-        <v>575.12</v>
+        <v>537.1</v>
       </c>
       <c r="E61" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="F61" t="n">
-        <v>3546</v>
+        <v>2696</v>
       </c>
       <c r="G61" t="n">
         <v>0</v>
@@ -2181,13 +2181,13 @@
         </is>
       </c>
       <c r="D63" t="n">
-        <v>1687.55</v>
+        <v>1430.06</v>
       </c>
       <c r="E63" t="n">
-        <v>94</v>
+        <v>79</v>
       </c>
       <c r="F63" t="n">
-        <v>12108</v>
+        <v>10235</v>
       </c>
       <c r="G63" t="n">
         <v>2329.66</v>
@@ -2209,13 +2209,13 @@
         </is>
       </c>
       <c r="D64" t="n">
-        <v>326.34</v>
+        <v>253.26</v>
       </c>
       <c r="E64" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="F64" t="n">
-        <v>2071</v>
+        <v>1604</v>
       </c>
       <c r="G64" t="n">
         <v>0</v>
@@ -2237,13 +2237,13 @@
         </is>
       </c>
       <c r="D65" t="n">
-        <v>1233.56</v>
+        <v>890.66</v>
       </c>
       <c r="E65" t="n">
-        <v>58</v>
+        <v>41</v>
       </c>
       <c r="F65" t="n">
-        <v>3308</v>
+        <v>2681</v>
       </c>
       <c r="G65" t="n">
         <v>1694.07</v>
@@ -2265,19 +2265,19 @@
         </is>
       </c>
       <c r="D66" t="n">
-        <v>510.75</v>
+        <v>146.98</v>
       </c>
       <c r="E66" t="n">
-        <v>27</v>
+        <v>6</v>
       </c>
       <c r="F66" t="n">
-        <v>996</v>
+        <v>371</v>
       </c>
       <c r="G66" t="n">
-        <v>5387.28</v>
+        <v>1795.76</v>
       </c>
       <c r="H66" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="67">
@@ -2293,13 +2293,13 @@
         </is>
       </c>
       <c r="D67" t="n">
-        <v>541.51</v>
+        <v>418.47</v>
       </c>
       <c r="E67" t="n">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="F67" t="n">
-        <v>612</v>
+        <v>549</v>
       </c>
       <c r="G67" t="n">
         <v>0</v>
@@ -2321,13 +2321,13 @@
         </is>
       </c>
       <c r="D68" t="n">
-        <v>1428.23</v>
+        <v>1213.77</v>
       </c>
       <c r="E68" t="n">
-        <v>61</v>
+        <v>52</v>
       </c>
       <c r="F68" t="n">
-        <v>10719</v>
+        <v>9586</v>
       </c>
       <c r="G68" t="n">
         <v>5252.55</v>
@@ -2349,13 +2349,13 @@
         </is>
       </c>
       <c r="D69" t="n">
-        <v>286.72</v>
+        <v>142.09</v>
       </c>
       <c r="E69" t="n">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="F69" t="n">
-        <v>1732</v>
+        <v>766</v>
       </c>
       <c r="G69" t="n">
         <v>0</v>
@@ -2377,13 +2377,13 @@
         </is>
       </c>
       <c r="D70" t="n">
-        <v>1207.5</v>
+        <v>1031.02</v>
       </c>
       <c r="E70" t="n">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="F70" t="n">
-        <v>3646</v>
+        <v>3273</v>
       </c>
       <c r="G70" t="n">
         <v>2965.26</v>
@@ -2405,13 +2405,13 @@
         </is>
       </c>
       <c r="D71" t="n">
-        <v>1089.28</v>
+        <v>865.3299999999999</v>
       </c>
       <c r="E71" t="n">
-        <v>38</v>
+        <v>29</v>
       </c>
       <c r="F71" t="n">
-        <v>7781</v>
+        <v>6086</v>
       </c>
       <c r="G71" t="n">
         <v>0</v>
@@ -2433,13 +2433,13 @@
         </is>
       </c>
       <c r="D72" t="n">
-        <v>622.13</v>
+        <v>429.67</v>
       </c>
       <c r="E72" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="F72" t="n">
-        <v>23498</v>
+        <v>14074</v>
       </c>
       <c r="G72" t="n">
         <v>0</v>
@@ -2461,13 +2461,13 @@
         </is>
       </c>
       <c r="D73" t="n">
-        <v>902.6800000000001</v>
+        <v>534.77</v>
       </c>
       <c r="E73" t="n">
-        <v>36</v>
+        <v>21</v>
       </c>
       <c r="F73" t="n">
-        <v>9205</v>
+        <v>4210</v>
       </c>
       <c r="G73" t="n">
         <v>0</v>
@@ -2489,13 +2489,13 @@
         </is>
       </c>
       <c r="D74" t="n">
-        <v>3602.95</v>
+        <v>3041.37</v>
       </c>
       <c r="E74" t="n">
-        <v>193</v>
+        <v>157</v>
       </c>
       <c r="F74" t="n">
-        <v>25247</v>
+        <v>18822</v>
       </c>
       <c r="G74" t="n">
         <v>5082.2</v>
@@ -2517,13 +2517,13 @@
         </is>
       </c>
       <c r="D75" t="n">
-        <v>1363.73</v>
+        <v>1205.44</v>
       </c>
       <c r="E75" t="n">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="F75" t="n">
-        <v>1653</v>
+        <v>1572</v>
       </c>
       <c r="G75" t="n">
         <v>5922.04</v>
@@ -2545,13 +2545,13 @@
         </is>
       </c>
       <c r="D76" t="n">
-        <v>1447.91</v>
+        <v>1308.46</v>
       </c>
       <c r="E76" t="n">
-        <v>56</v>
+        <v>51</v>
       </c>
       <c r="F76" t="n">
-        <v>7686</v>
+        <v>6091</v>
       </c>
       <c r="G76" t="n">
         <v>1355.08</v>
@@ -2573,13 +2573,13 @@
         </is>
       </c>
       <c r="D77" t="n">
-        <v>613.95</v>
+        <v>421.22</v>
       </c>
       <c r="E77" t="n">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="F77" t="n">
-        <v>2167</v>
+        <v>1681</v>
       </c>
       <c r="G77" t="n">
         <v>0</v>
@@ -2601,13 +2601,13 @@
         </is>
       </c>
       <c r="D78" t="n">
-        <v>906.83</v>
+        <v>899.79</v>
       </c>
       <c r="E78" t="n">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="F78" t="n">
-        <v>9390</v>
+        <v>9126</v>
       </c>
       <c r="G78" t="n">
         <v>3388.14</v>
@@ -2629,13 +2629,13 @@
         </is>
       </c>
       <c r="D79" t="n">
-        <v>645.58</v>
+        <v>588.22</v>
       </c>
       <c r="E79" t="n">
-        <v>114</v>
+        <v>101</v>
       </c>
       <c r="F79" t="n">
-        <v>4347</v>
+        <v>4063</v>
       </c>
       <c r="G79" t="n">
         <v>10729.66</v>
@@ -2657,13 +2657,13 @@
         </is>
       </c>
       <c r="D80" t="n">
-        <v>2234.79</v>
+        <v>2000.85</v>
       </c>
       <c r="E80" t="n">
-        <v>76</v>
+        <v>69</v>
       </c>
       <c r="F80" t="n">
-        <v>8428</v>
+        <v>7481</v>
       </c>
       <c r="G80" t="n">
         <v>7582.200000000001</v>
@@ -2685,19 +2685,19 @@
         </is>
       </c>
       <c r="D81" t="n">
-        <v>3734.61</v>
+        <v>3093.68</v>
       </c>
       <c r="E81" t="n">
-        <v>211</v>
+        <v>178</v>
       </c>
       <c r="F81" t="n">
-        <v>10800</v>
+        <v>9029</v>
       </c>
       <c r="G81" t="n">
-        <v>22277.1</v>
+        <v>19650.83</v>
       </c>
       <c r="H81" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="82">
@@ -2713,16 +2713,16 @@
         </is>
       </c>
       <c r="D82" t="n">
-        <v>2349.88</v>
+        <v>2054.29</v>
       </c>
       <c r="E82" t="n">
-        <v>131</v>
+        <v>113</v>
       </c>
       <c r="F82" t="n">
-        <v>5450</v>
+        <v>4850</v>
       </c>
       <c r="G82" t="n">
-        <v>13773.73</v>
+        <v>13931.36</v>
       </c>
       <c r="H82" t="n">
         <v>5</v>
@@ -2741,19 +2741,19 @@
         </is>
       </c>
       <c r="D83" t="n">
-        <v>6062.22</v>
+        <v>5243.16</v>
       </c>
       <c r="E83" t="n">
-        <v>278</v>
+        <v>235</v>
       </c>
       <c r="F83" t="n">
-        <v>32234</v>
+        <v>29595</v>
       </c>
       <c r="G83" t="n">
-        <v>19400.83</v>
+        <v>13978.8</v>
       </c>
       <c r="H83" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="84">
@@ -2769,19 +2769,19 @@
         </is>
       </c>
       <c r="D84" t="n">
-        <v>1628.61</v>
+        <v>905.7</v>
       </c>
       <c r="E84" t="n">
-        <v>99</v>
+        <v>54</v>
       </c>
       <c r="F84" t="n">
-        <v>24899</v>
+        <v>11941</v>
       </c>
       <c r="G84" t="n">
-        <v>2626.27</v>
+        <v>0</v>
       </c>
       <c r="H84" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="85">
@@ -2797,13 +2797,13 @@
         </is>
       </c>
       <c r="D85" t="n">
-        <v>690.05</v>
+        <v>474.89</v>
       </c>
       <c r="E85" t="n">
-        <v>27</v>
+        <v>18</v>
       </c>
       <c r="F85" t="n">
-        <v>15147</v>
+        <v>10658</v>
       </c>
       <c r="G85" t="n">
         <v>2626.27</v>
@@ -2825,13 +2825,13 @@
         </is>
       </c>
       <c r="D86" t="n">
-        <v>2516.66</v>
+        <v>1953.89</v>
       </c>
       <c r="E86" t="n">
-        <v>94</v>
+        <v>71</v>
       </c>
       <c r="F86" t="n">
-        <v>8975</v>
+        <v>6612</v>
       </c>
       <c r="G86" t="n">
         <v>6988.98</v>
@@ -2853,13 +2853,13 @@
         </is>
       </c>
       <c r="D87" t="n">
-        <v>976.26</v>
+        <v>646.0699999999999</v>
       </c>
       <c r="E87" t="n">
-        <v>62</v>
+        <v>41</v>
       </c>
       <c r="F87" t="n">
-        <v>12322</v>
+        <v>9415</v>
       </c>
       <c r="G87" t="n">
         <v>0</v>
@@ -2881,13 +2881,13 @@
         </is>
       </c>
       <c r="D88" t="n">
-        <v>312.29</v>
+        <v>114.05</v>
       </c>
       <c r="E88" t="n">
-        <v>18</v>
+        <v>6</v>
       </c>
       <c r="F88" t="n">
-        <v>7788</v>
+        <v>4112</v>
       </c>
       <c r="G88" t="n">
         <v>0</v>
@@ -2915,7 +2915,7 @@
         <v>39</v>
       </c>
       <c r="F89" t="n">
-        <v>3575</v>
+        <v>3174</v>
       </c>
       <c r="G89" t="n">
         <v>0</v>
@@ -2943,7 +2943,7 @@
         <v>21</v>
       </c>
       <c r="F90" t="n">
-        <v>3972</v>
+        <v>3395</v>
       </c>
       <c r="G90" t="n">
         <v>0</v>
@@ -2961,17 +2961,17 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>B0DB5YTQZV</t>
+          <t>B0DP2WC5VW</t>
         </is>
       </c>
       <c r="D91" t="n">
-        <v>0</v>
+        <v>579.5599999999999</v>
       </c>
       <c r="E91" t="n">
-        <v>0</v>
+        <v>37</v>
       </c>
       <c r="F91" t="n">
-        <v>0</v>
+        <v>10889</v>
       </c>
       <c r="G91" t="n">
         <v>0</v>
@@ -2989,17 +2989,17 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>B0DP2WC5VW</t>
+          <t>B0DP2Z5DQ9</t>
         </is>
       </c>
       <c r="D92" t="n">
-        <v>733.4200000000001</v>
+        <v>136.04</v>
       </c>
       <c r="E92" t="n">
-        <v>46</v>
+        <v>7</v>
       </c>
       <c r="F92" t="n">
-        <v>13786</v>
+        <v>1845</v>
       </c>
       <c r="G92" t="n">
         <v>0</v>
@@ -3017,17 +3017,17 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>B0DP2Z5DQ9</t>
+          <t>B0DP32F346</t>
         </is>
       </c>
       <c r="D93" t="n">
-        <v>136.04</v>
+        <v>107.6</v>
       </c>
       <c r="E93" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F93" t="n">
-        <v>1849</v>
+        <v>4408</v>
       </c>
       <c r="G93" t="n">
         <v>0</v>
@@ -3040,28 +3040,28 @@
       <c r="A94" t="inlineStr"/>
       <c r="B94" t="inlineStr">
         <is>
-          <t>WM-SP- Monitor Arms- Multi Asins - AT</t>
+          <t>WM-SP- Monitor Arms- Multi Asins - CT</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>B0DP32F346</t>
+          <t>B0DB5W4TCP</t>
         </is>
       </c>
       <c r="D94" t="n">
-        <v>121.44</v>
+        <v>267.85</v>
       </c>
       <c r="E94" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="F94" t="n">
-        <v>5615</v>
+        <v>1779</v>
       </c>
       <c r="G94" t="n">
-        <v>0</v>
+        <v>1355.08</v>
       </c>
       <c r="H94" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="95">
@@ -3073,23 +3073,23 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>B0DB5W4TCP</t>
+          <t>B0DB5YTQZV</t>
         </is>
       </c>
       <c r="D95" t="n">
-        <v>285.01</v>
+        <v>275.69</v>
       </c>
       <c r="E95" t="n">
         <v>14</v>
       </c>
       <c r="F95" t="n">
-        <v>1903</v>
+        <v>3108</v>
       </c>
       <c r="G95" t="n">
-        <v>1355.08</v>
+        <v>0</v>
       </c>
       <c r="H95" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="96">
@@ -3101,17 +3101,17 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>B0DB5YTQZV</t>
+          <t>B0DP2WC5VW</t>
         </is>
       </c>
       <c r="D96" t="n">
-        <v>320.24</v>
+        <v>492.43</v>
       </c>
       <c r="E96" t="n">
-        <v>16</v>
+        <v>27</v>
       </c>
       <c r="F96" t="n">
-        <v>3288</v>
+        <v>5267</v>
       </c>
       <c r="G96" t="n">
         <v>0</v>
@@ -3129,17 +3129,17 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>B0DP2WC5VW</t>
+          <t>B0DP2Z5DQ9</t>
         </is>
       </c>
       <c r="D97" t="n">
-        <v>557.08</v>
+        <v>273.23</v>
       </c>
       <c r="E97" t="n">
-        <v>30</v>
+        <v>13</v>
       </c>
       <c r="F97" t="n">
-        <v>5829</v>
+        <v>1921</v>
       </c>
       <c r="G97" t="n">
         <v>0</v>
@@ -3157,17 +3157,17 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>B0DP2Z5DQ9</t>
+          <t>B0DP32F346</t>
         </is>
       </c>
       <c r="D98" t="n">
-        <v>291.08</v>
+        <v>197.49</v>
       </c>
       <c r="E98" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="F98" t="n">
-        <v>1997</v>
+        <v>1060</v>
       </c>
       <c r="G98" t="n">
         <v>0</v>
@@ -3180,28 +3180,28 @@
       <c r="A99" t="inlineStr"/>
       <c r="B99" t="inlineStr">
         <is>
-          <t>WM-SP- Monitor Arms- Multi Asins - CT</t>
+          <t>WM-SP- Monitor Arms- Multi Asins - exact</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>B0DP32F346</t>
+          <t>B0DB5W4TCP</t>
         </is>
       </c>
       <c r="D99" t="n">
-        <v>197.49</v>
+        <v>785.24</v>
       </c>
       <c r="E99" t="n">
-        <v>13</v>
+        <v>44</v>
       </c>
       <c r="F99" t="n">
-        <v>1176</v>
+        <v>31702</v>
       </c>
       <c r="G99" t="n">
-        <v>0</v>
+        <v>1355.08</v>
       </c>
       <c r="H99" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="100">
@@ -3213,51 +3213,51 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>B0DB5W4TCP</t>
+          <t>B0DP2WC5VW</t>
         </is>
       </c>
       <c r="D100" t="n">
-        <v>946.8</v>
+        <v>1580.89</v>
       </c>
       <c r="E100" t="n">
-        <v>51</v>
+        <v>92</v>
       </c>
       <c r="F100" t="n">
-        <v>35442</v>
+        <v>41824</v>
       </c>
       <c r="G100" t="n">
-        <v>1355.08</v>
+        <v>5252.54</v>
       </c>
       <c r="H100" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr"/>
       <c r="B101" t="inlineStr">
         <is>
-          <t>WM-SP- Monitor Arms- Multi Asins - exact</t>
+          <t>WM-SP- Premium Monitor Arms- Multi Asins -Phrase</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>B0DP2WC5VW</t>
+          <t>B0DP3194QN</t>
         </is>
       </c>
       <c r="D101" t="n">
-        <v>2012.71</v>
+        <v>24.01</v>
       </c>
       <c r="E101" t="n">
-        <v>111</v>
+        <v>1</v>
       </c>
       <c r="F101" t="n">
-        <v>47802</v>
+        <v>317</v>
       </c>
       <c r="G101" t="n">
-        <v>5252.54</v>
+        <v>0</v>
       </c>
       <c r="H101" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="102">
@@ -3269,51 +3269,51 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>B0DP3194QN</t>
+          <t>B0DP32F346</t>
         </is>
       </c>
       <c r="D102" t="n">
-        <v>81.05</v>
+        <v>1905.61</v>
       </c>
       <c r="E102" t="n">
-        <v>3</v>
+        <v>88</v>
       </c>
       <c r="F102" t="n">
-        <v>571</v>
+        <v>31964</v>
       </c>
       <c r="G102" t="n">
-        <v>0</v>
+        <v>13004.23</v>
       </c>
       <c r="H102" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr"/>
       <c r="B103" t="inlineStr">
         <is>
-          <t>WM-SP- Premium Monitor Arms- Multi Asins -Phrase</t>
+          <t>WM-SP-Gas Spring -Multi Asins- Phrase &amp; Exact</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>B0DP32F346</t>
+          <t>B0DB5VG39T</t>
         </is>
       </c>
       <c r="D103" t="n">
-        <v>2078.3</v>
+        <v>2260.54</v>
       </c>
       <c r="E103" t="n">
-        <v>96</v>
+        <v>103</v>
       </c>
       <c r="F103" t="n">
-        <v>33533</v>
+        <v>56048</v>
       </c>
       <c r="G103" t="n">
-        <v>13004.23</v>
+        <v>9532.200000000001</v>
       </c>
       <c r="H103" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="104">
@@ -3325,58 +3325,58 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>B0DB5VG39T</t>
+          <t>B0DB5VVPSB</t>
         </is>
       </c>
       <c r="D104" t="n">
-        <v>2666.81</v>
+        <v>330.96</v>
       </c>
       <c r="E104" t="n">
-        <v>124</v>
+        <v>15</v>
       </c>
       <c r="F104" t="n">
-        <v>67246</v>
+        <v>2839</v>
       </c>
       <c r="G104" t="n">
-        <v>9532.200000000001</v>
+        <v>0</v>
       </c>
       <c r="H104" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr"/>
       <c r="B105" t="inlineStr">
         <is>
-          <t>WM-SP-Gas Spring -Multi Asins- Phrase &amp; Exact</t>
+          <t>WM-SP-Gas Spring MA- B0DB5VG39T- Broad</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>B0DB5VVPSB</t>
+          <t>B0DB5VG39T</t>
         </is>
       </c>
       <c r="D105" t="n">
-        <v>339.67</v>
+        <v>2027.23</v>
       </c>
       <c r="E105" t="n">
-        <v>16</v>
+        <v>146</v>
       </c>
       <c r="F105" t="n">
-        <v>3186</v>
+        <v>21040</v>
       </c>
       <c r="G105" t="n">
-        <v>3812.71</v>
+        <v>13299.99</v>
       </c>
       <c r="H105" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr"/>
       <c r="B106" t="inlineStr">
         <is>
-          <t>WM-SP-Gas Spring MA- B0DB5VG39T- Broad</t>
+          <t>WM-SP-Gas Spring MA- B0DB5VG39T- Exact &amp; Phrase</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
@@ -3385,26 +3385,26 @@
         </is>
       </c>
       <c r="D106" t="n">
-        <v>2198.05</v>
+        <v>541.79</v>
       </c>
       <c r="E106" t="n">
-        <v>160</v>
+        <v>16</v>
       </c>
       <c r="F106" t="n">
-        <v>23021</v>
+        <v>1786</v>
       </c>
       <c r="G106" t="n">
-        <v>15629.65</v>
+        <v>4955.93</v>
       </c>
       <c r="H106" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr"/>
       <c r="B107" t="inlineStr">
         <is>
-          <t>WM-SP-Gas Spring MA- B0DB5VG39T- Exact &amp; Phrase</t>
+          <t>WM-SP-Gas Spring MA- B0DB5VG39T/B0DB5VVPSB- PT</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
@@ -3413,19 +3413,19 @@
         </is>
       </c>
       <c r="D107" t="n">
-        <v>1055.61</v>
+        <v>1596.87</v>
       </c>
       <c r="E107" t="n">
-        <v>31</v>
+        <v>50</v>
       </c>
       <c r="F107" t="n">
-        <v>4475</v>
+        <v>4529</v>
       </c>
       <c r="G107" t="n">
-        <v>4955.93</v>
+        <v>2626.27</v>
       </c>
       <c r="H107" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="108">
@@ -3437,45 +3437,45 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>B0DB5VG39T</t>
+          <t>B0DB5VVPSB</t>
         </is>
       </c>
       <c r="D108" t="n">
-        <v>1676.92</v>
+        <v>598.7</v>
       </c>
       <c r="E108" t="n">
-        <v>52</v>
+        <v>20</v>
       </c>
       <c r="F108" t="n">
-        <v>5400</v>
+        <v>1778</v>
       </c>
       <c r="G108" t="n">
-        <v>5083.05</v>
+        <v>0</v>
       </c>
       <c r="H108" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr"/>
       <c r="B109" t="inlineStr">
         <is>
-          <t>WM-SP-Gas Spring MA- B0DB5VG39T/B0DB5VVPSB- PT</t>
+          <t>WM-SP-Monitor Arms- Branded</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>B0DB5VVPSB</t>
+          <t>B0DB5VG39T</t>
         </is>
       </c>
       <c r="D109" t="n">
-        <v>792.1799999999999</v>
+        <v>10.64</v>
       </c>
       <c r="E109" t="n">
-        <v>23</v>
+        <v>1</v>
       </c>
       <c r="F109" t="n">
-        <v>2005</v>
+        <v>233</v>
       </c>
       <c r="G109" t="n">
         <v>0</v>
@@ -3493,17 +3493,17 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>B0DB5VG39T</t>
+          <t>B0DB5VVPSB</t>
         </is>
       </c>
       <c r="D110" t="n">
-        <v>10.64</v>
+        <v>10.49</v>
       </c>
       <c r="E110" t="n">
         <v>1</v>
       </c>
       <c r="F110" t="n">
-        <v>233</v>
+        <v>201</v>
       </c>
       <c r="G110" t="n">
         <v>0</v>
@@ -3521,17 +3521,17 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>B0DB5VVPSB</t>
+          <t>B0DB5W4TCP</t>
         </is>
       </c>
       <c r="D111" t="n">
-        <v>10.49</v>
+        <v>0</v>
       </c>
       <c r="E111" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F111" t="n">
-        <v>201</v>
+        <v>498</v>
       </c>
       <c r="G111" t="n">
         <v>0</v>
@@ -3549,7 +3549,7 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>B0DB5W4TCP</t>
+          <t>B0DB5YTQZV</t>
         </is>
       </c>
       <c r="D112" t="n">
@@ -3559,7 +3559,7 @@
         <v>0</v>
       </c>
       <c r="F112" t="n">
-        <v>498</v>
+        <v>166</v>
       </c>
       <c r="G112" t="n">
         <v>0</v>
@@ -3577,7 +3577,7 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>B0DB5YTQZV</t>
+          <t>B0DP2Z5DQ9</t>
         </is>
       </c>
       <c r="D113" t="n">
@@ -3587,7 +3587,7 @@
         <v>0</v>
       </c>
       <c r="F113" t="n">
-        <v>166</v>
+        <v>573</v>
       </c>
       <c r="G113" t="n">
         <v>0</v>
@@ -3605,17 +3605,17 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>B0DP2Z5DQ9</t>
+          <t>B0DP32F346</t>
         </is>
       </c>
       <c r="D114" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="E114" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F114" t="n">
-        <v>573</v>
+        <v>893</v>
       </c>
       <c r="G114" t="n">
         <v>0</v>
@@ -3628,22 +3628,22 @@
       <c r="A115" t="inlineStr"/>
       <c r="B115" t="inlineStr">
         <is>
-          <t>WM-SP-Monitor Arms- Branded</t>
+          <t>WM-SP-Monitor Arms- Defensive</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>B0DP32F346</t>
+          <t>B0DB5VG39T</t>
         </is>
       </c>
       <c r="D115" t="n">
-        <v>10</v>
+        <v>65.27</v>
       </c>
       <c r="E115" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="F115" t="n">
-        <v>893</v>
+        <v>407</v>
       </c>
       <c r="G115" t="n">
         <v>0</v>
@@ -3661,23 +3661,23 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>B0DB5VG39T</t>
+          <t>B0DB5VVPSB</t>
         </is>
       </c>
       <c r="D116" t="n">
-        <v>65.27</v>
+        <v>140.73</v>
       </c>
       <c r="E116" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="F116" t="n">
-        <v>407</v>
+        <v>1106</v>
       </c>
       <c r="G116" t="n">
-        <v>0</v>
+        <v>3812.72</v>
       </c>
       <c r="H116" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="117">
@@ -3689,23 +3689,23 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>B0DB5VVPSB</t>
+          <t>B0DB5W4TCP</t>
         </is>
       </c>
       <c r="D117" t="n">
-        <v>140.73</v>
+        <v>23.96</v>
       </c>
       <c r="E117" t="n">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="F117" t="n">
-        <v>1108</v>
+        <v>453</v>
       </c>
       <c r="G117" t="n">
-        <v>3812.72</v>
+        <v>0</v>
       </c>
       <c r="H117" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="118">
@@ -3717,17 +3717,17 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>B0DB5W4TCP</t>
+          <t>B0DB5YTQZV</t>
         </is>
       </c>
       <c r="D118" t="n">
-        <v>23.96</v>
+        <v>163.73</v>
       </c>
       <c r="E118" t="n">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="F118" t="n">
-        <v>453</v>
+        <v>2406</v>
       </c>
       <c r="G118" t="n">
         <v>0</v>
@@ -3745,23 +3745,23 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>B0DB5YTQZV</t>
+          <t>B0DP2Z5DQ9</t>
         </is>
       </c>
       <c r="D119" t="n">
-        <v>163.73</v>
+        <v>150.22</v>
       </c>
       <c r="E119" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="F119" t="n">
-        <v>2406</v>
+        <v>1200</v>
       </c>
       <c r="G119" t="n">
-        <v>0</v>
+        <v>2514.41</v>
       </c>
       <c r="H119" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="120">
@@ -3773,58 +3773,58 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>B0DP2Z5DQ9</t>
+          <t>B0DP32F346</t>
         </is>
       </c>
       <c r="D120" t="n">
-        <v>150.22</v>
+        <v>38.99</v>
       </c>
       <c r="E120" t="n">
-        <v>14</v>
+        <v>3</v>
       </c>
       <c r="F120" t="n">
-        <v>1200</v>
+        <v>312</v>
       </c>
       <c r="G120" t="n">
-        <v>2514.41</v>
+        <v>0</v>
       </c>
       <c r="H120" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr"/>
       <c r="B121" t="inlineStr">
         <is>
-          <t>WM-SP-Monitor Arms- Defensive</t>
+          <t>WM-SP-Monitor Stand-B0DP2Z5DQ9 - PT</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>B0DP32F346</t>
+          <t>B0DP2Z5DQ9</t>
         </is>
       </c>
       <c r="D121" t="n">
-        <v>38.99</v>
+        <v>762.8399999999999</v>
       </c>
       <c r="E121" t="n">
+        <v>48</v>
+      </c>
+      <c r="F121" t="n">
+        <v>3791</v>
+      </c>
+      <c r="G121" t="n">
+        <v>5028.809999999999</v>
+      </c>
+      <c r="H121" t="n">
         <v>3</v>
-      </c>
-      <c r="F121" t="n">
-        <v>312</v>
-      </c>
-      <c r="G121" t="n">
-        <v>0</v>
-      </c>
-      <c r="H121" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr"/>
       <c r="B122" t="inlineStr">
         <is>
-          <t>WM-SP-Monitor Stand-B0DP2Z5DQ9 - PT</t>
+          <t>WM-SP-Monitor Stand-B0DP2Z5DQ9 - Phrase</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
@@ -3833,26 +3833,26 @@
         </is>
       </c>
       <c r="D122" t="n">
-        <v>847.8299999999999</v>
+        <v>1343.12</v>
       </c>
       <c r="E122" t="n">
-        <v>53</v>
+        <v>85</v>
       </c>
       <c r="F122" t="n">
-        <v>4129</v>
+        <v>9343</v>
       </c>
       <c r="G122" t="n">
-        <v>7543.219999999999</v>
+        <v>4849.139999999999</v>
       </c>
       <c r="H122" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr"/>
       <c r="B123" t="inlineStr">
         <is>
-          <t>WM-SP-Monitor Stand-B0DP2Z5DQ9 - Phrase</t>
+          <t>WM-SP-Monitor Stand-B0DP2Z5DQ9 -Phrase</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
@@ -3861,69 +3861,69 @@
         </is>
       </c>
       <c r="D123" t="n">
-        <v>1538.27</v>
+        <v>1081.89</v>
       </c>
       <c r="E123" t="n">
-        <v>97</v>
+        <v>51</v>
       </c>
       <c r="F123" t="n">
-        <v>10082</v>
+        <v>12209</v>
       </c>
       <c r="G123" t="n">
-        <v>7363.549999999999</v>
+        <v>15508.48</v>
       </c>
       <c r="H123" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr"/>
       <c r="B124" t="inlineStr">
         <is>
-          <t>WM-SP-Monitor Stand-B0DP2Z5DQ9 -Phrase</t>
+          <t>WM-SP-POS stand- Multi - PT</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>B0DP2Z5DQ9</t>
+          <t>B0FN4FPJ83</t>
         </is>
       </c>
       <c r="D124" t="n">
-        <v>1136.88</v>
+        <v>0</v>
       </c>
       <c r="E124" t="n">
-        <v>54</v>
+        <v>0</v>
       </c>
       <c r="F124" t="n">
-        <v>13754</v>
+        <v>8</v>
       </c>
       <c r="G124" t="n">
-        <v>15508.48</v>
+        <v>0</v>
       </c>
       <c r="H124" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr"/>
       <c r="B125" t="inlineStr">
         <is>
-          <t>WM-SP-POS stand- Multi - PT</t>
+          <t>WM-SP-TV Brackets- Multi Asins- CT</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>B0FN4FPJ83</t>
+          <t>B0FHVWHQHR</t>
         </is>
       </c>
       <c r="D125" t="n">
-        <v>0</v>
+        <v>60.49</v>
       </c>
       <c r="E125" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F125" t="n">
-        <v>10</v>
+        <v>395</v>
       </c>
       <c r="G125" t="n">
         <v>0</v>
@@ -3941,23 +3941,23 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>B0FHVWHQHR</t>
+          <t>B0FN4D3C89</t>
         </is>
       </c>
       <c r="D126" t="n">
-        <v>81.40000000000001</v>
+        <v>792.8</v>
       </c>
       <c r="E126" t="n">
-        <v>4</v>
+        <v>44</v>
       </c>
       <c r="F126" t="n">
-        <v>787</v>
+        <v>6377</v>
       </c>
       <c r="G126" t="n">
-        <v>0</v>
+        <v>363.56</v>
       </c>
       <c r="H126" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="127">
@@ -3969,20 +3969,20 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>B0FN4D3C89</t>
+          <t>B0FN4DSQ6P</t>
         </is>
       </c>
       <c r="D127" t="n">
-        <v>941.95</v>
+        <v>225.47</v>
       </c>
       <c r="E127" t="n">
-        <v>52</v>
+        <v>16</v>
       </c>
       <c r="F127" t="n">
-        <v>7699</v>
+        <v>2472</v>
       </c>
       <c r="G127" t="n">
-        <v>363.56</v>
+        <v>490.68</v>
       </c>
       <c r="H127" t="n">
         <v>1</v>
@@ -3997,45 +3997,45 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>B0FN4DSQ6P</t>
+          <t>B0FN4HDM6Z</t>
         </is>
       </c>
       <c r="D128" t="n">
-        <v>248.82</v>
+        <v>292.58</v>
       </c>
       <c r="E128" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F128" t="n">
-        <v>3030</v>
+        <v>2407</v>
       </c>
       <c r="G128" t="n">
-        <v>490.68</v>
+        <v>0</v>
       </c>
       <c r="H128" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr"/>
       <c r="B129" t="inlineStr">
         <is>
-          <t>WM-SP-TV Brackets- Multi Asins- CT</t>
+          <t>WM-SP-TV Brackets- Multi Asins- Exact</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>B0FN4HDM6Z</t>
+          <t>B0FHVWHQHR</t>
         </is>
       </c>
       <c r="D129" t="n">
-        <v>456.11</v>
+        <v>7.55</v>
       </c>
       <c r="E129" t="n">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="F129" t="n">
-        <v>2999</v>
+        <v>332</v>
       </c>
       <c r="G129" t="n">
         <v>0</v>
@@ -4053,23 +4053,23 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>B0FHVWHQHR</t>
+          <t>B0FN4D3C89</t>
         </is>
       </c>
       <c r="D130" t="n">
-        <v>7.55</v>
+        <v>811.5699999999999</v>
       </c>
       <c r="E130" t="n">
-        <v>1</v>
+        <v>99</v>
       </c>
       <c r="F130" t="n">
-        <v>405</v>
+        <v>21651</v>
       </c>
       <c r="G130" t="n">
-        <v>0</v>
+        <v>3053.4</v>
       </c>
       <c r="H130" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
     </row>
     <row r="131">
@@ -4081,51 +4081,51 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>B0FN4D3C89</t>
+          <t>B0FN4DSQ6P</t>
         </is>
       </c>
       <c r="D131" t="n">
-        <v>893.4300000000001</v>
+        <v>140.32</v>
       </c>
       <c r="E131" t="n">
-        <v>108</v>
+        <v>15</v>
       </c>
       <c r="F131" t="n">
-        <v>26055</v>
+        <v>3331</v>
       </c>
       <c r="G131" t="n">
-        <v>3544.08</v>
+        <v>1708.48</v>
       </c>
       <c r="H131" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr"/>
       <c r="B132" t="inlineStr">
         <is>
-          <t>WM-SP-TV Brackets- Multi Asins- Exact</t>
+          <t>WM-SP-TV Brackets- Multi Asins- PT</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>B0FN4DSQ6P</t>
+          <t>B0FHVWHQHR</t>
         </is>
       </c>
       <c r="D132" t="n">
-        <v>147.81</v>
+        <v>98.56</v>
       </c>
       <c r="E132" t="n">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="F132" t="n">
-        <v>3954</v>
+        <v>822</v>
       </c>
       <c r="G132" t="n">
-        <v>1708.48</v>
+        <v>617.8</v>
       </c>
       <c r="H132" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="133">
@@ -4137,23 +4137,23 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>B0FHVWHQHR</t>
+          <t>B0FN4D3C89</t>
         </is>
       </c>
       <c r="D133" t="n">
-        <v>98.56</v>
+        <v>727.13</v>
       </c>
       <c r="E133" t="n">
-        <v>5</v>
+        <v>34</v>
       </c>
       <c r="F133" t="n">
-        <v>946</v>
+        <v>4789</v>
       </c>
       <c r="G133" t="n">
-        <v>617.8</v>
+        <v>1581.36</v>
       </c>
       <c r="H133" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="134">
@@ -4165,23 +4165,23 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>B0FN4D3C89</t>
+          <t>B0FN4DSQ6P</t>
         </is>
       </c>
       <c r="D134" t="n">
-        <v>789.8099999999999</v>
+        <v>559.3399999999999</v>
       </c>
       <c r="E134" t="n">
-        <v>38</v>
+        <v>23</v>
       </c>
       <c r="F134" t="n">
-        <v>5413</v>
+        <v>2157</v>
       </c>
       <c r="G134" t="n">
-        <v>1581.36</v>
+        <v>2453.4</v>
       </c>
       <c r="H134" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="135">
@@ -4193,51 +4193,51 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>B0FN4DSQ6P</t>
+          <t>B0FN4HDM6Z</t>
         </is>
       </c>
       <c r="D135" t="n">
-        <v>559.3399999999999</v>
+        <v>629.0599999999999</v>
       </c>
       <c r="E135" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="F135" t="n">
-        <v>2390</v>
+        <v>1866</v>
       </c>
       <c r="G135" t="n">
-        <v>2453.4</v>
+        <v>0</v>
       </c>
       <c r="H135" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr"/>
       <c r="B136" t="inlineStr">
         <is>
-          <t>WM-SP-TV Brackets- Multi Asins- PT</t>
+          <t>WM-SP-TV Brackets- Multi Asins- PT01</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>B0FN4HDM6Z</t>
+          <t>B0FN4D3C89</t>
         </is>
       </c>
       <c r="D136" t="n">
-        <v>774.63</v>
+        <v>1160.23</v>
       </c>
       <c r="E136" t="n">
-        <v>31</v>
+        <v>85</v>
       </c>
       <c r="F136" t="n">
-        <v>2264</v>
+        <v>12612</v>
       </c>
       <c r="G136" t="n">
-        <v>0</v>
+        <v>2435.6</v>
       </c>
       <c r="H136" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
     </row>
     <row r="137">
@@ -4249,23 +4249,23 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>B0FN4D3C89</t>
+          <t>B0FN4DSQ6P</t>
         </is>
       </c>
       <c r="D137" t="n">
-        <v>1267.55</v>
+        <v>411.65</v>
       </c>
       <c r="E137" t="n">
-        <v>92</v>
+        <v>31</v>
       </c>
       <c r="F137" t="n">
-        <v>14276</v>
+        <v>3746</v>
       </c>
       <c r="G137" t="n">
-        <v>2435.6</v>
+        <v>1708.48</v>
       </c>
       <c r="H137" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
     </row>
     <row r="138">
@@ -4277,78 +4277,50 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>B0FN4DSQ6P</t>
+          <t>B0FN4GQ9HT</t>
         </is>
       </c>
       <c r="D138" t="n">
-        <v>488.96</v>
+        <v>78.28999999999999</v>
       </c>
       <c r="E138" t="n">
-        <v>36</v>
+        <v>5</v>
       </c>
       <c r="F138" t="n">
-        <v>4486</v>
+        <v>765</v>
       </c>
       <c r="G138" t="n">
-        <v>2199.16</v>
+        <v>0</v>
       </c>
       <c r="H138" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr"/>
       <c r="B139" t="inlineStr">
         <is>
-          <t>WM-SP-TV Brackets- Multi Asins- PT01</t>
+          <t>WM_SP_KT_Adjustable_Exact_Manual_HV</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>B0FN4GQ9HT</t>
+          <t>B0CPT3Q25C</t>
         </is>
       </c>
       <c r="D139" t="n">
-        <v>126.99</v>
+        <v>2212.5</v>
       </c>
       <c r="E139" t="n">
-        <v>7</v>
+        <v>77</v>
       </c>
       <c r="F139" t="n">
-        <v>1263</v>
+        <v>41850</v>
       </c>
       <c r="G139" t="n">
         <v>0</v>
       </c>
       <c r="H139" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="140">
-      <c r="A140" t="inlineStr"/>
-      <c r="B140" t="inlineStr">
-        <is>
-          <t>WM_SP_KT_Adjustable_Exact_Manual_HV</t>
-        </is>
-      </c>
-      <c r="C140" t="inlineStr">
-        <is>
-          <t>B0CPT3Q25C</t>
-        </is>
-      </c>
-      <c r="D140" t="n">
-        <v>2597.11</v>
-      </c>
-      <c r="E140" t="n">
-        <v>89</v>
-      </c>
-      <c r="F140" t="n">
-        <v>54479</v>
-      </c>
-      <c r="G140" t="n">
-        <v>0</v>
-      </c>
-      <c r="H140" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4645,13 +4617,13 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>892.91</v>
+        <v>757.21</v>
       </c>
       <c r="E10" t="n">
-        <v>67</v>
+        <v>58</v>
       </c>
       <c r="F10" t="n">
-        <v>31215</v>
+        <v>25409</v>
       </c>
       <c r="G10" t="n">
         <v>0</v>
@@ -4673,13 +4645,13 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>837.21</v>
+        <v>717.03</v>
       </c>
       <c r="E11" t="n">
-        <v>96</v>
+        <v>90</v>
       </c>
       <c r="F11" t="n">
-        <v>29740</v>
+        <v>28144</v>
       </c>
       <c r="G11" t="n">
         <v>2989.83</v>
@@ -4763,7 +4735,7 @@
         <v>53</v>
       </c>
       <c r="F14" t="n">
-        <v>22725</v>
+        <v>22638</v>
       </c>
       <c r="G14" t="n">
         <v>0</v>
@@ -4785,13 +4757,13 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>732.74</v>
+        <v>581.97</v>
       </c>
       <c r="E15" t="n">
-        <v>99</v>
+        <v>83</v>
       </c>
       <c r="F15" t="n">
-        <v>25322</v>
+        <v>20464</v>
       </c>
       <c r="G15" t="n">
         <v>7878.82</v>
@@ -4895,7 +4867,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I27"/>
+  <dimension ref="A1:I30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5354,19 +5326,19 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>7917</v>
+        <v>2699</v>
       </c>
       <c r="E14" t="n">
-        <v>340</v>
+        <v>114</v>
       </c>
       <c r="F14" t="n">
-        <v>733.86</v>
+        <v>248.9471468494729</v>
       </c>
       <c r="G14" t="n">
-        <v>38441.945</v>
+        <v>12684.41370457933</v>
       </c>
       <c r="H14" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
@@ -5383,23 +5355,23 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>B0CPFS24ML</t>
+          <t>B0BFVNS8HS</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>7917</v>
+        <v>2861</v>
       </c>
       <c r="E15" t="n">
-        <v>340</v>
+        <v>121</v>
       </c>
       <c r="F15" t="n">
-        <v>733.86</v>
+        <v>263.8859037867783</v>
       </c>
       <c r="G15" t="n">
-        <v>38441.945</v>
+        <v>13445.57676920169</v>
       </c>
       <c r="H15" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
@@ -5411,25 +5383,25 @@
       <c r="A16" t="inlineStr"/>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Camb-SB-Multiple Asin- product collection- Reach</t>
+          <t>Camb-SB-Multiple Asin- Product collection- exact /Reach</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>B0CPT3Q25C</t>
+          <t>B0BFWD6SNF</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>4039</v>
+        <v>2715</v>
       </c>
       <c r="E16" t="n">
-        <v>78</v>
+        <v>115</v>
       </c>
       <c r="F16" t="n">
-        <v>561.6066666666667</v>
+        <v>250.4382781298041</v>
       </c>
       <c r="G16" t="n">
-        <v>15845.76333333333</v>
+        <v>12760.39017704317</v>
       </c>
       <c r="H16" t="n">
         <v>2</v>
@@ -5444,25 +5416,25 @@
       <c r="A17" t="inlineStr"/>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Camb-SB-Multiple Asin- product collection- Reach</t>
+          <t>Camb-SB-Multiple Asin- Product collection- exact /Reach</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>B0DQ1NV8D2</t>
+          <t>B0CPFS24ML</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>4039</v>
+        <v>2683</v>
       </c>
       <c r="E17" t="n">
-        <v>78</v>
+        <v>114</v>
       </c>
       <c r="F17" t="n">
-        <v>561.6066666666667</v>
+        <v>247.4563674170135</v>
       </c>
       <c r="G17" t="n">
-        <v>15845.76333333333</v>
+        <v>12608.45515955119</v>
       </c>
       <c r="H17" t="n">
         <v>2</v>
@@ -5477,25 +5449,25 @@
       <c r="A18" t="inlineStr"/>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Camb-SB-Multiple Asin- product collection- Reach</t>
+          <t>Camb-SB-Multiple Asin- Product collection- exact /Reach</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>B0DQ4YWSMC</t>
+          <t>B0DQPK7MFH</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>4039</v>
+        <v>2300</v>
       </c>
       <c r="E18" t="n">
-        <v>78</v>
+        <v>97</v>
       </c>
       <c r="F18" t="n">
-        <v>561.6066666666667</v>
+        <v>212.1523038169314</v>
       </c>
       <c r="G18" t="n">
-        <v>15845.76333333333</v>
+        <v>10809.63418962462</v>
       </c>
       <c r="H18" t="n">
         <v>2</v>
@@ -5510,28 +5482,28 @@
       <c r="A19" t="inlineStr"/>
       <c r="B19" t="inlineStr">
         <is>
-          <t>WM- SBV- Wooden Arm- B0DP32F346- Phrase</t>
+          <t>Camb-SB-Multiple Asin- product collection- Reach</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>B0DP32F346</t>
+          <t>B0CPT3Q25C</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>9282</v>
+        <v>3412</v>
       </c>
       <c r="E19" t="n">
-        <v>116</v>
+        <v>62</v>
       </c>
       <c r="F19" t="n">
-        <v>1354.82</v>
+        <v>478.47</v>
       </c>
       <c r="G19" t="n">
-        <v>0</v>
+        <v>4801.693333333334</v>
       </c>
       <c r="H19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
@@ -5543,28 +5515,28 @@
       <c r="A20" t="inlineStr"/>
       <c r="B20" t="inlineStr">
         <is>
-          <t>WM- SBV-Wall Mounted Stand- B0DP2WC5VW- Phrase &amp; exact</t>
+          <t>Camb-SB-Multiple Asin- product collection- Reach</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>B0DP2WC5VW</t>
+          <t>B0DQ1NV8D2</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>17945</v>
+        <v>3412</v>
       </c>
       <c r="E20" t="n">
-        <v>201</v>
+        <v>62</v>
       </c>
       <c r="F20" t="n">
-        <v>2724.67</v>
+        <v>478.47</v>
       </c>
       <c r="G20" t="n">
-        <v>5422.030000000001</v>
+        <v>4801.693333333334</v>
       </c>
       <c r="H20" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
@@ -5576,28 +5548,28 @@
       <c r="A21" t="inlineStr"/>
       <c r="B21" t="inlineStr">
         <is>
-          <t>WM-SB-Monitor Arms-Defensive</t>
+          <t>Camb-SB-Multiple Asin- product collection- Reach</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>B0DB5VG39T</t>
+          <t>B0DQ4YWSMC</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>409</v>
+        <v>3412</v>
       </c>
       <c r="E21" t="n">
-        <v>7</v>
+        <v>62</v>
       </c>
       <c r="F21" t="n">
-        <v>74.98833333333332</v>
+        <v>478.47</v>
       </c>
       <c r="G21" t="n">
-        <v>0</v>
+        <v>4801.693333333334</v>
       </c>
       <c r="H21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
@@ -5609,22 +5581,22 @@
       <c r="A22" t="inlineStr"/>
       <c r="B22" t="inlineStr">
         <is>
-          <t>WM-SB-Monitor Arms-Defensive</t>
+          <t>WM- SBV- Wooden Arm- B0DP32F346- Phrase</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>B0DB5VVPSB</t>
+          <t>B0DP32F346</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>409</v>
+        <v>8112</v>
       </c>
       <c r="E22" t="n">
-        <v>7</v>
+        <v>98</v>
       </c>
       <c r="F22" t="n">
-        <v>74.98833333333332</v>
+        <v>1166.81</v>
       </c>
       <c r="G22" t="n">
         <v>0</v>
@@ -5642,28 +5614,28 @@
       <c r="A23" t="inlineStr"/>
       <c r="B23" t="inlineStr">
         <is>
-          <t>WM-SB-Monitor Arms-Defensive</t>
+          <t>WM- SBV-Wall Mounted Stand- B0DP2WC5VW- Phrase &amp; exact</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>B0DB5W4TCP</t>
+          <t>B0DP2WC5VW</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>409</v>
+        <v>14721</v>
       </c>
       <c r="E23" t="n">
-        <v>7</v>
+        <v>171</v>
       </c>
       <c r="F23" t="n">
-        <v>74.98833333333332</v>
+        <v>2406.42</v>
       </c>
       <c r="G23" t="n">
-        <v>0</v>
+        <v>5422.030000000001</v>
       </c>
       <c r="H23" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I23" t="inlineStr">
         <is>
@@ -5680,7 +5652,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>B0DB5YTQZV</t>
+          <t>B0DB5VG39T</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -5713,7 +5685,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>B0DP2Z5DQ9</t>
+          <t>B0DB5VVPSB</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -5746,7 +5718,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>B0DP32F346</t>
+          <t>B0DB5W4TCP</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -5774,30 +5746,129 @@
       <c r="A27" t="inlineStr"/>
       <c r="B27" t="inlineStr">
         <is>
+          <t>WM-SB-Monitor Arms-Defensive</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>B0DB5YTQZV</t>
+        </is>
+      </c>
+      <c r="D27" t="n">
+        <v>409</v>
+      </c>
+      <c r="E27" t="n">
+        <v>7</v>
+      </c>
+      <c r="F27" t="n">
+        <v>74.98833333333332</v>
+      </c>
+      <c r="G27" t="n">
+        <v>0</v>
+      </c>
+      <c r="H27" t="n">
+        <v>0</v>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>White Mulberry</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr"/>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>WM-SB-Monitor Arms-Defensive</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>B0DP2Z5DQ9</t>
+        </is>
+      </c>
+      <c r="D28" t="n">
+        <v>409</v>
+      </c>
+      <c r="E28" t="n">
+        <v>7</v>
+      </c>
+      <c r="F28" t="n">
+        <v>74.98833333333332</v>
+      </c>
+      <c r="G28" t="n">
+        <v>0</v>
+      </c>
+      <c r="H28" t="n">
+        <v>0</v>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>White Mulberry</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr"/>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>WM-SB-Monitor Arms-Defensive</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>B0DP32F346</t>
+        </is>
+      </c>
+      <c r="D29" t="n">
+        <v>409</v>
+      </c>
+      <c r="E29" t="n">
+        <v>7</v>
+      </c>
+      <c r="F29" t="n">
+        <v>74.98833333333332</v>
+      </c>
+      <c r="G29" t="n">
+        <v>0</v>
+      </c>
+      <c r="H29" t="n">
+        <v>0</v>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>White Mulberry</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr"/>
+      <c r="B30" t="inlineStr">
+        <is>
           <t>WM-SBV-Gas Spring MA- B0DB5VG39T- Phrase</t>
         </is>
       </c>
-      <c r="C27" t="inlineStr">
+      <c r="C30" t="inlineStr">
         <is>
           <t>B0DB5VG39T</t>
         </is>
       </c>
-      <c r="D27" t="n">
-        <v>16265</v>
-      </c>
-      <c r="E27" t="n">
-        <v>129</v>
-      </c>
-      <c r="F27" t="n">
-        <v>2247.89</v>
-      </c>
-      <c r="G27" t="n">
-        <v>0</v>
-      </c>
-      <c r="H27" t="n">
-        <v>0</v>
-      </c>
-      <c r="I27" t="inlineStr">
+      <c r="D30" t="n">
+        <v>13742</v>
+      </c>
+      <c r="E30" t="n">
+        <v>106</v>
+      </c>
+      <c r="F30" t="n">
+        <v>1843.07</v>
+      </c>
+      <c r="G30" t="n">
+        <v>0</v>
+      </c>
+      <c r="H30" t="n">
+        <v>0</v>
+      </c>
+      <c r="I30" t="inlineStr">
         <is>
           <t>White Mulberry</t>
         </is>

--- a/data/ams_weekly_data/White_Mulberry/ads_report_week22.xlsx
+++ b/data/ams_weekly_data/White_Mulberry/ads_report_week22.xlsx
@@ -1039,7 +1039,7 @@
         <v>164</v>
       </c>
       <c r="F22" t="n">
-        <v>27844</v>
+        <v>27842</v>
       </c>
       <c r="G22" t="n">
         <v>0</v>
@@ -1151,7 +1151,7 @@
         <v>54</v>
       </c>
       <c r="F26" t="n">
-        <v>5231</v>
+        <v>5230</v>
       </c>
       <c r="G26" t="n">
         <v>0</v>
@@ -1179,7 +1179,7 @@
         <v>9</v>
       </c>
       <c r="F27" t="n">
-        <v>1382</v>
+        <v>1380</v>
       </c>
       <c r="G27" t="n">
         <v>0</v>
@@ -1235,7 +1235,7 @@
         <v>25</v>
       </c>
       <c r="F29" t="n">
-        <v>5417</v>
+        <v>5416</v>
       </c>
       <c r="G29" t="n">
         <v>0</v>
@@ -1347,7 +1347,7 @@
         <v>112</v>
       </c>
       <c r="F33" t="n">
-        <v>36803</v>
+        <v>36802</v>
       </c>
       <c r="G33" t="n">
         <v>0</v>
@@ -3279,7 +3279,7 @@
         <v>88</v>
       </c>
       <c r="F102" t="n">
-        <v>31964</v>
+        <v>31963</v>
       </c>
       <c r="G102" t="n">
         <v>13004.23</v>
@@ -3307,7 +3307,7 @@
         <v>103</v>
       </c>
       <c r="F103" t="n">
-        <v>56048</v>
+        <v>56045</v>
       </c>
       <c r="G103" t="n">
         <v>9532.200000000001</v>
@@ -4315,7 +4315,7 @@
         <v>77</v>
       </c>
       <c r="F139" t="n">
-        <v>41850</v>
+        <v>41849</v>
       </c>
       <c r="G139" t="n">
         <v>0</v>
@@ -4651,7 +4651,7 @@
         <v>90</v>
       </c>
       <c r="F11" t="n">
-        <v>28144</v>
+        <v>28142</v>
       </c>
       <c r="G11" t="n">
         <v>2989.83</v>
@@ -4735,7 +4735,7 @@
         <v>53</v>
       </c>
       <c r="F14" t="n">
-        <v>22638</v>
+        <v>22637</v>
       </c>
       <c r="G14" t="n">
         <v>0</v>
@@ -4757,13 +4757,13 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>581.97</v>
+        <v>576.37</v>
       </c>
       <c r="E15" t="n">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="F15" t="n">
-        <v>20464</v>
+        <v>20463</v>
       </c>
       <c r="G15" t="n">
         <v>7878.82</v>

--- a/data/ams_weekly_data/White_Mulberry/ads_report_week22.xlsx
+++ b/data/ams_weekly_data/White_Mulberry/ads_report_week22.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H139"/>
+  <dimension ref="A1:H118"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -473,13 +473,13 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>334.8</v>
+        <v>271.34</v>
       </c>
       <c r="E2" t="n">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="F2" t="n">
-        <v>2782</v>
+        <v>2349</v>
       </c>
       <c r="G2" t="n">
         <v>0</v>
@@ -501,13 +501,13 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>122.03</v>
+        <v>109.36</v>
       </c>
       <c r="E3" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F3" t="n">
-        <v>2082</v>
+        <v>1512</v>
       </c>
       <c r="G3" t="n">
         <v>0</v>
@@ -520,7 +520,7 @@
       <c r="A4" t="inlineStr"/>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Camb-B0BFVMDJ2K /B0BFWD6SNF -L shaped-SP-KT-BM</t>
+          <t>Camb-B0BFVMDJ2K-L Shaped -Exact &amp; Phrase(1)-SP</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -529,13 +529,13 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>419.75</v>
+        <v>328.46</v>
       </c>
       <c r="E4" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="F4" t="n">
-        <v>2399</v>
+        <v>2477</v>
       </c>
       <c r="G4" t="n">
         <v>0</v>
@@ -548,22 +548,22 @@
       <c r="A5" t="inlineStr"/>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Camb-B0BFVMDJ2K-L Shaped -Exact &amp; Phrase(1)-SP</t>
+          <t>Camb-B0BFW59TRG-L-Shape-Phrase-Exact-SP</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>B0BFVMDJ2K</t>
+          <t>B0BFW59TRG</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>328.46</v>
+        <v>32.79</v>
       </c>
       <c r="E5" t="n">
-        <v>17</v>
+        <v>1</v>
       </c>
       <c r="F5" t="n">
-        <v>2477</v>
+        <v>128</v>
       </c>
       <c r="G5" t="n">
         <v>0</v>
@@ -576,22 +576,22 @@
       <c r="A6" t="inlineStr"/>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Camb-B0BFW59TRG-L-Shape-Phrase-Exact-SP</t>
+          <t>Camb-B0CPT3Q25C - Motorized-SP-PT</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>B0BFW59TRG</t>
+          <t>B0CPT3Q25C</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>32.79</v>
+        <v>545.3199999999999</v>
       </c>
       <c r="E6" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="F6" t="n">
-        <v>128</v>
+        <v>595</v>
       </c>
       <c r="G6" t="n">
         <v>0</v>
@@ -604,28 +604,28 @@
       <c r="A7" t="inlineStr"/>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Camb-B0CPT3Q25C - Motorized-SP-PT</t>
+          <t>Camb-L shaped-SP- B0BFVMDJ2K /B0BFWD6SNF -BM</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>B0CPT3Q25C</t>
+          <t>B0BFVMDJ2K</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>1453.69</v>
+        <v>234.84</v>
       </c>
       <c r="E7" t="n">
-        <v>38</v>
+        <v>10</v>
       </c>
       <c r="F7" t="n">
-        <v>3511</v>
+        <v>1771</v>
       </c>
       <c r="G7" t="n">
-        <v>12712.72</v>
+        <v>0</v>
       </c>
       <c r="H7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -637,17 +637,17 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>B0BFVMDJ2K</t>
+          <t>B0BFWD6SNF</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>234.84</v>
+        <v>80.72</v>
       </c>
       <c r="E8" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="F8" t="n">
-        <v>1771</v>
+        <v>2705</v>
       </c>
       <c r="G8" t="n">
         <v>0</v>
@@ -660,22 +660,22 @@
       <c r="A9" t="inlineStr"/>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Camb-L shaped-SP- B0BFVMDJ2K /B0BFWD6SNF -BM</t>
+          <t>Camb-Lshape- B0BFVMDJ2K/ B0BFWD6SNF - BM</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>B0BFWD6SNF</t>
+          <t>B0BFVMDJ2K</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>80.72</v>
+        <v>273.46</v>
       </c>
       <c r="E9" t="n">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="F9" t="n">
-        <v>2705</v>
+        <v>1636</v>
       </c>
       <c r="G9" t="n">
         <v>0</v>
@@ -693,17 +693,17 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>B0BFVMDJ2K</t>
+          <t>B0BFWD6SNF</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>273.46</v>
+        <v>242.05</v>
       </c>
       <c r="E10" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="F10" t="n">
-        <v>1636</v>
+        <v>3341</v>
       </c>
       <c r="G10" t="n">
         <v>0</v>
@@ -716,22 +716,22 @@
       <c r="A11" t="inlineStr"/>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Camb-Lshape- B0BFVMDJ2K/ B0BFWD6SNF - BM</t>
+          <t>Camb-Lshape- B0BFVMDJ2K/ B0BFWD6SNF - Phrase</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>B0BFWD6SNF</t>
+          <t>B0BFVMDJ2K</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>242.05</v>
+        <v>0</v>
       </c>
       <c r="E11" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="F11" t="n">
-        <v>3341</v>
+        <v>64</v>
       </c>
       <c r="G11" t="n">
         <v>0</v>
@@ -749,7 +749,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>B0BFVMDJ2K</t>
+          <t>B0BFWD6SNF</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -772,22 +772,22 @@
       <c r="A13" t="inlineStr"/>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Camb-Lshape- B0BFVMDJ2K/ B0BFWD6SNF - Phrase</t>
+          <t>Camb-Motorized  Desk- B0CPT3Q25C - PT</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>B0BFWD6SNF</t>
+          <t>B0CPT3Q25C</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>0</v>
+        <v>248.55</v>
       </c>
       <c r="E13" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="F13" t="n">
-        <v>64</v>
+        <v>552</v>
       </c>
       <c r="G13" t="n">
         <v>0</v>
@@ -800,22 +800,22 @@
       <c r="A14" t="inlineStr"/>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Camb-Motorized  Desk- B0CPT3Q25C - PT</t>
+          <t>Camb-SP-B0BFVNS8HS -L-Shape-Exact-phrase</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>B0CPT3Q25C</t>
+          <t>B0BFVNS8HS</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>568.9399999999999</v>
+        <v>54.92</v>
       </c>
       <c r="E14" t="n">
-        <v>14</v>
+        <v>2</v>
       </c>
       <c r="F14" t="n">
-        <v>1264</v>
+        <v>37</v>
       </c>
       <c r="G14" t="n">
         <v>0</v>
@@ -828,22 +828,22 @@
       <c r="A15" t="inlineStr"/>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Camb-SP-B0BFVNS8HS -L-Shape-Exact-phrase</t>
+          <t>Camb-SP-Branded</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>B0BFVNS8HS</t>
+          <t>B0BFVMDJ2K</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>54.92</v>
+        <v>0</v>
       </c>
       <c r="E15" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F15" t="n">
-        <v>37</v>
+        <v>9</v>
       </c>
       <c r="G15" t="n">
         <v>0</v>
@@ -861,7 +861,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>B0BFVMDJ2K</t>
+          <t>B0BFVNS8HS</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -871,7 +871,7 @@
         <v>0</v>
       </c>
       <c r="F16" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="G16" t="n">
         <v>0</v>
@@ -889,7 +889,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>B0BFVNS8HS</t>
+          <t>B0BFW59TRG</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -899,7 +899,7 @@
         <v>0</v>
       </c>
       <c r="F17" t="n">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="G17" t="n">
         <v>0</v>
@@ -917,7 +917,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>B0BFW59TRG</t>
+          <t>B0BFWD6SNF</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -927,7 +927,7 @@
         <v>0</v>
       </c>
       <c r="F18" t="n">
-        <v>17</v>
+        <v>29</v>
       </c>
       <c r="G18" t="n">
         <v>0</v>
@@ -945,17 +945,17 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>B0BFWD6SNF</t>
+          <t>B0CPT3Q25C</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>0</v>
+        <v>24.39</v>
       </c>
       <c r="E19" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F19" t="n">
-        <v>29</v>
+        <v>287</v>
       </c>
       <c r="G19" t="n">
         <v>0</v>
@@ -973,17 +973,17 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>B0CPT3Q25C</t>
+          <t>B0DQ4YWSMC</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>72.89</v>
+        <v>0</v>
       </c>
       <c r="E20" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="F20" t="n">
-        <v>361</v>
+        <v>147</v>
       </c>
       <c r="G20" t="n">
         <v>0</v>
@@ -996,22 +996,22 @@
       <c r="A21" t="inlineStr"/>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Camb-SP-Branded</t>
+          <t>Camb-SP-Lshape-B0BFVMDJ2K/B0BFWD6SNF- Exact/Phrase</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>B0DQ4YWSMC</t>
+          <t>B0BFVMDJ2K</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>0</v>
+        <v>1235.44</v>
       </c>
       <c r="E21" t="n">
-        <v>0</v>
+        <v>58</v>
       </c>
       <c r="F21" t="n">
-        <v>199</v>
+        <v>11945</v>
       </c>
       <c r="G21" t="n">
         <v>0</v>
@@ -1024,22 +1024,22 @@
       <c r="A22" t="inlineStr"/>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Camb-SP-Lshape-B0BFVMDJ2K/B0BFWD6SNF- Exact/Phrase</t>
+          <t>Camb-SP-Lshape-B0BFWD6SNF - Broad</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>B0BFVMDJ2K</t>
+          <t>B0BFWD6SNF</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>3717.25</v>
+        <v>103.37</v>
       </c>
       <c r="E22" t="n">
-        <v>164</v>
+        <v>11</v>
       </c>
       <c r="F22" t="n">
-        <v>27842</v>
+        <v>1381</v>
       </c>
       <c r="G22" t="n">
         <v>0</v>
@@ -1052,22 +1052,22 @@
       <c r="A23" t="inlineStr"/>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Camb-SP-Lshape-B0BFWD6SNF - Broad</t>
+          <t>Camb-SP-Lshape-CDesk-Multiple Asin- PT</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>B0BFWD6SNF</t>
+          <t>B0BFW59TRG</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>545.05</v>
+        <v>228.1</v>
       </c>
       <c r="E23" t="n">
-        <v>45</v>
+        <v>9</v>
       </c>
       <c r="F23" t="n">
-        <v>6020</v>
+        <v>1158</v>
       </c>
       <c r="G23" t="n">
         <v>0</v>
@@ -1080,50 +1080,50 @@
       <c r="A24" t="inlineStr"/>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Camb-SP-Lshape-CDesk-Multiple Asin- PT</t>
+          <t>Camb-SP-Lshape-Multi Asin- AT</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>B0BFW59TRG</t>
+          <t>B0BFVMDJ2K</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>396.88</v>
+        <v>416.65</v>
       </c>
       <c r="E24" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="F24" t="n">
-        <v>2169</v>
+        <v>1822</v>
       </c>
       <c r="G24" t="n">
-        <v>7202.54</v>
+        <v>0</v>
       </c>
       <c r="H24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr"/>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Camb-SP-Lshape-CDesk-Multiple Asin- PT</t>
+          <t>Camb-SP-Lshape-Multi Asin- AT</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>B0BFWD6SNF</t>
+          <t>B0BFVNS8HS</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>0</v>
+        <v>50.11</v>
       </c>
       <c r="E25" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F25" t="n">
-        <v>242</v>
+        <v>392</v>
       </c>
       <c r="G25" t="n">
         <v>0</v>
@@ -1141,17 +1141,17 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>B0BFVMDJ2K</t>
+          <t>B0BFW59TRG</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>1342.88</v>
+        <v>59.19</v>
       </c>
       <c r="E26" t="n">
-        <v>54</v>
+        <v>2</v>
       </c>
       <c r="F26" t="n">
-        <v>5230</v>
+        <v>327</v>
       </c>
       <c r="G26" t="n">
         <v>0</v>
@@ -1169,17 +1169,17 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>B0BFVNS8HS</t>
+          <t>B0BFWD6SNF</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>234.06</v>
+        <v>330.96</v>
       </c>
       <c r="E27" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="F27" t="n">
-        <v>1380</v>
+        <v>2689</v>
       </c>
       <c r="G27" t="n">
         <v>0</v>
@@ -1192,22 +1192,22 @@
       <c r="A28" t="inlineStr"/>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Camb-SP-Lshape-Multi Asin- AT</t>
+          <t>Camb-SP-Lshape-Multiple Asins- Exact 01</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>B0BFW59TRG</t>
+          <t>B0BFVMDJ2K</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>117.55</v>
+        <v>1201.54</v>
       </c>
       <c r="E28" t="n">
-        <v>4</v>
+        <v>45</v>
       </c>
       <c r="F28" t="n">
-        <v>799</v>
+        <v>13867</v>
       </c>
       <c r="G28" t="n">
         <v>0</v>
@@ -1220,22 +1220,22 @@
       <c r="A29" t="inlineStr"/>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Camb-SP-Lshape-Multi Asin- AT</t>
+          <t>Camb-SP-Lshape-Multiple Asins- Exact 01</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>B0BFWD6SNF</t>
+          <t>B0BFW59TRG</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>667.89</v>
+        <v>55.52</v>
       </c>
       <c r="E29" t="n">
-        <v>25</v>
+        <v>3</v>
       </c>
       <c r="F29" t="n">
-        <v>5416</v>
+        <v>1843</v>
       </c>
       <c r="G29" t="n">
         <v>0</v>
@@ -1248,7 +1248,7 @@
       <c r="A30" t="inlineStr"/>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Camb-SP-Lshape-Multiple Asins- Exact 01</t>
+          <t>Camb-SP-Lshape-Multiple Asins- Exact/Phrase</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -1257,26 +1257,26 @@
         </is>
       </c>
       <c r="D30" t="n">
-        <v>3831.96</v>
+        <v>63.86</v>
       </c>
       <c r="E30" t="n">
-        <v>141</v>
+        <v>4</v>
       </c>
       <c r="F30" t="n">
-        <v>38433</v>
+        <v>807</v>
       </c>
       <c r="G30" t="n">
-        <v>0</v>
+        <v>7075.42</v>
       </c>
       <c r="H30" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr"/>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Camb-SP-Lshape-Multiple Asins- Exact 01</t>
+          <t>Camb-SP-Lshape-Multiple Asins- Exact/Phrase</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -1285,13 +1285,13 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>171.19</v>
+        <v>879.39</v>
       </c>
       <c r="E31" t="n">
-        <v>7</v>
+        <v>42</v>
       </c>
       <c r="F31" t="n">
-        <v>2979</v>
+        <v>14022</v>
       </c>
       <c r="G31" t="n">
         <v>0</v>
@@ -1309,45 +1309,45 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>B0BFVMDJ2K</t>
+          <t>B0BFWD6SNF</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>118.49</v>
+        <v>98.16</v>
       </c>
       <c r="E32" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F32" t="n">
-        <v>1496</v>
+        <v>2170</v>
       </c>
       <c r="G32" t="n">
-        <v>7075.42</v>
+        <v>0</v>
       </c>
       <c r="H32" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr"/>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Camb-SP-Lshape-Multiple Asins- Exact/Phrase</t>
+          <t>Camb-SP-Motorized Desk- B0CPT3Q25C- Exact</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>B0BFW59TRG</t>
+          <t>B0CPT3Q25C</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>2636.23</v>
+        <v>471.98</v>
       </c>
       <c r="E33" t="n">
-        <v>112</v>
+        <v>14</v>
       </c>
       <c r="F33" t="n">
-        <v>36802</v>
+        <v>2212</v>
       </c>
       <c r="G33" t="n">
         <v>0</v>
@@ -1360,22 +1360,22 @@
       <c r="A34" t="inlineStr"/>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Camb-SP-Lshape-Multiple Asins- Exact/Phrase</t>
+          <t>Camb-SP-Motorized Desk-B0CPT3Q25C - PT01</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>B0BFWD6SNF</t>
+          <t>B0CPT3Q25C</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>170.35</v>
+        <v>330.83</v>
       </c>
       <c r="E34" t="n">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="F34" t="n">
-        <v>3541</v>
+        <v>1421</v>
       </c>
       <c r="G34" t="n">
         <v>0</v>
@@ -1388,22 +1388,22 @@
       <c r="A35" t="inlineStr"/>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Camb-SP-Lshape-Multiple Asins- PT</t>
+          <t>Camb-SP-Motorized Desk-B0CPT3Q25C- Exact</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>B0BFVMDJ2K</t>
+          <t>B0CPT3Q25C</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>0</v>
+        <v>648.99</v>
       </c>
       <c r="E35" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="F35" t="n">
-        <v>0</v>
+        <v>7264</v>
       </c>
       <c r="G35" t="n">
         <v>0</v>
@@ -1416,22 +1416,22 @@
       <c r="A36" t="inlineStr"/>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Camb-SP-Lshape-Multiple Asins- PT</t>
+          <t>Camb-SP-Zshape-B0CPFS24ML- CT ref</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>B0BFW59TRG</t>
+          <t>B0CPFS24ML</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>0</v>
+        <v>242.34</v>
       </c>
       <c r="E36" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="F36" t="n">
-        <v>2</v>
+        <v>5845</v>
       </c>
       <c r="G36" t="n">
         <v>0</v>
@@ -1444,22 +1444,22 @@
       <c r="A37" t="inlineStr"/>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Camb-SP-Lshape-Multiple Asins- PT</t>
+          <t>Camb-SP-Zshape-B0CPFS24ML- PT</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>B0BFWD6SNF</t>
+          <t>B0CPFS24ML</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>0</v>
+        <v>24.47</v>
       </c>
       <c r="E37" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F37" t="n">
-        <v>2</v>
+        <v>119</v>
       </c>
       <c r="G37" t="n">
         <v>0</v>
@@ -1472,50 +1472,50 @@
       <c r="A38" t="inlineStr"/>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Camb-SP-Motorized Desk- B0CPT3Q25C- Exact</t>
+          <t>Camb-SP-Zshape-B0CPFS24ML- Phrase</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>B0CPT3Q25C</t>
+          <t>B0CPFS24ML</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>987.98</v>
+        <v>221.09</v>
       </c>
       <c r="E38" t="n">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="F38" t="n">
-        <v>5854</v>
+        <v>1798</v>
       </c>
       <c r="G38" t="n">
-        <v>7202.54</v>
+        <v>0</v>
       </c>
       <c r="H38" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr"/>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Camb-SP-Motorized Desk- B0CPT3Q25C- Phrase/Exact</t>
+          <t>Camb-SP-Zshape-B0CPFS24ML-PT01</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>B0CPT3Q25C</t>
+          <t>B0CPFS24ML</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>516.85</v>
+        <v>69.8</v>
       </c>
       <c r="E39" t="n">
-        <v>17</v>
+        <v>5</v>
       </c>
       <c r="F39" t="n">
-        <v>4128</v>
+        <v>438</v>
       </c>
       <c r="G39" t="n">
         <v>0</v>
@@ -1528,7 +1528,7 @@
       <c r="A40" t="inlineStr"/>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Camb-SP-Motorized Desk-B0CPT3Q25C - PT01</t>
+          <t>Camb-SP-stand desk- B0DQ1NV8D2- PT</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -1537,13 +1537,13 @@
         </is>
       </c>
       <c r="D40" t="n">
-        <v>1004.43</v>
+        <v>867.75</v>
       </c>
       <c r="E40" t="n">
-        <v>47</v>
+        <v>29</v>
       </c>
       <c r="F40" t="n">
-        <v>4831</v>
+        <v>3481</v>
       </c>
       <c r="G40" t="n">
         <v>0</v>
@@ -1556,50 +1556,50 @@
       <c r="A41" t="inlineStr"/>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Camb-SP-Motorized Desk-B0CPT3Q25C- Exact</t>
+          <t>Camb-Zshape-Gaming- B0CPFS24ML-Phrase/Exact</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>B0CPT3Q25C</t>
+          <t>B0CPFS24ML</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>648.99</v>
+        <v>513.62</v>
       </c>
       <c r="E41" t="n">
-        <v>30</v>
+        <v>50</v>
       </c>
       <c r="F41" t="n">
-        <v>7264</v>
+        <v>5203</v>
       </c>
       <c r="G41" t="n">
-        <v>0</v>
+        <v>7202.54</v>
       </c>
       <c r="H41" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr"/>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Camb-SP-Stand Desk- B0DQ1PKNSP- Broad</t>
+          <t>SP CT PT_B0CPFS24ML_Gaming</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>B0DQ1PKNSP</t>
+          <t>B0CPFS24ML</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>415.17</v>
+        <v>246.57</v>
       </c>
       <c r="E42" t="n">
-        <v>23</v>
+        <v>32</v>
       </c>
       <c r="F42" t="n">
-        <v>10827</v>
+        <v>3505</v>
       </c>
       <c r="G42" t="n">
         <v>0</v>
@@ -1612,22 +1612,22 @@
       <c r="A43" t="inlineStr"/>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Camb-SP-Stand Desk-B0DQ1NV8D2- PT</t>
+          <t>SP KT_B0CPFS24ML_Manual_Gaming</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>B0DQ1NV8D2</t>
+          <t>B0CPFS24ML</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>202.5</v>
+        <v>385.67</v>
       </c>
       <c r="E43" t="n">
-        <v>8</v>
+        <v>27</v>
       </c>
       <c r="F43" t="n">
-        <v>863</v>
+        <v>2280</v>
       </c>
       <c r="G43" t="n">
         <v>0</v>
@@ -1640,22 +1640,22 @@
       <c r="A44" t="inlineStr"/>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Camb-SP-Zshape-B0CPFS24ML- CT ref</t>
+          <t>SP_KT_L shape Non Performing Ex</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>B0CPFS24ML</t>
+          <t>B0BFVMDJ2K</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>479.15</v>
+        <v>56.82</v>
       </c>
       <c r="E44" t="n">
-        <v>37</v>
+        <v>2</v>
       </c>
       <c r="F44" t="n">
-        <v>9929</v>
+        <v>877</v>
       </c>
       <c r="G44" t="n">
         <v>0</v>
@@ -1668,22 +1668,22 @@
       <c r="A45" t="inlineStr"/>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Camb-SP-Zshape-B0CPFS24ML- PT</t>
+          <t>SP_KT_L shape Non Performing Ex</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>B0CPFS24ML</t>
+          <t>B0BFW59TRG</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>330.6</v>
+        <v>0</v>
       </c>
       <c r="E45" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="F45" t="n">
-        <v>1434</v>
+        <v>395</v>
       </c>
       <c r="G45" t="n">
         <v>0</v>
@@ -1696,22 +1696,22 @@
       <c r="A46" t="inlineStr"/>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Camb-SP-Zshape-B0CPFS24ML- Phrase</t>
+          <t>SP_KT_L shape Non Performing Ex</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>B0CPFS24ML</t>
+          <t>B0BFWD6SNF</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>440.12</v>
+        <v>118.88</v>
       </c>
       <c r="E46" t="n">
-        <v>40</v>
+        <v>4</v>
       </c>
       <c r="F46" t="n">
-        <v>2686</v>
+        <v>436</v>
       </c>
       <c r="G46" t="n">
         <v>0</v>
@@ -1724,22 +1724,22 @@
       <c r="A47" t="inlineStr"/>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Camb-SP-Zshape-B0CPFS24ML-PT01</t>
+          <t>SP_PT_L shape Non Performing PT</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>B0CPFS24ML</t>
+          <t>B0BFVMDJ2K</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>280.14</v>
+        <v>204.27</v>
       </c>
       <c r="E47" t="n">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="F47" t="n">
-        <v>1377</v>
+        <v>392</v>
       </c>
       <c r="G47" t="n">
         <v>0</v>
@@ -1752,50 +1752,50 @@
       <c r="A48" t="inlineStr"/>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Camb-SP-stand desk- B0DQ1NV8D2- PT</t>
+          <t>SP_PT_L shape Non Performing PT</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>B0CPT3Q25C</t>
+          <t>B0BFWD6SNF</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>2073.13</v>
+        <v>141.79</v>
       </c>
       <c r="E48" t="n">
-        <v>69</v>
+        <v>4</v>
       </c>
       <c r="F48" t="n">
-        <v>7620</v>
+        <v>500</v>
       </c>
       <c r="G48" t="n">
-        <v>12712.72</v>
+        <v>0</v>
       </c>
       <c r="H48" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr"/>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Camb-SP-stand desk- B0DQ1NV8D2- PT</t>
+          <t>WB- SP- B0DB5VG39T - PT</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>B0DQ1NV8D2</t>
+          <t>B0DB5VG39T</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>403.12</v>
+        <v>490.05</v>
       </c>
       <c r="E49" t="n">
-        <v>13</v>
+        <v>27</v>
       </c>
       <c r="F49" t="n">
-        <v>1589</v>
+        <v>3994</v>
       </c>
       <c r="G49" t="n">
         <v>0</v>
@@ -1808,22 +1808,22 @@
       <c r="A50" t="inlineStr"/>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Camb-Stand Desk- B0DQ1NV8D2/ B0DQ1PKNSP - PT</t>
+          <t>WB- SP- B0DB5YTQZV-B0DB5VVPSB- PT</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>B0DQ1NV8D2</t>
+          <t>B0DB5YTQZV</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>308.95</v>
+        <v>0</v>
       </c>
       <c r="E50" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="F50" t="n">
-        <v>1086</v>
+        <v>0</v>
       </c>
       <c r="G50" t="n">
         <v>0</v>
@@ -1836,22 +1836,22 @@
       <c r="A51" t="inlineStr"/>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Camb-Stand Desk- B0DQ1NV8D2/ B0DQ1PKNSP - PT</t>
+          <t>WB- SP- B0DP2VVRND - PT</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>B0DQ1PKNSP</t>
+          <t>B0DP2VVRND</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>83.54000000000001</v>
+        <v>0</v>
       </c>
       <c r="E51" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F51" t="n">
-        <v>236</v>
+        <v>2</v>
       </c>
       <c r="G51" t="n">
         <v>0</v>
@@ -1864,22 +1864,22 @@
       <c r="A52" t="inlineStr"/>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Camb-Stand Desk- B0DQ1NV8D2/ B0DQ1PKNSP - Phrase</t>
+          <t>WB- SP- B0DP2WC5VW - PT</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>B0DQ1NV8D2</t>
+          <t>B0DP2WC5VW</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>658.6600000000001</v>
+        <v>112.99</v>
       </c>
       <c r="E52" t="n">
-        <v>25</v>
+        <v>8</v>
       </c>
       <c r="F52" t="n">
-        <v>20309</v>
+        <v>251</v>
       </c>
       <c r="G52" t="n">
         <v>0</v>
@@ -1892,78 +1892,78 @@
       <c r="A53" t="inlineStr"/>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Camb-Stand Desk- B0DQ1NV8D2/ B0DQ1PKNSP - Phrase</t>
+          <t>WB- SP- B0DP32F346 - PT</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>B0DQ1PKNSP</t>
+          <t>B0DP32F346</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>213.79</v>
+        <v>412.9100000000001</v>
       </c>
       <c r="E53" t="n">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="F53" t="n">
-        <v>2164</v>
+        <v>3396</v>
       </c>
       <c r="G53" t="n">
-        <v>0</v>
+        <v>2626.28</v>
       </c>
       <c r="H53" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr"/>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Camb-Zshape-Gaming- B0CPFS24ML-Phrase/Exact</t>
+          <t>WB- SP-B0DB5W4TCP-PT</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>B0CPFS24ML</t>
+          <t>B0DB5W4TCP</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>1216.53</v>
+        <v>0</v>
       </c>
       <c r="E54" t="n">
-        <v>102</v>
+        <v>0</v>
       </c>
       <c r="F54" t="n">
-        <v>12088</v>
+        <v>0</v>
       </c>
       <c r="G54" t="n">
-        <v>7202.54</v>
+        <v>0</v>
       </c>
       <c r="H54" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr"/>
       <c r="B55" t="inlineStr">
         <is>
-          <t>SP CT PT_B0CPFS24ML_Gaming</t>
+          <t>WB- SP-B0DP3194QN-PT</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>B0CPFS24ML</t>
+          <t>B0DP3194QN</t>
         </is>
       </c>
       <c r="D55" t="n">
-        <v>246.57</v>
+        <v>385.14</v>
       </c>
       <c r="E55" t="n">
-        <v>32</v>
+        <v>13</v>
       </c>
       <c r="F55" t="n">
-        <v>3505</v>
+        <v>949</v>
       </c>
       <c r="G55" t="n">
         <v>0</v>
@@ -1976,22 +1976,22 @@
       <c r="A56" t="inlineStr"/>
       <c r="B56" t="inlineStr">
         <is>
-          <t>SP KT_B0CPFS24ML_Manual_Gaming</t>
+          <t>WM- Adj Metal desk- B0DB5W4TCP-SP-KT-Phrase</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>B0CPFS24ML</t>
+          <t>B0DB5W4TCP</t>
         </is>
       </c>
       <c r="D56" t="n">
-        <v>385.67</v>
+        <v>356.94</v>
       </c>
       <c r="E56" t="n">
-        <v>27</v>
+        <v>10</v>
       </c>
       <c r="F56" t="n">
-        <v>2280</v>
+        <v>2037</v>
       </c>
       <c r="G56" t="n">
         <v>0</v>
@@ -2004,22 +2004,22 @@
       <c r="A57" t="inlineStr"/>
       <c r="B57" t="inlineStr">
         <is>
-          <t>SP_KT_L shape Non Performing Ex</t>
+          <t>WM- Heavy-Duty Mechanical- B0DP3194QN - SP-KT-Phrase/BM</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>B0BFVMDJ2K</t>
+          <t>B0DP3194QN</t>
         </is>
       </c>
       <c r="D57" t="n">
-        <v>139.94</v>
+        <v>0</v>
       </c>
       <c r="E57" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="F57" t="n">
-        <v>2149</v>
+        <v>0</v>
       </c>
       <c r="G57" t="n">
         <v>0</v>
@@ -2032,50 +2032,50 @@
       <c r="A58" t="inlineStr"/>
       <c r="B58" t="inlineStr">
         <is>
-          <t>SP_KT_L shape Non Performing Ex</t>
+          <t>WM- Height Adj stand Dual-B0DB5YTQZV-SP-KT-Phrase/BM</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>B0BFW59TRG</t>
+          <t>B0DB5YTQZV</t>
         </is>
       </c>
       <c r="D58" t="n">
-        <v>0</v>
+        <v>824.95</v>
       </c>
       <c r="E58" t="n">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="F58" t="n">
-        <v>506</v>
+        <v>4118</v>
       </c>
       <c r="G58" t="n">
-        <v>0</v>
+        <v>5082.2</v>
       </c>
       <c r="H58" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr"/>
       <c r="B59" t="inlineStr">
         <is>
-          <t>SP_KT_L shape Non Performing Ex</t>
+          <t>WM- Height Adjustable stand- Dual-B0DB5YTQZV- PT</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>B0BFWD6SNF</t>
+          <t>B0DB5YTQZV</t>
         </is>
       </c>
       <c r="D59" t="n">
-        <v>118.88</v>
+        <v>507.47</v>
       </c>
       <c r="E59" t="n">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="F59" t="n">
-        <v>1017</v>
+        <v>672</v>
       </c>
       <c r="G59" t="n">
         <v>0</v>
@@ -2088,22 +2088,22 @@
       <c r="A60" t="inlineStr"/>
       <c r="B60" t="inlineStr">
         <is>
-          <t>SP_PT_L shape Non Performing PT</t>
+          <t>WM- SP- Adj Metal desk- Multi Asins- PT</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>B0BFVMDJ2K</t>
+          <t>B0DB5W4TCP</t>
         </is>
       </c>
       <c r="D60" t="n">
-        <v>860</v>
+        <v>420.1</v>
       </c>
       <c r="E60" t="n">
-        <v>36</v>
+        <v>14</v>
       </c>
       <c r="F60" t="n">
-        <v>2254</v>
+        <v>1980</v>
       </c>
       <c r="G60" t="n">
         <v>0</v>
@@ -2116,175 +2116,175 @@
       <c r="A61" t="inlineStr"/>
       <c r="B61" t="inlineStr">
         <is>
-          <t>SP_PT_L shape Non Performing PT</t>
+          <t>WM- SP- Height Adjustable stand- Dual-B0DB5YTQZV- Broad</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>B0BFWD6SNF</t>
+          <t>B0DB5YTQZV</t>
         </is>
       </c>
       <c r="D61" t="n">
-        <v>537.1</v>
+        <v>412.41</v>
       </c>
       <c r="E61" t="n">
-        <v>17</v>
+        <v>33</v>
       </c>
       <c r="F61" t="n">
-        <v>2696</v>
+        <v>3992</v>
       </c>
       <c r="G61" t="n">
-        <v>0</v>
+        <v>1694.07</v>
       </c>
       <c r="H61" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr"/>
       <c r="B62" t="inlineStr">
         <is>
-          <t>WB- SP- B0DB5VG39T - CT ref</t>
+          <t>WM- SP- Wall Mounted Stand- B0DP2WC5VW- Broad</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>B0DB5VG39T</t>
+          <t>B0DP2WC5VW</t>
         </is>
       </c>
       <c r="D62" t="n">
-        <v>0</v>
+        <v>383.96</v>
       </c>
       <c r="E62" t="n">
-        <v>0</v>
+        <v>61</v>
       </c>
       <c r="F62" t="n">
-        <v>0</v>
+        <v>2325</v>
       </c>
       <c r="G62" t="n">
-        <v>0</v>
+        <v>5477.12</v>
       </c>
       <c r="H62" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr"/>
       <c r="B63" t="inlineStr">
         <is>
-          <t>WB- SP- B0DB5VG39T - PT</t>
+          <t>WM- SP- Wooden Arm- B0DP32F346- PT</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>B0DB5VG39T</t>
+          <t>B0DP32F346</t>
         </is>
       </c>
       <c r="D63" t="n">
-        <v>1430.06</v>
+        <v>784.9400000000001</v>
       </c>
       <c r="E63" t="n">
-        <v>79</v>
+        <v>26</v>
       </c>
       <c r="F63" t="n">
-        <v>10235</v>
+        <v>3056</v>
       </c>
       <c r="G63" t="n">
-        <v>2329.66</v>
+        <v>0</v>
       </c>
       <c r="H63" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr"/>
       <c r="B64" t="inlineStr">
         <is>
-          <t>WB- SP- B0DB5YTQZV-B0DB5VVPSB- PT</t>
+          <t>WM- SP-Wall Mounted Stand- B0DP2WC5VW- Exact &amp; Phrase</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>B0DB5VVPSB</t>
+          <t>B0DP2WC5VW</t>
         </is>
       </c>
       <c r="D64" t="n">
-        <v>253.26</v>
+        <v>1148.29</v>
       </c>
       <c r="E64" t="n">
-        <v>12</v>
+        <v>69</v>
       </c>
       <c r="F64" t="n">
-        <v>1604</v>
+        <v>2866</v>
       </c>
       <c r="G64" t="n">
-        <v>0</v>
+        <v>8487.280000000001</v>
       </c>
       <c r="H64" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr"/>
       <c r="B65" t="inlineStr">
         <is>
-          <t>WB- SP- B0DB5YTQZV-B0DB5VVPSB- PT</t>
+          <t>WM- Wall Mounted Stand- B0DP2WC5VW- PT</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>B0DB5YTQZV</t>
+          <t>B0DP2WC5VW</t>
         </is>
       </c>
       <c r="D65" t="n">
-        <v>890.66</v>
+        <v>685.29</v>
       </c>
       <c r="E65" t="n">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="F65" t="n">
-        <v>2681</v>
+        <v>1287</v>
       </c>
       <c r="G65" t="n">
-        <v>1694.07</v>
+        <v>13931.36</v>
       </c>
       <c r="H65" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr"/>
       <c r="B66" t="inlineStr">
         <is>
-          <t>WB- SP- B0DP2VVRND - PT</t>
+          <t>WM- Wall Mounted Stand- B0DP2WC5VW- Phrase &amp; exact</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>B0DP2VVRND</t>
+          <t>B0DP2WC5VW</t>
         </is>
       </c>
       <c r="D66" t="n">
-        <v>146.98</v>
+        <v>1744.44</v>
       </c>
       <c r="E66" t="n">
-        <v>6</v>
+        <v>77</v>
       </c>
       <c r="F66" t="n">
-        <v>371</v>
+        <v>9528</v>
       </c>
       <c r="G66" t="n">
-        <v>1795.76</v>
+        <v>11352.53</v>
       </c>
       <c r="H66" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr"/>
       <c r="B67" t="inlineStr">
         <is>
-          <t>WB- SP- B0DP2WC5VW - PT</t>
+          <t>WM- Wall Mounted Stand- B0DP2WC5VW- SP-KT-Phrase/BM</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -2293,13 +2293,13 @@
         </is>
       </c>
       <c r="D67" t="n">
-        <v>418.47</v>
+        <v>0</v>
       </c>
       <c r="E67" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="F67" t="n">
-        <v>549</v>
+        <v>0</v>
       </c>
       <c r="G67" t="n">
         <v>0</v>
@@ -2312,50 +2312,50 @@
       <c r="A68" t="inlineStr"/>
       <c r="B68" t="inlineStr">
         <is>
-          <t>WB- SP- B0DP32F346 - PT</t>
+          <t>WM-Gas Spring MA- B0DB5VG39T-SP-KT-Phrase/BM</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>B0DP32F346</t>
+          <t>B0DB5VG39T</t>
         </is>
       </c>
       <c r="D68" t="n">
-        <v>1213.77</v>
+        <v>572.27</v>
       </c>
       <c r="E68" t="n">
-        <v>52</v>
+        <v>22</v>
       </c>
       <c r="F68" t="n">
-        <v>9586</v>
+        <v>2680</v>
       </c>
       <c r="G68" t="n">
-        <v>5252.55</v>
+        <v>0</v>
       </c>
       <c r="H68" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr"/>
       <c r="B69" t="inlineStr">
         <is>
-          <t>WB- SP-B0DB5W4TCP-PT</t>
+          <t>WM-Gas Spring MA- Dual - B0DB5VVPSB-SP-KT-Phrase/BM</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>B0DB5W4TCP</t>
+          <t>B0DB5VVPSB</t>
         </is>
       </c>
       <c r="D69" t="n">
-        <v>142.09</v>
+        <v>0</v>
       </c>
       <c r="E69" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="F69" t="n">
-        <v>766</v>
+        <v>0</v>
       </c>
       <c r="G69" t="n">
         <v>0</v>
@@ -2368,35 +2368,35 @@
       <c r="A70" t="inlineStr"/>
       <c r="B70" t="inlineStr">
         <is>
-          <t>WB- SP-B0DP3194QN-PT</t>
+          <t>WM-SP- Monitor Arms- Multi Asins - AT</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>B0DP3194QN</t>
+          <t>B0DB5VVPSB</t>
         </is>
       </c>
       <c r="D70" t="n">
-        <v>1031.02</v>
+        <v>298.38</v>
       </c>
       <c r="E70" t="n">
-        <v>37</v>
+        <v>15</v>
       </c>
       <c r="F70" t="n">
-        <v>3273</v>
+        <v>914</v>
       </c>
       <c r="G70" t="n">
-        <v>2965.26</v>
+        <v>0</v>
       </c>
       <c r="H70" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr"/>
       <c r="B71" t="inlineStr">
         <is>
-          <t>WM- Adj Metal desk- B0DB5W4TCP-SP-KT-Phrase</t>
+          <t>WM-SP- Monitor Arms- Multi Asins - AT</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -2405,13 +2405,13 @@
         </is>
       </c>
       <c r="D71" t="n">
-        <v>865.3299999999999</v>
+        <v>212.01</v>
       </c>
       <c r="E71" t="n">
-        <v>29</v>
+        <v>9</v>
       </c>
       <c r="F71" t="n">
-        <v>6086</v>
+        <v>985</v>
       </c>
       <c r="G71" t="n">
         <v>0</v>
@@ -2424,22 +2424,22 @@
       <c r="A72" t="inlineStr"/>
       <c r="B72" t="inlineStr">
         <is>
-          <t>WM- Heavy-Duty Mechanical- B0DP3194QN - SP-KT-Phrase/BM</t>
+          <t>WM-SP- Monitor Arms- Multi Asins - AT</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>B0DP3194QN</t>
+          <t>B0DP2WC5VW</t>
         </is>
       </c>
       <c r="D72" t="n">
-        <v>429.67</v>
+        <v>197.5</v>
       </c>
       <c r="E72" t="n">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="F72" t="n">
-        <v>14074</v>
+        <v>1555</v>
       </c>
       <c r="G72" t="n">
         <v>0</v>
@@ -2452,22 +2452,22 @@
       <c r="A73" t="inlineStr"/>
       <c r="B73" t="inlineStr">
         <is>
-          <t>WM- Height Adj stand - B0DP2VVRND-SP-KT-Phrase</t>
+          <t>WM-SP- Monitor Arms- Multi Asins - AT</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>B0DP2VVRND</t>
+          <t>B0DP2Z5DQ9</t>
         </is>
       </c>
       <c r="D73" t="n">
-        <v>534.77</v>
+        <v>75.86</v>
       </c>
       <c r="E73" t="n">
-        <v>21</v>
+        <v>4</v>
       </c>
       <c r="F73" t="n">
-        <v>4210</v>
+        <v>595</v>
       </c>
       <c r="G73" t="n">
         <v>0</v>
@@ -2480,106 +2480,106 @@
       <c r="A74" t="inlineStr"/>
       <c r="B74" t="inlineStr">
         <is>
-          <t>WM- Height Adj stand Dual-B0DB5YTQZV-SP-KT-Phrase/BM</t>
+          <t>WM-SP- Monitor Arms- Multi Asins - AT</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>B0DB5YTQZV</t>
+          <t>B0DP32F346</t>
         </is>
       </c>
       <c r="D74" t="n">
-        <v>3041.37</v>
+        <v>48.66</v>
       </c>
       <c r="E74" t="n">
-        <v>157</v>
+        <v>3</v>
       </c>
       <c r="F74" t="n">
-        <v>18822</v>
+        <v>1063</v>
       </c>
       <c r="G74" t="n">
-        <v>5082.2</v>
+        <v>0</v>
       </c>
       <c r="H74" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr"/>
       <c r="B75" t="inlineStr">
         <is>
-          <t>WM- Height Adjustable stand- Dual-B0DB5YTQZV- PT</t>
+          <t>WM-SP- Monitor Arms- Multi Asins - CT</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>B0DB5YTQZV</t>
+          <t>B0DB5W4TCP</t>
         </is>
       </c>
       <c r="D75" t="n">
-        <v>1205.44</v>
+        <v>180.43</v>
       </c>
       <c r="E75" t="n">
-        <v>34</v>
+        <v>9</v>
       </c>
       <c r="F75" t="n">
-        <v>1572</v>
+        <v>944</v>
       </c>
       <c r="G75" t="n">
-        <v>5922.04</v>
+        <v>1355.08</v>
       </c>
       <c r="H75" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr"/>
       <c r="B76" t="inlineStr">
         <is>
-          <t>WM- SP- Adj Metal desk- Multi Asins- PT</t>
+          <t>WM-SP- Monitor Arms- Multi Asins - CT</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>B0DB5W4TCP</t>
+          <t>B0DB5YTQZV</t>
         </is>
       </c>
       <c r="D76" t="n">
-        <v>1308.46</v>
+        <v>140.97</v>
       </c>
       <c r="E76" t="n">
-        <v>51</v>
+        <v>7</v>
       </c>
       <c r="F76" t="n">
-        <v>6091</v>
+        <v>1478</v>
       </c>
       <c r="G76" t="n">
-        <v>1355.08</v>
+        <v>0</v>
       </c>
       <c r="H76" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr"/>
       <c r="B77" t="inlineStr">
         <is>
-          <t>WM- SP- Adj Metal desk- Multi Asins- PT</t>
+          <t>WM-SP- Monitor Arms- Multi Asins - CT</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>B0DB5YTQZV</t>
+          <t>B0DP2WC5VW</t>
         </is>
       </c>
       <c r="D77" t="n">
-        <v>421.22</v>
+        <v>131.61</v>
       </c>
       <c r="E77" t="n">
-        <v>17</v>
+        <v>6</v>
       </c>
       <c r="F77" t="n">
-        <v>1681</v>
+        <v>1781</v>
       </c>
       <c r="G77" t="n">
         <v>0</v>
@@ -2592,91 +2592,91 @@
       <c r="A78" t="inlineStr"/>
       <c r="B78" t="inlineStr">
         <is>
-          <t>WM- SP- Height Adjustable stand- Dual-B0DB5YTQZV- Broad</t>
+          <t>WM-SP- Monitor Arms- Multi Asins - CT</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>B0DB5YTQZV</t>
+          <t>B0DP2Z5DQ9</t>
         </is>
       </c>
       <c r="D78" t="n">
-        <v>899.79</v>
+        <v>163.39</v>
       </c>
       <c r="E78" t="n">
-        <v>77</v>
+        <v>8</v>
       </c>
       <c r="F78" t="n">
-        <v>9126</v>
+        <v>1352</v>
       </c>
       <c r="G78" t="n">
-        <v>3388.14</v>
+        <v>0</v>
       </c>
       <c r="H78" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr"/>
       <c r="B79" t="inlineStr">
         <is>
-          <t>WM- SP- Wall Mounted Stand- B0DP2WC5VW- Broad</t>
+          <t>WM-SP- Monitor Arms- Multi Asins - CT</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>B0DP2WC5VW</t>
+          <t>B0DP32F346</t>
         </is>
       </c>
       <c r="D79" t="n">
-        <v>588.22</v>
+        <v>49.57</v>
       </c>
       <c r="E79" t="n">
-        <v>101</v>
+        <v>3</v>
       </c>
       <c r="F79" t="n">
-        <v>4063</v>
+        <v>327</v>
       </c>
       <c r="G79" t="n">
-        <v>10729.66</v>
+        <v>0</v>
       </c>
       <c r="H79" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr"/>
       <c r="B80" t="inlineStr">
         <is>
-          <t>WM- SP- Wooden Arm- B0DP32F346- PT</t>
+          <t>WM-SP- Monitor Arms- Multi Asins - exact</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>B0DP32F346</t>
+          <t>B0DB5W4TCP</t>
         </is>
       </c>
       <c r="D80" t="n">
-        <v>2000.85</v>
+        <v>185.09</v>
       </c>
       <c r="E80" t="n">
-        <v>69</v>
+        <v>12</v>
       </c>
       <c r="F80" t="n">
-        <v>7481</v>
+        <v>6746</v>
       </c>
       <c r="G80" t="n">
-        <v>7582.200000000001</v>
+        <v>0</v>
       </c>
       <c r="H80" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr"/>
       <c r="B81" t="inlineStr">
         <is>
-          <t>WM- SP-Wall Mounted Stand- B0DP2WC5VW- Exact &amp; Phrase</t>
+          <t>WM-SP- Monitor Arms- Multi Asins - exact</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
@@ -2685,97 +2685,97 @@
         </is>
       </c>
       <c r="D81" t="n">
-        <v>3093.68</v>
+        <v>587.3</v>
       </c>
       <c r="E81" t="n">
-        <v>178</v>
+        <v>36</v>
       </c>
       <c r="F81" t="n">
-        <v>9029</v>
+        <v>17577</v>
       </c>
       <c r="G81" t="n">
-        <v>19650.83</v>
+        <v>2626.27</v>
       </c>
       <c r="H81" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr"/>
       <c r="B82" t="inlineStr">
         <is>
-          <t>WM- Wall Mounted Stand- B0DP2WC5VW- PT</t>
+          <t>WM-SP- Premium Monitor Arms- Multi Asins -Phrase</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>B0DP2WC5VW</t>
+          <t>B0DP3194QN</t>
         </is>
       </c>
       <c r="D82" t="n">
-        <v>2054.29</v>
+        <v>0</v>
       </c>
       <c r="E82" t="n">
-        <v>113</v>
+        <v>0</v>
       </c>
       <c r="F82" t="n">
-        <v>4850</v>
+        <v>0</v>
       </c>
       <c r="G82" t="n">
-        <v>13931.36</v>
+        <v>0</v>
       </c>
       <c r="H82" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr"/>
       <c r="B83" t="inlineStr">
         <is>
-          <t>WM- Wall Mounted Stand- B0DP2WC5VW- Phrase &amp; exact</t>
+          <t>WM-SP- Premium Monitor Arms- Multi Asins -Phrase</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>B0DP2WC5VW</t>
+          <t>B0DP32F346</t>
         </is>
       </c>
       <c r="D83" t="n">
-        <v>5243.16</v>
+        <v>716.2</v>
       </c>
       <c r="E83" t="n">
-        <v>235</v>
+        <v>34</v>
       </c>
       <c r="F83" t="n">
-        <v>29595</v>
+        <v>15278</v>
       </c>
       <c r="G83" t="n">
-        <v>13978.8</v>
+        <v>5422.030000000001</v>
       </c>
       <c r="H83" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr"/>
       <c r="B84" t="inlineStr">
         <is>
-          <t>WM- Wall Mounted Stand- B0DP2WC5VW- SP-KT-Phrase/BM</t>
+          <t>WM-SP-Gas Spring -Multi Asins- Phrase &amp; Exact</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>B0DP2WC5VW</t>
+          <t>B0DB5VG39T</t>
         </is>
       </c>
       <c r="D84" t="n">
-        <v>905.7</v>
+        <v>787.4400000000001</v>
       </c>
       <c r="E84" t="n">
-        <v>54</v>
+        <v>37</v>
       </c>
       <c r="F84" t="n">
-        <v>11941</v>
+        <v>14645</v>
       </c>
       <c r="G84" t="n">
         <v>0</v>
@@ -2788,35 +2788,35 @@
       <c r="A85" t="inlineStr"/>
       <c r="B85" t="inlineStr">
         <is>
-          <t>WM- Wooden Arm- B0DP32F346-SP-KT-Phrase</t>
+          <t>WM-SP-Gas Spring -Multi Asins- Phrase &amp; Exact</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>B0DP32F346</t>
+          <t>B0DB5VVPSB</t>
         </is>
       </c>
       <c r="D85" t="n">
-        <v>474.89</v>
+        <v>181.76</v>
       </c>
       <c r="E85" t="n">
-        <v>18</v>
+        <v>7</v>
       </c>
       <c r="F85" t="n">
-        <v>10658</v>
+        <v>1253</v>
       </c>
       <c r="G85" t="n">
-        <v>2626.27</v>
+        <v>0</v>
       </c>
       <c r="H85" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr"/>
       <c r="B86" t="inlineStr">
         <is>
-          <t>WM-Gas Spring MA- B0DB5VG39T-SP-KT-Phrase/BM</t>
+          <t>WM-SP-Gas Spring MA- B0DB5VG39T- Broad</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
@@ -2825,41 +2825,41 @@
         </is>
       </c>
       <c r="D86" t="n">
-        <v>1953.89</v>
+        <v>582.28</v>
       </c>
       <c r="E86" t="n">
-        <v>71</v>
+        <v>42</v>
       </c>
       <c r="F86" t="n">
-        <v>6612</v>
+        <v>6109</v>
       </c>
       <c r="G86" t="n">
-        <v>6988.98</v>
+        <v>4659.32</v>
       </c>
       <c r="H86" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr"/>
       <c r="B87" t="inlineStr">
         <is>
-          <t>WM-Gas Spring MA- Dual - B0DB5VVPSB-SP-KT-Phrase/BM</t>
+          <t>WM-SP-Gas Spring MA- B0DB5VG39T- Exact &amp; Phrase</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>B0DB5VVPSB</t>
+          <t>B0DB5VG39T</t>
         </is>
       </c>
       <c r="D87" t="n">
-        <v>646.0699999999999</v>
+        <v>0</v>
       </c>
       <c r="E87" t="n">
-        <v>41</v>
+        <v>0</v>
       </c>
       <c r="F87" t="n">
-        <v>9415</v>
+        <v>0</v>
       </c>
       <c r="G87" t="n">
         <v>0</v>
@@ -2872,7 +2872,7 @@
       <c r="A88" t="inlineStr"/>
       <c r="B88" t="inlineStr">
         <is>
-          <t>WM-SP- Monitor Arms- Multi Asins - AT</t>
+          <t>WM-SP-Gas Spring MA- B0DB5VG39T/B0DB5VVPSB- PT</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
@@ -2881,13 +2881,13 @@
         </is>
       </c>
       <c r="D88" t="n">
-        <v>114.05</v>
+        <v>620.51</v>
       </c>
       <c r="E88" t="n">
-        <v>6</v>
+        <v>19</v>
       </c>
       <c r="F88" t="n">
-        <v>4112</v>
+        <v>1775</v>
       </c>
       <c r="G88" t="n">
         <v>0</v>
@@ -2900,7 +2900,7 @@
       <c r="A89" t="inlineStr"/>
       <c r="B89" t="inlineStr">
         <is>
-          <t>WM-SP- Monitor Arms- Multi Asins - AT</t>
+          <t>WM-SP-Gas Spring MA- B0DB5VG39T/B0DB5VVPSB- PT</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
@@ -2909,13 +2909,13 @@
         </is>
       </c>
       <c r="D89" t="n">
-        <v>797.27</v>
+        <v>192.88</v>
       </c>
       <c r="E89" t="n">
-        <v>39</v>
+        <v>7</v>
       </c>
       <c r="F89" t="n">
-        <v>3174</v>
+        <v>418</v>
       </c>
       <c r="G89" t="n">
         <v>0</v>
@@ -2928,22 +2928,22 @@
       <c r="A90" t="inlineStr"/>
       <c r="B90" t="inlineStr">
         <is>
-          <t>WM-SP- Monitor Arms- Multi Asins - AT</t>
+          <t>WM-SP-Monitor Arms- Branded</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>B0DB5W4TCP</t>
+          <t>B0DB5VG39T</t>
         </is>
       </c>
       <c r="D90" t="n">
-        <v>432.73</v>
+        <v>10.64</v>
       </c>
       <c r="E90" t="n">
-        <v>21</v>
+        <v>1</v>
       </c>
       <c r="F90" t="n">
-        <v>3395</v>
+        <v>182</v>
       </c>
       <c r="G90" t="n">
         <v>0</v>
@@ -2956,22 +2956,22 @@
       <c r="A91" t="inlineStr"/>
       <c r="B91" t="inlineStr">
         <is>
-          <t>WM-SP- Monitor Arms- Multi Asins - AT</t>
+          <t>WM-SP-Monitor Arms- Branded</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>B0DP2WC5VW</t>
+          <t>B0DB5VVPSB</t>
         </is>
       </c>
       <c r="D91" t="n">
-        <v>579.5599999999999</v>
+        <v>0</v>
       </c>
       <c r="E91" t="n">
-        <v>37</v>
+        <v>0</v>
       </c>
       <c r="F91" t="n">
-        <v>10889</v>
+        <v>162</v>
       </c>
       <c r="G91" t="n">
         <v>0</v>
@@ -2984,22 +2984,22 @@
       <c r="A92" t="inlineStr"/>
       <c r="B92" t="inlineStr">
         <is>
-          <t>WM-SP- Monitor Arms- Multi Asins - AT</t>
+          <t>WM-SP-Monitor Arms- Branded</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>B0DP2Z5DQ9</t>
+          <t>B0DB5W4TCP</t>
         </is>
       </c>
       <c r="D92" t="n">
-        <v>136.04</v>
+        <v>0</v>
       </c>
       <c r="E92" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="F92" t="n">
-        <v>1845</v>
+        <v>367</v>
       </c>
       <c r="G92" t="n">
         <v>0</v>
@@ -3012,22 +3012,22 @@
       <c r="A93" t="inlineStr"/>
       <c r="B93" t="inlineStr">
         <is>
-          <t>WM-SP- Monitor Arms- Multi Asins - AT</t>
+          <t>WM-SP-Monitor Arms- Branded</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>B0DP32F346</t>
+          <t>B0DB5YTQZV</t>
         </is>
       </c>
       <c r="D93" t="n">
-        <v>107.6</v>
+        <v>0</v>
       </c>
       <c r="E93" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="F93" t="n">
-        <v>4408</v>
+        <v>144</v>
       </c>
       <c r="G93" t="n">
         <v>0</v>
@@ -3040,50 +3040,50 @@
       <c r="A94" t="inlineStr"/>
       <c r="B94" t="inlineStr">
         <is>
-          <t>WM-SP- Monitor Arms- Multi Asins - CT</t>
+          <t>WM-SP-Monitor Arms- Branded</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>B0DB5W4TCP</t>
+          <t>B0DP2Z5DQ9</t>
         </is>
       </c>
       <c r="D94" t="n">
-        <v>267.85</v>
+        <v>0</v>
       </c>
       <c r="E94" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="F94" t="n">
-        <v>1779</v>
+        <v>532</v>
       </c>
       <c r="G94" t="n">
-        <v>1355.08</v>
+        <v>0</v>
       </c>
       <c r="H94" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr"/>
       <c r="B95" t="inlineStr">
         <is>
-          <t>WM-SP- Monitor Arms- Multi Asins - CT</t>
+          <t>WM-SP-Monitor Arms- Branded</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>B0DB5YTQZV</t>
+          <t>B0DP32F346</t>
         </is>
       </c>
       <c r="D95" t="n">
-        <v>275.69</v>
+        <v>10</v>
       </c>
       <c r="E95" t="n">
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="F95" t="n">
-        <v>3108</v>
+        <v>848</v>
       </c>
       <c r="G95" t="n">
         <v>0</v>
@@ -3096,22 +3096,22 @@
       <c r="A96" t="inlineStr"/>
       <c r="B96" t="inlineStr">
         <is>
-          <t>WM-SP- Monitor Arms- Multi Asins - CT</t>
+          <t>WM-SP-Monitor Arms- Defensive</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>B0DP2WC5VW</t>
+          <t>B0DB5VG39T</t>
         </is>
       </c>
       <c r="D96" t="n">
-        <v>492.43</v>
+        <v>39.66</v>
       </c>
       <c r="E96" t="n">
-        <v>27</v>
+        <v>3</v>
       </c>
       <c r="F96" t="n">
-        <v>5267</v>
+        <v>342</v>
       </c>
       <c r="G96" t="n">
         <v>0</v>
@@ -3124,50 +3124,50 @@
       <c r="A97" t="inlineStr"/>
       <c r="B97" t="inlineStr">
         <is>
-          <t>WM-SP- Monitor Arms- Multi Asins - CT</t>
+          <t>WM-SP-Monitor Arms- Defensive</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>B0DP2Z5DQ9</t>
+          <t>B0DB5VVPSB</t>
         </is>
       </c>
       <c r="D97" t="n">
-        <v>273.23</v>
+        <v>105</v>
       </c>
       <c r="E97" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="F97" t="n">
-        <v>1921</v>
+        <v>796</v>
       </c>
       <c r="G97" t="n">
-        <v>0</v>
+        <v>3812.72</v>
       </c>
       <c r="H97" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr"/>
       <c r="B98" t="inlineStr">
         <is>
-          <t>WM-SP- Monitor Arms- Multi Asins - CT</t>
+          <t>WM-SP-Monitor Arms- Defensive</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>B0DP32F346</t>
+          <t>B0DB5W4TCP</t>
         </is>
       </c>
       <c r="D98" t="n">
-        <v>197.49</v>
+        <v>11.55</v>
       </c>
       <c r="E98" t="n">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="F98" t="n">
-        <v>1060</v>
+        <v>337</v>
       </c>
       <c r="G98" t="n">
         <v>0</v>
@@ -3180,78 +3180,78 @@
       <c r="A99" t="inlineStr"/>
       <c r="B99" t="inlineStr">
         <is>
-          <t>WM-SP- Monitor Arms- Multi Asins - exact</t>
+          <t>WM-SP-Monitor Arms- Defensive</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>B0DB5W4TCP</t>
+          <t>B0DB5YTQZV</t>
         </is>
       </c>
       <c r="D99" t="n">
-        <v>785.24</v>
+        <v>111.53</v>
       </c>
       <c r="E99" t="n">
-        <v>44</v>
+        <v>10</v>
       </c>
       <c r="F99" t="n">
-        <v>31702</v>
+        <v>1770</v>
       </c>
       <c r="G99" t="n">
-        <v>1355.08</v>
+        <v>0</v>
       </c>
       <c r="H99" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr"/>
       <c r="B100" t="inlineStr">
         <is>
-          <t>WM-SP- Monitor Arms- Multi Asins - exact</t>
+          <t>WM-SP-Monitor Arms- Defensive</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>B0DP2WC5VW</t>
+          <t>B0DP2Z5DQ9</t>
         </is>
       </c>
       <c r="D100" t="n">
-        <v>1580.89</v>
+        <v>125.95</v>
       </c>
       <c r="E100" t="n">
-        <v>92</v>
+        <v>12</v>
       </c>
       <c r="F100" t="n">
-        <v>41824</v>
+        <v>1035</v>
       </c>
       <c r="G100" t="n">
-        <v>5252.54</v>
+        <v>2514.41</v>
       </c>
       <c r="H100" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr"/>
       <c r="B101" t="inlineStr">
         <is>
-          <t>WM-SP- Premium Monitor Arms- Multi Asins -Phrase</t>
+          <t>WM-SP-Monitor Arms- Defensive</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>B0DP3194QN</t>
+          <t>B0DP32F346</t>
         </is>
       </c>
       <c r="D101" t="n">
-        <v>24.01</v>
+        <v>38.99</v>
       </c>
       <c r="E101" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F101" t="n">
-        <v>317</v>
+        <v>243</v>
       </c>
       <c r="G101" t="n">
         <v>0</v>
@@ -3264,190 +3264,190 @@
       <c r="A102" t="inlineStr"/>
       <c r="B102" t="inlineStr">
         <is>
-          <t>WM-SP- Premium Monitor Arms- Multi Asins -Phrase</t>
+          <t>WM-SP-Monitor Stand-B0DP2Z5DQ9 - PT</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>B0DP32F346</t>
+          <t>B0DP2Z5DQ9</t>
         </is>
       </c>
       <c r="D102" t="n">
-        <v>1905.61</v>
+        <v>350.04</v>
       </c>
       <c r="E102" t="n">
-        <v>88</v>
+        <v>28</v>
       </c>
       <c r="F102" t="n">
-        <v>31963</v>
+        <v>1945</v>
       </c>
       <c r="G102" t="n">
-        <v>13004.23</v>
+        <v>2514.41</v>
       </c>
       <c r="H102" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr"/>
       <c r="B103" t="inlineStr">
         <is>
-          <t>WM-SP-Gas Spring -Multi Asins- Phrase &amp; Exact</t>
+          <t>WM-SP-Monitor Stand-B0DP2Z5DQ9 - Phrase</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>B0DB5VG39T</t>
+          <t>B0DP2Z5DQ9</t>
         </is>
       </c>
       <c r="D103" t="n">
-        <v>2260.54</v>
+        <v>587.6900000000001</v>
       </c>
       <c r="E103" t="n">
-        <v>103</v>
+        <v>41</v>
       </c>
       <c r="F103" t="n">
-        <v>56045</v>
+        <v>3530</v>
       </c>
       <c r="G103" t="n">
-        <v>9532.200000000001</v>
+        <v>2514.4</v>
       </c>
       <c r="H103" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr"/>
       <c r="B104" t="inlineStr">
         <is>
-          <t>WM-SP-Gas Spring -Multi Asins- Phrase &amp; Exact</t>
+          <t>WM-SP-Monitor Stand-B0DP2Z5DQ9 -Phrase</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>B0DB5VVPSB</t>
+          <t>B0DP2Z5DQ9</t>
         </is>
       </c>
       <c r="D104" t="n">
-        <v>330.96</v>
+        <v>524.45</v>
       </c>
       <c r="E104" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="F104" t="n">
-        <v>2839</v>
+        <v>5434</v>
       </c>
       <c r="G104" t="n">
-        <v>0</v>
+        <v>15508.48</v>
       </c>
       <c r="H104" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr"/>
       <c r="B105" t="inlineStr">
         <is>
-          <t>WM-SP-Gas Spring MA- B0DB5VG39T- Broad</t>
+          <t>WM-SP-POS stand- Multi - PT</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>B0DB5VG39T</t>
+          <t>B0FN4FPJ83</t>
         </is>
       </c>
       <c r="D105" t="n">
-        <v>2027.23</v>
+        <v>0</v>
       </c>
       <c r="E105" t="n">
-        <v>146</v>
+        <v>0</v>
       </c>
       <c r="F105" t="n">
-        <v>21040</v>
+        <v>3</v>
       </c>
       <c r="G105" t="n">
-        <v>13299.99</v>
+        <v>0</v>
       </c>
       <c r="H105" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr"/>
       <c r="B106" t="inlineStr">
         <is>
-          <t>WM-SP-Gas Spring MA- B0DB5VG39T- Exact &amp; Phrase</t>
+          <t>WM-SP-TV Brackets- Multi Asins- CT</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>B0DB5VG39T</t>
+          <t>B0FN4D3C89</t>
         </is>
       </c>
       <c r="D106" t="n">
-        <v>541.79</v>
+        <v>245.74</v>
       </c>
       <c r="E106" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="F106" t="n">
-        <v>1786</v>
+        <v>1122</v>
       </c>
       <c r="G106" t="n">
-        <v>4955.93</v>
+        <v>0</v>
       </c>
       <c r="H106" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr"/>
       <c r="B107" t="inlineStr">
         <is>
-          <t>WM-SP-Gas Spring MA- B0DB5VG39T/B0DB5VVPSB- PT</t>
+          <t>WM-SP-TV Brackets- Multi Asins- CT</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>B0DB5VG39T</t>
+          <t>B0FN4DSQ6P</t>
         </is>
       </c>
       <c r="D107" t="n">
-        <v>1596.87</v>
+        <v>42.18</v>
       </c>
       <c r="E107" t="n">
-        <v>50</v>
+        <v>2</v>
       </c>
       <c r="F107" t="n">
-        <v>4529</v>
+        <v>540</v>
       </c>
       <c r="G107" t="n">
-        <v>2626.27</v>
+        <v>0</v>
       </c>
       <c r="H107" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr"/>
       <c r="B108" t="inlineStr">
         <is>
-          <t>WM-SP-Gas Spring MA- B0DB5VG39T/B0DB5VVPSB- PT</t>
+          <t>WM-SP-TV Brackets- Multi Asins- CT</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>B0DB5VVPSB</t>
+          <t>B0FN4HDM6Z</t>
         </is>
       </c>
       <c r="D108" t="n">
-        <v>598.7</v>
+        <v>0</v>
       </c>
       <c r="E108" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="F108" t="n">
-        <v>1778</v>
+        <v>369</v>
       </c>
       <c r="G108" t="n">
         <v>0</v>
@@ -3460,22 +3460,22 @@
       <c r="A109" t="inlineStr"/>
       <c r="B109" t="inlineStr">
         <is>
-          <t>WM-SP-Monitor Arms- Branded</t>
+          <t>WM-SP-TV Brackets- Multi Asins- Exact</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>B0DB5VG39T</t>
+          <t>B0FHVWHQHR</t>
         </is>
       </c>
       <c r="D109" t="n">
-        <v>10.64</v>
+        <v>0</v>
       </c>
       <c r="E109" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F109" t="n">
-        <v>233</v>
+        <v>127</v>
       </c>
       <c r="G109" t="n">
         <v>0</v>
@@ -3488,78 +3488,78 @@
       <c r="A110" t="inlineStr"/>
       <c r="B110" t="inlineStr">
         <is>
-          <t>WM-SP-Monitor Arms- Branded</t>
+          <t>WM-SP-TV Brackets- Multi Asins- Exact</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>B0DB5VVPSB</t>
+          <t>B0FN4D3C89</t>
         </is>
       </c>
       <c r="D110" t="n">
-        <v>10.49</v>
+        <v>243.75</v>
       </c>
       <c r="E110" t="n">
-        <v>1</v>
+        <v>31</v>
       </c>
       <c r="F110" t="n">
-        <v>201</v>
+        <v>5775</v>
       </c>
       <c r="G110" t="n">
-        <v>0</v>
+        <v>854.24</v>
       </c>
       <c r="H110" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr"/>
       <c r="B111" t="inlineStr">
         <is>
-          <t>WM-SP-Monitor Arms- Branded</t>
+          <t>WM-SP-TV Brackets- Multi Asins- Exact</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>B0DB5W4TCP</t>
+          <t>B0FN4DSQ6P</t>
         </is>
       </c>
       <c r="D111" t="n">
-        <v>0</v>
+        <v>64.23</v>
       </c>
       <c r="E111" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="F111" t="n">
-        <v>498</v>
+        <v>941</v>
       </c>
       <c r="G111" t="n">
-        <v>0</v>
+        <v>1708.48</v>
       </c>
       <c r="H111" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr"/>
       <c r="B112" t="inlineStr">
         <is>
-          <t>WM-SP-Monitor Arms- Branded</t>
+          <t>WM-SP-TV Brackets- Multi Asins- PT</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>B0DB5YTQZV</t>
+          <t>B0FHVWHQHR</t>
         </is>
       </c>
       <c r="D112" t="n">
-        <v>0</v>
+        <v>28.42</v>
       </c>
       <c r="E112" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F112" t="n">
-        <v>166</v>
+        <v>161</v>
       </c>
       <c r="G112" t="n">
         <v>0</v>
@@ -3572,50 +3572,50 @@
       <c r="A113" t="inlineStr"/>
       <c r="B113" t="inlineStr">
         <is>
-          <t>WM-SP-Monitor Arms- Branded</t>
+          <t>WM-SP-TV Brackets- Multi Asins- PT</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>B0DP2Z5DQ9</t>
+          <t>B0FN4D3C89</t>
         </is>
       </c>
       <c r="D113" t="n">
-        <v>0</v>
+        <v>267.21</v>
       </c>
       <c r="E113" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="F113" t="n">
-        <v>573</v>
+        <v>1132</v>
       </c>
       <c r="G113" t="n">
-        <v>0</v>
+        <v>854.24</v>
       </c>
       <c r="H113" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr"/>
       <c r="B114" t="inlineStr">
         <is>
-          <t>WM-SP-Monitor Arms- Branded</t>
+          <t>WM-SP-TV Brackets- Multi Asins- PT</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>B0DP32F346</t>
+          <t>B0FN4DSQ6P</t>
         </is>
       </c>
       <c r="D114" t="n">
-        <v>10</v>
+        <v>47.88</v>
       </c>
       <c r="E114" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F114" t="n">
-        <v>893</v>
+        <v>181</v>
       </c>
       <c r="G114" t="n">
         <v>0</v>
@@ -3628,22 +3628,22 @@
       <c r="A115" t="inlineStr"/>
       <c r="B115" t="inlineStr">
         <is>
-          <t>WM-SP-Monitor Arms- Defensive</t>
+          <t>WM-SP-TV Brackets- Multi Asins- PT</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>B0DB5VG39T</t>
+          <t>B0FN4HDM6Z</t>
         </is>
       </c>
       <c r="D115" t="n">
-        <v>65.27</v>
+        <v>246.22</v>
       </c>
       <c r="E115" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="F115" t="n">
-        <v>407</v>
+        <v>467</v>
       </c>
       <c r="G115" t="n">
         <v>0</v>
@@ -3656,50 +3656,50 @@
       <c r="A116" t="inlineStr"/>
       <c r="B116" t="inlineStr">
         <is>
-          <t>WM-SP-Monitor Arms- Defensive</t>
+          <t>WM-SP-TV Brackets- Multi Asins- PT01</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>B0DB5VVPSB</t>
+          <t>B0FN4D3C89</t>
         </is>
       </c>
       <c r="D116" t="n">
-        <v>140.73</v>
+        <v>368.04</v>
       </c>
       <c r="E116" t="n">
-        <v>11</v>
+        <v>28</v>
       </c>
       <c r="F116" t="n">
-        <v>1106</v>
+        <v>3425</v>
       </c>
       <c r="G116" t="n">
-        <v>3812.72</v>
+        <v>1708.48</v>
       </c>
       <c r="H116" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr"/>
       <c r="B117" t="inlineStr">
         <is>
-          <t>WM-SP-Monitor Arms- Defensive</t>
+          <t>WM-SP-TV Brackets- Multi Asins- PT01</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>B0DB5W4TCP</t>
+          <t>B0FN4DSQ6P</t>
         </is>
       </c>
       <c r="D117" t="n">
-        <v>23.96</v>
+        <v>67.11</v>
       </c>
       <c r="E117" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="F117" t="n">
-        <v>453</v>
+        <v>753</v>
       </c>
       <c r="G117" t="n">
         <v>0</v>
@@ -3712,615 +3712,27 @@
       <c r="A118" t="inlineStr"/>
       <c r="B118" t="inlineStr">
         <is>
-          <t>WM-SP-Monitor Arms- Defensive</t>
+          <t>WM_SP_KT_Adjustable_Exact_Manual_HV</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>B0DB5YTQZV</t>
+          <t>B0CPT3Q25C</t>
         </is>
       </c>
       <c r="D118" t="n">
-        <v>163.73</v>
+        <v>902</v>
       </c>
       <c r="E118" t="n">
-        <v>15</v>
+        <v>32</v>
       </c>
       <c r="F118" t="n">
-        <v>2406</v>
+        <v>17591</v>
       </c>
       <c r="G118" t="n">
         <v>0</v>
       </c>
       <c r="H118" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="119">
-      <c r="A119" t="inlineStr"/>
-      <c r="B119" t="inlineStr">
-        <is>
-          <t>WM-SP-Monitor Arms- Defensive</t>
-        </is>
-      </c>
-      <c r="C119" t="inlineStr">
-        <is>
-          <t>B0DP2Z5DQ9</t>
-        </is>
-      </c>
-      <c r="D119" t="n">
-        <v>150.22</v>
-      </c>
-      <c r="E119" t="n">
-        <v>14</v>
-      </c>
-      <c r="F119" t="n">
-        <v>1200</v>
-      </c>
-      <c r="G119" t="n">
-        <v>2514.41</v>
-      </c>
-      <c r="H119" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="120">
-      <c r="A120" t="inlineStr"/>
-      <c r="B120" t="inlineStr">
-        <is>
-          <t>WM-SP-Monitor Arms- Defensive</t>
-        </is>
-      </c>
-      <c r="C120" t="inlineStr">
-        <is>
-          <t>B0DP32F346</t>
-        </is>
-      </c>
-      <c r="D120" t="n">
-        <v>38.99</v>
-      </c>
-      <c r="E120" t="n">
-        <v>3</v>
-      </c>
-      <c r="F120" t="n">
-        <v>312</v>
-      </c>
-      <c r="G120" t="n">
-        <v>0</v>
-      </c>
-      <c r="H120" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="121">
-      <c r="A121" t="inlineStr"/>
-      <c r="B121" t="inlineStr">
-        <is>
-          <t>WM-SP-Monitor Stand-B0DP2Z5DQ9 - PT</t>
-        </is>
-      </c>
-      <c r="C121" t="inlineStr">
-        <is>
-          <t>B0DP2Z5DQ9</t>
-        </is>
-      </c>
-      <c r="D121" t="n">
-        <v>762.8399999999999</v>
-      </c>
-      <c r="E121" t="n">
-        <v>48</v>
-      </c>
-      <c r="F121" t="n">
-        <v>3791</v>
-      </c>
-      <c r="G121" t="n">
-        <v>5028.809999999999</v>
-      </c>
-      <c r="H121" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="122">
-      <c r="A122" t="inlineStr"/>
-      <c r="B122" t="inlineStr">
-        <is>
-          <t>WM-SP-Monitor Stand-B0DP2Z5DQ9 - Phrase</t>
-        </is>
-      </c>
-      <c r="C122" t="inlineStr">
-        <is>
-          <t>B0DP2Z5DQ9</t>
-        </is>
-      </c>
-      <c r="D122" t="n">
-        <v>1343.12</v>
-      </c>
-      <c r="E122" t="n">
-        <v>85</v>
-      </c>
-      <c r="F122" t="n">
-        <v>9343</v>
-      </c>
-      <c r="G122" t="n">
-        <v>4849.139999999999</v>
-      </c>
-      <c r="H122" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="123">
-      <c r="A123" t="inlineStr"/>
-      <c r="B123" t="inlineStr">
-        <is>
-          <t>WM-SP-Monitor Stand-B0DP2Z5DQ9 -Phrase</t>
-        </is>
-      </c>
-      <c r="C123" t="inlineStr">
-        <is>
-          <t>B0DP2Z5DQ9</t>
-        </is>
-      </c>
-      <c r="D123" t="n">
-        <v>1081.89</v>
-      </c>
-      <c r="E123" t="n">
-        <v>51</v>
-      </c>
-      <c r="F123" t="n">
-        <v>12209</v>
-      </c>
-      <c r="G123" t="n">
-        <v>15508.48</v>
-      </c>
-      <c r="H123" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="124">
-      <c r="A124" t="inlineStr"/>
-      <c r="B124" t="inlineStr">
-        <is>
-          <t>WM-SP-POS stand- Multi - PT</t>
-        </is>
-      </c>
-      <c r="C124" t="inlineStr">
-        <is>
-          <t>B0FN4FPJ83</t>
-        </is>
-      </c>
-      <c r="D124" t="n">
-        <v>0</v>
-      </c>
-      <c r="E124" t="n">
-        <v>0</v>
-      </c>
-      <c r="F124" t="n">
-        <v>8</v>
-      </c>
-      <c r="G124" t="n">
-        <v>0</v>
-      </c>
-      <c r="H124" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="125">
-      <c r="A125" t="inlineStr"/>
-      <c r="B125" t="inlineStr">
-        <is>
-          <t>WM-SP-TV Brackets- Multi Asins- CT</t>
-        </is>
-      </c>
-      <c r="C125" t="inlineStr">
-        <is>
-          <t>B0FHVWHQHR</t>
-        </is>
-      </c>
-      <c r="D125" t="n">
-        <v>60.49</v>
-      </c>
-      <c r="E125" t="n">
-        <v>3</v>
-      </c>
-      <c r="F125" t="n">
-        <v>395</v>
-      </c>
-      <c r="G125" t="n">
-        <v>0</v>
-      </c>
-      <c r="H125" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="126">
-      <c r="A126" t="inlineStr"/>
-      <c r="B126" t="inlineStr">
-        <is>
-          <t>WM-SP-TV Brackets- Multi Asins- CT</t>
-        </is>
-      </c>
-      <c r="C126" t="inlineStr">
-        <is>
-          <t>B0FN4D3C89</t>
-        </is>
-      </c>
-      <c r="D126" t="n">
-        <v>792.8</v>
-      </c>
-      <c r="E126" t="n">
-        <v>44</v>
-      </c>
-      <c r="F126" t="n">
-        <v>6377</v>
-      </c>
-      <c r="G126" t="n">
-        <v>363.56</v>
-      </c>
-      <c r="H126" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="127">
-      <c r="A127" t="inlineStr"/>
-      <c r="B127" t="inlineStr">
-        <is>
-          <t>WM-SP-TV Brackets- Multi Asins- CT</t>
-        </is>
-      </c>
-      <c r="C127" t="inlineStr">
-        <is>
-          <t>B0FN4DSQ6P</t>
-        </is>
-      </c>
-      <c r="D127" t="n">
-        <v>225.47</v>
-      </c>
-      <c r="E127" t="n">
-        <v>16</v>
-      </c>
-      <c r="F127" t="n">
-        <v>2472</v>
-      </c>
-      <c r="G127" t="n">
-        <v>490.68</v>
-      </c>
-      <c r="H127" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="128">
-      <c r="A128" t="inlineStr"/>
-      <c r="B128" t="inlineStr">
-        <is>
-          <t>WM-SP-TV Brackets- Multi Asins- CT</t>
-        </is>
-      </c>
-      <c r="C128" t="inlineStr">
-        <is>
-          <t>B0FN4HDM6Z</t>
-        </is>
-      </c>
-      <c r="D128" t="n">
-        <v>292.58</v>
-      </c>
-      <c r="E128" t="n">
-        <v>17</v>
-      </c>
-      <c r="F128" t="n">
-        <v>2407</v>
-      </c>
-      <c r="G128" t="n">
-        <v>0</v>
-      </c>
-      <c r="H128" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="129">
-      <c r="A129" t="inlineStr"/>
-      <c r="B129" t="inlineStr">
-        <is>
-          <t>WM-SP-TV Brackets- Multi Asins- Exact</t>
-        </is>
-      </c>
-      <c r="C129" t="inlineStr">
-        <is>
-          <t>B0FHVWHQHR</t>
-        </is>
-      </c>
-      <c r="D129" t="n">
-        <v>7.55</v>
-      </c>
-      <c r="E129" t="n">
-        <v>1</v>
-      </c>
-      <c r="F129" t="n">
-        <v>332</v>
-      </c>
-      <c r="G129" t="n">
-        <v>0</v>
-      </c>
-      <c r="H129" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="130">
-      <c r="A130" t="inlineStr"/>
-      <c r="B130" t="inlineStr">
-        <is>
-          <t>WM-SP-TV Brackets- Multi Asins- Exact</t>
-        </is>
-      </c>
-      <c r="C130" t="inlineStr">
-        <is>
-          <t>B0FN4D3C89</t>
-        </is>
-      </c>
-      <c r="D130" t="n">
-        <v>811.5699999999999</v>
-      </c>
-      <c r="E130" t="n">
-        <v>99</v>
-      </c>
-      <c r="F130" t="n">
-        <v>21651</v>
-      </c>
-      <c r="G130" t="n">
-        <v>3053.4</v>
-      </c>
-      <c r="H130" t="n">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="131">
-      <c r="A131" t="inlineStr"/>
-      <c r="B131" t="inlineStr">
-        <is>
-          <t>WM-SP-TV Brackets- Multi Asins- Exact</t>
-        </is>
-      </c>
-      <c r="C131" t="inlineStr">
-        <is>
-          <t>B0FN4DSQ6P</t>
-        </is>
-      </c>
-      <c r="D131" t="n">
-        <v>140.32</v>
-      </c>
-      <c r="E131" t="n">
-        <v>15</v>
-      </c>
-      <c r="F131" t="n">
-        <v>3331</v>
-      </c>
-      <c r="G131" t="n">
-        <v>1708.48</v>
-      </c>
-      <c r="H131" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="132">
-      <c r="A132" t="inlineStr"/>
-      <c r="B132" t="inlineStr">
-        <is>
-          <t>WM-SP-TV Brackets- Multi Asins- PT</t>
-        </is>
-      </c>
-      <c r="C132" t="inlineStr">
-        <is>
-          <t>B0FHVWHQHR</t>
-        </is>
-      </c>
-      <c r="D132" t="n">
-        <v>98.56</v>
-      </c>
-      <c r="E132" t="n">
-        <v>5</v>
-      </c>
-      <c r="F132" t="n">
-        <v>822</v>
-      </c>
-      <c r="G132" t="n">
-        <v>617.8</v>
-      </c>
-      <c r="H132" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="133">
-      <c r="A133" t="inlineStr"/>
-      <c r="B133" t="inlineStr">
-        <is>
-          <t>WM-SP-TV Brackets- Multi Asins- PT</t>
-        </is>
-      </c>
-      <c r="C133" t="inlineStr">
-        <is>
-          <t>B0FN4D3C89</t>
-        </is>
-      </c>
-      <c r="D133" t="n">
-        <v>727.13</v>
-      </c>
-      <c r="E133" t="n">
-        <v>34</v>
-      </c>
-      <c r="F133" t="n">
-        <v>4789</v>
-      </c>
-      <c r="G133" t="n">
-        <v>1581.36</v>
-      </c>
-      <c r="H133" t="n">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="134">
-      <c r="A134" t="inlineStr"/>
-      <c r="B134" t="inlineStr">
-        <is>
-          <t>WM-SP-TV Brackets- Multi Asins- PT</t>
-        </is>
-      </c>
-      <c r="C134" t="inlineStr">
-        <is>
-          <t>B0FN4DSQ6P</t>
-        </is>
-      </c>
-      <c r="D134" t="n">
-        <v>559.3399999999999</v>
-      </c>
-      <c r="E134" t="n">
-        <v>23</v>
-      </c>
-      <c r="F134" t="n">
-        <v>2157</v>
-      </c>
-      <c r="G134" t="n">
-        <v>2453.4</v>
-      </c>
-      <c r="H134" t="n">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="135">
-      <c r="A135" t="inlineStr"/>
-      <c r="B135" t="inlineStr">
-        <is>
-          <t>WM-SP-TV Brackets- Multi Asins- PT</t>
-        </is>
-      </c>
-      <c r="C135" t="inlineStr">
-        <is>
-          <t>B0FN4HDM6Z</t>
-        </is>
-      </c>
-      <c r="D135" t="n">
-        <v>629.0599999999999</v>
-      </c>
-      <c r="E135" t="n">
-        <v>26</v>
-      </c>
-      <c r="F135" t="n">
-        <v>1866</v>
-      </c>
-      <c r="G135" t="n">
-        <v>0</v>
-      </c>
-      <c r="H135" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="136">
-      <c r="A136" t="inlineStr"/>
-      <c r="B136" t="inlineStr">
-        <is>
-          <t>WM-SP-TV Brackets- Multi Asins- PT01</t>
-        </is>
-      </c>
-      <c r="C136" t="inlineStr">
-        <is>
-          <t>B0FN4D3C89</t>
-        </is>
-      </c>
-      <c r="D136" t="n">
-        <v>1160.23</v>
-      </c>
-      <c r="E136" t="n">
-        <v>85</v>
-      </c>
-      <c r="F136" t="n">
-        <v>12612</v>
-      </c>
-      <c r="G136" t="n">
-        <v>2435.6</v>
-      </c>
-      <c r="H136" t="n">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="137">
-      <c r="A137" t="inlineStr"/>
-      <c r="B137" t="inlineStr">
-        <is>
-          <t>WM-SP-TV Brackets- Multi Asins- PT01</t>
-        </is>
-      </c>
-      <c r="C137" t="inlineStr">
-        <is>
-          <t>B0FN4DSQ6P</t>
-        </is>
-      </c>
-      <c r="D137" t="n">
-        <v>411.65</v>
-      </c>
-      <c r="E137" t="n">
-        <v>31</v>
-      </c>
-      <c r="F137" t="n">
-        <v>3746</v>
-      </c>
-      <c r="G137" t="n">
-        <v>1708.48</v>
-      </c>
-      <c r="H137" t="n">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="138">
-      <c r="A138" t="inlineStr"/>
-      <c r="B138" t="inlineStr">
-        <is>
-          <t>WM-SP-TV Brackets- Multi Asins- PT01</t>
-        </is>
-      </c>
-      <c r="C138" t="inlineStr">
-        <is>
-          <t>B0FN4GQ9HT</t>
-        </is>
-      </c>
-      <c r="D138" t="n">
-        <v>78.28999999999999</v>
-      </c>
-      <c r="E138" t="n">
-        <v>5</v>
-      </c>
-      <c r="F138" t="n">
-        <v>765</v>
-      </c>
-      <c r="G138" t="n">
-        <v>0</v>
-      </c>
-      <c r="H138" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="139">
-      <c r="A139" t="inlineStr"/>
-      <c r="B139" t="inlineStr">
-        <is>
-          <t>WM_SP_KT_Adjustable_Exact_Manual_HV</t>
-        </is>
-      </c>
-      <c r="C139" t="inlineStr">
-        <is>
-          <t>B0CPT3Q25C</t>
-        </is>
-      </c>
-      <c r="D139" t="n">
-        <v>2212.5</v>
-      </c>
-      <c r="E139" t="n">
-        <v>77</v>
-      </c>
-      <c r="F139" t="n">
-        <v>41849</v>
-      </c>
-      <c r="G139" t="n">
-        <v>0</v>
-      </c>
-      <c r="H139" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4617,13 +4029,13 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>757.21</v>
+        <v>200.51</v>
       </c>
       <c r="E10" t="n">
-        <v>58</v>
+        <v>15</v>
       </c>
       <c r="F10" t="n">
-        <v>25409</v>
+        <v>6378</v>
       </c>
       <c r="G10" t="n">
         <v>0</v>
@@ -4645,19 +4057,19 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>717.03</v>
+        <v>232.84</v>
       </c>
       <c r="E11" t="n">
-        <v>90</v>
+        <v>24</v>
       </c>
       <c r="F11" t="n">
-        <v>28142</v>
+        <v>9520</v>
       </c>
       <c r="G11" t="n">
-        <v>2989.83</v>
+        <v>2626.27</v>
       </c>
       <c r="H11" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="12">
@@ -4729,13 +4141,13 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>645.85</v>
+        <v>233.23</v>
       </c>
       <c r="E14" t="n">
-        <v>53</v>
+        <v>23</v>
       </c>
       <c r="F14" t="n">
-        <v>22637</v>
+        <v>9367</v>
       </c>
       <c r="G14" t="n">
         <v>0</v>
@@ -4757,13 +4169,13 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>576.37</v>
+        <v>221.81</v>
       </c>
       <c r="E15" t="n">
-        <v>82</v>
+        <v>34</v>
       </c>
       <c r="F15" t="n">
-        <v>20463</v>
+        <v>7289</v>
       </c>
       <c r="G15" t="n">
         <v>7878.82</v>
@@ -4867,7 +4279,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I30"/>
+  <dimension ref="A1:I27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4930,7 +4342,7 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E2" t="n">
         <v>0</v>
@@ -4963,7 +4375,7 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E3" t="n">
         <v>0</v>
@@ -4996,7 +4408,7 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E4" t="n">
         <v>0</v>
@@ -5029,7 +4441,7 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E5" t="n">
         <v>0</v>
@@ -5062,7 +4474,7 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E6" t="n">
         <v>0</v>
@@ -5095,7 +4507,7 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E7" t="n">
         <v>0</v>
@@ -5326,19 +4738,19 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>2699</v>
+        <v>2320</v>
       </c>
       <c r="E14" t="n">
-        <v>114</v>
+        <v>90</v>
       </c>
       <c r="F14" t="n">
-        <v>248.9471468494729</v>
+        <v>211.525</v>
       </c>
       <c r="G14" t="n">
-        <v>12684.41370457933</v>
+        <v>6573.73</v>
       </c>
       <c r="H14" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
@@ -5355,23 +4767,23 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>B0BFVNS8HS</t>
+          <t>B0CPFS24ML</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>2861</v>
+        <v>2320</v>
       </c>
       <c r="E15" t="n">
-        <v>121</v>
+        <v>90</v>
       </c>
       <c r="F15" t="n">
-        <v>263.8859037867783</v>
+        <v>211.525</v>
       </c>
       <c r="G15" t="n">
-        <v>13445.57676920169</v>
+        <v>6573.73</v>
       </c>
       <c r="H15" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
@@ -5383,28 +4795,28 @@
       <c r="A16" t="inlineStr"/>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Camb-SB-Multiple Asin- Product collection- exact /Reach</t>
+          <t>Camb-SB-Multiple Asin- product collection- Reach</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>B0BFWD6SNF</t>
+          <t>B0CPT3Q25C</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>2715</v>
+        <v>1116</v>
       </c>
       <c r="E16" t="n">
-        <v>115</v>
+        <v>17</v>
       </c>
       <c r="F16" t="n">
-        <v>250.4382781298041</v>
+        <v>156.5366666666667</v>
       </c>
       <c r="G16" t="n">
-        <v>12760.39017704317</v>
+        <v>2400.846666666667</v>
       </c>
       <c r="H16" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
@@ -5416,28 +4828,28 @@
       <c r="A17" t="inlineStr"/>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Camb-SB-Multiple Asin- Product collection- exact /Reach</t>
+          <t>Camb-SB-Multiple Asin- product collection- Reach</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>B0CPFS24ML</t>
+          <t>B0DQ1NV8D2</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>2683</v>
+        <v>1116</v>
       </c>
       <c r="E17" t="n">
-        <v>114</v>
+        <v>17</v>
       </c>
       <c r="F17" t="n">
-        <v>247.4563674170135</v>
+        <v>156.5366666666667</v>
       </c>
       <c r="G17" t="n">
-        <v>12608.45515955119</v>
+        <v>2400.846666666667</v>
       </c>
       <c r="H17" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
@@ -5449,28 +4861,28 @@
       <c r="A18" t="inlineStr"/>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Camb-SB-Multiple Asin- Product collection- exact /Reach</t>
+          <t>Camb-SB-Multiple Asin- product collection- Reach</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>B0DQPK7MFH</t>
+          <t>B0DQ4YWSMC</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>2300</v>
+        <v>1116</v>
       </c>
       <c r="E18" t="n">
-        <v>97</v>
+        <v>17</v>
       </c>
       <c r="F18" t="n">
-        <v>212.1523038169314</v>
+        <v>156.5366666666667</v>
       </c>
       <c r="G18" t="n">
-        <v>10809.63418962462</v>
+        <v>2400.846666666667</v>
       </c>
       <c r="H18" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
@@ -5482,28 +4894,28 @@
       <c r="A19" t="inlineStr"/>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Camb-SB-Multiple Asin- product collection- Reach</t>
+          <t>WM- SBV- Wooden Arm- B0DP32F346- Phrase</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>B0CPT3Q25C</t>
+          <t>B0DP32F346</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>3412</v>
+        <v>3090</v>
       </c>
       <c r="E19" t="n">
-        <v>62</v>
+        <v>37</v>
       </c>
       <c r="F19" t="n">
-        <v>478.47</v>
+        <v>413.9400000000001</v>
       </c>
       <c r="G19" t="n">
-        <v>4801.693333333334</v>
+        <v>0</v>
       </c>
       <c r="H19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
@@ -5515,28 +4927,28 @@
       <c r="A20" t="inlineStr"/>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Camb-SB-Multiple Asin- product collection- Reach</t>
+          <t>WM- SBV-Wall Mounted Stand- B0DP2WC5VW- Phrase &amp; exact</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>B0DQ1NV8D2</t>
+          <t>B0DP2WC5VW</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>3412</v>
+        <v>4671</v>
       </c>
       <c r="E20" t="n">
-        <v>62</v>
+        <v>54</v>
       </c>
       <c r="F20" t="n">
-        <v>478.47</v>
+        <v>828.5999999999999</v>
       </c>
       <c r="G20" t="n">
-        <v>4801.693333333334</v>
+        <v>0</v>
       </c>
       <c r="H20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
@@ -5548,28 +4960,28 @@
       <c r="A21" t="inlineStr"/>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Camb-SB-Multiple Asin- product collection- Reach</t>
+          <t>WM-SB-Monitor Arms-Defensive</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>B0DQ4YWSMC</t>
+          <t>B0DB5VG39T</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>3412</v>
+        <v>409</v>
       </c>
       <c r="E21" t="n">
-        <v>62</v>
+        <v>7</v>
       </c>
       <c r="F21" t="n">
-        <v>478.47</v>
+        <v>74.98833333333332</v>
       </c>
       <c r="G21" t="n">
-        <v>4801.693333333334</v>
+        <v>607.2033333333333</v>
       </c>
       <c r="H21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
@@ -5581,25 +4993,25 @@
       <c r="A22" t="inlineStr"/>
       <c r="B22" t="inlineStr">
         <is>
-          <t>WM- SBV- Wooden Arm- B0DP32F346- Phrase</t>
+          <t>WM-SB-Monitor Arms-Defensive</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>B0DP32F346</t>
+          <t>B0DB5VVPSB</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>8112</v>
+        <v>409</v>
       </c>
       <c r="E22" t="n">
-        <v>98</v>
+        <v>7</v>
       </c>
       <c r="F22" t="n">
-        <v>1166.81</v>
+        <v>74.98833333333332</v>
       </c>
       <c r="G22" t="n">
-        <v>0</v>
+        <v>607.2033333333333</v>
       </c>
       <c r="H22" t="n">
         <v>0</v>
@@ -5614,28 +5026,28 @@
       <c r="A23" t="inlineStr"/>
       <c r="B23" t="inlineStr">
         <is>
-          <t>WM- SBV-Wall Mounted Stand- B0DP2WC5VW- Phrase &amp; exact</t>
+          <t>WM-SB-Monitor Arms-Defensive</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>B0DP2WC5VW</t>
+          <t>B0DB5W4TCP</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>14721</v>
+        <v>409</v>
       </c>
       <c r="E23" t="n">
-        <v>171</v>
+        <v>7</v>
       </c>
       <c r="F23" t="n">
-        <v>2406.42</v>
+        <v>74.98833333333332</v>
       </c>
       <c r="G23" t="n">
-        <v>5422.030000000001</v>
+        <v>607.2033333333333</v>
       </c>
       <c r="H23" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I23" t="inlineStr">
         <is>
@@ -5652,7 +5064,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>B0DB5VG39T</t>
+          <t>B0DB5YTQZV</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -5665,7 +5077,7 @@
         <v>74.98833333333332</v>
       </c>
       <c r="G24" t="n">
-        <v>0</v>
+        <v>607.2033333333333</v>
       </c>
       <c r="H24" t="n">
         <v>0</v>
@@ -5685,7 +5097,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>B0DB5VVPSB</t>
+          <t>B0DP2Z5DQ9</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -5698,7 +5110,7 @@
         <v>74.98833333333332</v>
       </c>
       <c r="G25" t="n">
-        <v>0</v>
+        <v>607.2033333333333</v>
       </c>
       <c r="H25" t="n">
         <v>0</v>
@@ -5718,7 +5130,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>B0DB5W4TCP</t>
+          <t>B0DP32F346</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -5731,7 +5143,7 @@
         <v>74.98833333333332</v>
       </c>
       <c r="G26" t="n">
-        <v>0</v>
+        <v>607.2033333333333</v>
       </c>
       <c r="H26" t="n">
         <v>0</v>
@@ -5746,22 +5158,22 @@
       <c r="A27" t="inlineStr"/>
       <c r="B27" t="inlineStr">
         <is>
-          <t>WM-SB-Monitor Arms-Defensive</t>
+          <t>WM-SBV-Gas Spring MA- B0DB5VG39T- Phrase</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>B0DB5YTQZV</t>
+          <t>B0DB5VG39T</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>409</v>
+        <v>4957</v>
       </c>
       <c r="E27" t="n">
-        <v>7</v>
+        <v>38</v>
       </c>
       <c r="F27" t="n">
-        <v>74.98833333333332</v>
+        <v>699.6800000000001</v>
       </c>
       <c r="G27" t="n">
         <v>0</v>
@@ -5770,105 +5182,6 @@
         <v>0</v>
       </c>
       <c r="I27" t="inlineStr">
-        <is>
-          <t>White Mulberry</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr"/>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>WM-SB-Monitor Arms-Defensive</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>B0DP2Z5DQ9</t>
-        </is>
-      </c>
-      <c r="D28" t="n">
-        <v>409</v>
-      </c>
-      <c r="E28" t="n">
-        <v>7</v>
-      </c>
-      <c r="F28" t="n">
-        <v>74.98833333333332</v>
-      </c>
-      <c r="G28" t="n">
-        <v>0</v>
-      </c>
-      <c r="H28" t="n">
-        <v>0</v>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>White Mulberry</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr"/>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>WM-SB-Monitor Arms-Defensive</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>B0DP32F346</t>
-        </is>
-      </c>
-      <c r="D29" t="n">
-        <v>409</v>
-      </c>
-      <c r="E29" t="n">
-        <v>7</v>
-      </c>
-      <c r="F29" t="n">
-        <v>74.98833333333332</v>
-      </c>
-      <c r="G29" t="n">
-        <v>0</v>
-      </c>
-      <c r="H29" t="n">
-        <v>0</v>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>White Mulberry</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr"/>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>WM-SBV-Gas Spring MA- B0DB5VG39T- Phrase</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>B0DB5VG39T</t>
-        </is>
-      </c>
-      <c r="D30" t="n">
-        <v>13742</v>
-      </c>
-      <c r="E30" t="n">
-        <v>106</v>
-      </c>
-      <c r="F30" t="n">
-        <v>1843.07</v>
-      </c>
-      <c r="G30" t="n">
-        <v>0</v>
-      </c>
-      <c r="H30" t="n">
-        <v>0</v>
-      </c>
-      <c r="I30" t="inlineStr">
         <is>
           <t>White Mulberry</t>
         </is>

--- a/data/ams_weekly_data/White_Mulberry/ads_report_week22.xlsx
+++ b/data/ams_weekly_data/White_Mulberry/ads_report_week22.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H118"/>
+  <dimension ref="A1:H140"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -473,13 +473,13 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>271.34</v>
+        <v>334.8</v>
       </c>
       <c r="E2" t="n">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="F2" t="n">
-        <v>2349</v>
+        <v>2782</v>
       </c>
       <c r="G2" t="n">
         <v>0</v>
@@ -501,13 +501,13 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>109.36</v>
+        <v>122.03</v>
       </c>
       <c r="E3" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F3" t="n">
-        <v>1512</v>
+        <v>2082</v>
       </c>
       <c r="G3" t="n">
         <v>0</v>
@@ -520,7 +520,7 @@
       <c r="A4" t="inlineStr"/>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Camb-B0BFVMDJ2K-L Shaped -Exact &amp; Phrase(1)-SP</t>
+          <t>Camb-B0BFVMDJ2K /B0BFWD6SNF -L shaped-SP-KT-BM</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -529,13 +529,13 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>328.46</v>
+        <v>755.02</v>
       </c>
       <c r="E4" t="n">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="F4" t="n">
-        <v>2477</v>
+        <v>4293</v>
       </c>
       <c r="G4" t="n">
         <v>0</v>
@@ -548,22 +548,22 @@
       <c r="A5" t="inlineStr"/>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Camb-B0BFW59TRG-L-Shape-Phrase-Exact-SP</t>
+          <t>Camb-B0BFVMDJ2K-L Shaped -Exact &amp; Phrase(1)-SP</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>B0BFW59TRG</t>
+          <t>B0BFVMDJ2K</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>32.79</v>
+        <v>328.46</v>
       </c>
       <c r="E5" t="n">
-        <v>1</v>
+        <v>17</v>
       </c>
       <c r="F5" t="n">
-        <v>128</v>
+        <v>2477</v>
       </c>
       <c r="G5" t="n">
         <v>0</v>
@@ -576,22 +576,22 @@
       <c r="A6" t="inlineStr"/>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Camb-B0CPT3Q25C - Motorized-SP-PT</t>
+          <t>Camb-B0BFW59TRG-L-Shape-Phrase-Exact-SP</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>B0CPT3Q25C</t>
+          <t>B0BFW59TRG</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>545.3199999999999</v>
+        <v>32.79</v>
       </c>
       <c r="E6" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="F6" t="n">
-        <v>595</v>
+        <v>128</v>
       </c>
       <c r="G6" t="n">
         <v>0</v>
@@ -604,28 +604,28 @@
       <c r="A7" t="inlineStr"/>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Camb-L shaped-SP- B0BFVMDJ2K /B0BFWD6SNF -BM</t>
+          <t>Camb-B0CPT3Q25C - Motorized-SP-PT</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>B0BFVMDJ2K</t>
+          <t>B0CPT3Q25C</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>234.84</v>
+        <v>1686.64</v>
       </c>
       <c r="E7" t="n">
-        <v>10</v>
+        <v>46</v>
       </c>
       <c r="F7" t="n">
-        <v>1771</v>
+        <v>4613</v>
       </c>
       <c r="G7" t="n">
-        <v>0</v>
+        <v>12712.72</v>
       </c>
       <c r="H7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="8">
@@ -637,17 +637,17 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>B0BFWD6SNF</t>
+          <t>B0BFVMDJ2K</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>80.72</v>
+        <v>234.84</v>
       </c>
       <c r="E8" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="F8" t="n">
-        <v>2705</v>
+        <v>1771</v>
       </c>
       <c r="G8" t="n">
         <v>0</v>
@@ -660,22 +660,22 @@
       <c r="A9" t="inlineStr"/>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Camb-Lshape- B0BFVMDJ2K/ B0BFWD6SNF - BM</t>
+          <t>Camb-L shaped-SP- B0BFVMDJ2K /B0BFWD6SNF -BM</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>B0BFVMDJ2K</t>
+          <t>B0BFWD6SNF</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>273.46</v>
+        <v>80.72</v>
       </c>
       <c r="E9" t="n">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="F9" t="n">
-        <v>1636</v>
+        <v>2705</v>
       </c>
       <c r="G9" t="n">
         <v>0</v>
@@ -693,17 +693,17 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>B0BFWD6SNF</t>
+          <t>B0BFVMDJ2K</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>242.05</v>
+        <v>273.46</v>
       </c>
       <c r="E10" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="F10" t="n">
-        <v>3341</v>
+        <v>1636</v>
       </c>
       <c r="G10" t="n">
         <v>0</v>
@@ -716,22 +716,22 @@
       <c r="A11" t="inlineStr"/>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Camb-Lshape- B0BFVMDJ2K/ B0BFWD6SNF - Phrase</t>
+          <t>Camb-Lshape- B0BFVMDJ2K/ B0BFWD6SNF - BM</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>B0BFVMDJ2K</t>
+          <t>B0BFWD6SNF</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>0</v>
+        <v>242.05</v>
       </c>
       <c r="E11" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="F11" t="n">
-        <v>64</v>
+        <v>3341</v>
       </c>
       <c r="G11" t="n">
         <v>0</v>
@@ -749,7 +749,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>B0BFWD6SNF</t>
+          <t>B0BFVMDJ2K</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -772,22 +772,22 @@
       <c r="A13" t="inlineStr"/>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Camb-Motorized  Desk- B0CPT3Q25C - PT</t>
+          <t>Camb-Lshape- B0BFVMDJ2K/ B0BFWD6SNF - Phrase</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>B0CPT3Q25C</t>
+          <t>B0BFWD6SNF</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>248.55</v>
+        <v>0</v>
       </c>
       <c r="E13" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="F13" t="n">
-        <v>552</v>
+        <v>64</v>
       </c>
       <c r="G13" t="n">
         <v>0</v>
@@ -800,22 +800,22 @@
       <c r="A14" t="inlineStr"/>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Camb-SP-B0BFVNS8HS -L-Shape-Exact-phrase</t>
+          <t>Camb-Motorized  Desk- B0CPT3Q25C - PT</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>B0BFVNS8HS</t>
+          <t>B0CPT3Q25C</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>54.92</v>
+        <v>568.9399999999999</v>
       </c>
       <c r="E14" t="n">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="F14" t="n">
-        <v>37</v>
+        <v>1395</v>
       </c>
       <c r="G14" t="n">
         <v>0</v>
@@ -828,22 +828,22 @@
       <c r="A15" t="inlineStr"/>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Camb-SP-Branded</t>
+          <t>Camb-SP-B0BFVNS8HS -L-Shape-Exact-phrase</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>B0BFVMDJ2K</t>
+          <t>B0BFVNS8HS</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>0</v>
+        <v>54.92</v>
       </c>
       <c r="E15" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F15" t="n">
-        <v>9</v>
+        <v>37</v>
       </c>
       <c r="G15" t="n">
         <v>0</v>
@@ -861,7 +861,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>B0BFVNS8HS</t>
+          <t>B0BFVMDJ2K</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -871,7 +871,7 @@
         <v>0</v>
       </c>
       <c r="F16" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="G16" t="n">
         <v>0</v>
@@ -889,7 +889,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>B0BFW59TRG</t>
+          <t>B0BFVNS8HS</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -899,7 +899,7 @@
         <v>0</v>
       </c>
       <c r="F17" t="n">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="G17" t="n">
         <v>0</v>
@@ -917,7 +917,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>B0BFWD6SNF</t>
+          <t>B0BFW59TRG</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -927,7 +927,7 @@
         <v>0</v>
       </c>
       <c r="F18" t="n">
-        <v>29</v>
+        <v>17</v>
       </c>
       <c r="G18" t="n">
         <v>0</v>
@@ -945,17 +945,17 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>B0CPT3Q25C</t>
+          <t>B0BFWD6SNF</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>24.39</v>
+        <v>0</v>
       </c>
       <c r="E19" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F19" t="n">
-        <v>287</v>
+        <v>29</v>
       </c>
       <c r="G19" t="n">
         <v>0</v>
@@ -973,17 +973,17 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>B0DQ4YWSMC</t>
+          <t>B0CPT3Q25C</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>0</v>
+        <v>72.89</v>
       </c>
       <c r="E20" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="F20" t="n">
-        <v>147</v>
+        <v>361</v>
       </c>
       <c r="G20" t="n">
         <v>0</v>
@@ -996,22 +996,22 @@
       <c r="A21" t="inlineStr"/>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Camb-SP-Lshape-B0BFVMDJ2K/B0BFWD6SNF- Exact/Phrase</t>
+          <t>Camb-SP-Branded</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>B0BFVMDJ2K</t>
+          <t>B0DQ4YWSMC</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>1235.44</v>
+        <v>0</v>
       </c>
       <c r="E21" t="n">
-        <v>58</v>
+        <v>0</v>
       </c>
       <c r="F21" t="n">
-        <v>11945</v>
+        <v>199</v>
       </c>
       <c r="G21" t="n">
         <v>0</v>
@@ -1024,22 +1024,22 @@
       <c r="A22" t="inlineStr"/>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Camb-SP-Lshape-B0BFWD6SNF - Broad</t>
+          <t>Camb-SP-Lshape-B0BFVMDJ2K/B0BFWD6SNF- Exact/Phrase</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>B0BFWD6SNF</t>
+          <t>B0BFVMDJ2K</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>103.37</v>
+        <v>4360.23</v>
       </c>
       <c r="E22" t="n">
-        <v>11</v>
+        <v>196</v>
       </c>
       <c r="F22" t="n">
-        <v>1381</v>
+        <v>32062</v>
       </c>
       <c r="G22" t="n">
         <v>0</v>
@@ -1052,22 +1052,22 @@
       <c r="A23" t="inlineStr"/>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Camb-SP-Lshape-CDesk-Multiple Asin- PT</t>
+          <t>Camb-SP-Lshape-B0BFWD6SNF - Broad</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>B0BFW59TRG</t>
+          <t>B0BFWD6SNF</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>228.1</v>
+        <v>617.98</v>
       </c>
       <c r="E23" t="n">
-        <v>9</v>
+        <v>50</v>
       </c>
       <c r="F23" t="n">
-        <v>1158</v>
+        <v>6749</v>
       </c>
       <c r="G23" t="n">
         <v>0</v>
@@ -1080,50 +1080,50 @@
       <c r="A24" t="inlineStr"/>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Camb-SP-Lshape-Multi Asin- AT</t>
+          <t>Camb-SP-Lshape-CDesk-Multiple Asin- PT</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>B0BFVMDJ2K</t>
+          <t>B0BFW59TRG</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>416.65</v>
+        <v>483.13</v>
       </c>
       <c r="E24" t="n">
         <v>17</v>
       </c>
       <c r="F24" t="n">
-        <v>1822</v>
+        <v>2235</v>
       </c>
       <c r="G24" t="n">
-        <v>0</v>
+        <v>7202.54</v>
       </c>
       <c r="H24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr"/>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Camb-SP-Lshape-Multi Asin- AT</t>
+          <t>Camb-SP-Lshape-CDesk-Multiple Asin- PT</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>B0BFVNS8HS</t>
+          <t>B0BFWD6SNF</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>50.11</v>
+        <v>76.38</v>
       </c>
       <c r="E25" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F25" t="n">
-        <v>392</v>
+        <v>448</v>
       </c>
       <c r="G25" t="n">
         <v>0</v>
@@ -1141,23 +1141,23 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>B0BFW59TRG</t>
+          <t>B0BFVMDJ2K</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>59.19</v>
+        <v>1541.99</v>
       </c>
       <c r="E26" t="n">
-        <v>2</v>
+        <v>64</v>
       </c>
       <c r="F26" t="n">
-        <v>327</v>
+        <v>6712</v>
       </c>
       <c r="G26" t="n">
-        <v>0</v>
+        <v>7075.42</v>
       </c>
       <c r="H26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="27">
@@ -1169,17 +1169,17 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>B0BFWD6SNF</t>
+          <t>B0BFVNS8HS</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>330.96</v>
+        <v>234.06</v>
       </c>
       <c r="E27" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="F27" t="n">
-        <v>2689</v>
+        <v>1469</v>
       </c>
       <c r="G27" t="n">
         <v>0</v>
@@ -1192,22 +1192,22 @@
       <c r="A28" t="inlineStr"/>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Camb-SP-Lshape-Multiple Asins- Exact 01</t>
+          <t>Camb-SP-Lshape-Multi Asin- AT</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>B0BFVMDJ2K</t>
+          <t>B0BFW59TRG</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>1201.54</v>
+        <v>133.16</v>
       </c>
       <c r="E28" t="n">
-        <v>45</v>
+        <v>5</v>
       </c>
       <c r="F28" t="n">
-        <v>13867</v>
+        <v>831</v>
       </c>
       <c r="G28" t="n">
         <v>0</v>
@@ -1220,22 +1220,22 @@
       <c r="A29" t="inlineStr"/>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Camb-SP-Lshape-Multiple Asins- Exact 01</t>
+          <t>Camb-SP-Lshape-Multi Asin- AT</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>B0BFW59TRG</t>
+          <t>B0BFWD6SNF</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>55.52</v>
+        <v>771.41</v>
       </c>
       <c r="E29" t="n">
-        <v>3</v>
+        <v>30</v>
       </c>
       <c r="F29" t="n">
-        <v>1843</v>
+        <v>6303</v>
       </c>
       <c r="G29" t="n">
         <v>0</v>
@@ -1248,7 +1248,7 @@
       <c r="A30" t="inlineStr"/>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Camb-SP-Lshape-Multiple Asins- Exact/Phrase</t>
+          <t>Camb-SP-Lshape-Multiple Asins- Exact 01</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -1257,26 +1257,26 @@
         </is>
       </c>
       <c r="D30" t="n">
-        <v>63.86</v>
+        <v>4472.37</v>
       </c>
       <c r="E30" t="n">
-        <v>4</v>
+        <v>165</v>
       </c>
       <c r="F30" t="n">
-        <v>807</v>
+        <v>46188</v>
       </c>
       <c r="G30" t="n">
-        <v>7075.42</v>
+        <v>0</v>
       </c>
       <c r="H30" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr"/>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Camb-SP-Lshape-Multiple Asins- Exact/Phrase</t>
+          <t>Camb-SP-Lshape-Multiple Asins- Exact 01</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -1285,13 +1285,13 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>879.39</v>
+        <v>303.31</v>
       </c>
       <c r="E31" t="n">
-        <v>42</v>
+        <v>10</v>
       </c>
       <c r="F31" t="n">
-        <v>14022</v>
+        <v>3291</v>
       </c>
       <c r="G31" t="n">
         <v>0</v>
@@ -1309,17 +1309,17 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>B0BFWD6SNF</t>
+          <t>B0BFVMDJ2K</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>98.16</v>
+        <v>138.13</v>
       </c>
       <c r="E32" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="F32" t="n">
-        <v>2170</v>
+        <v>1625</v>
       </c>
       <c r="G32" t="n">
         <v>0</v>
@@ -1332,22 +1332,22 @@
       <c r="A33" t="inlineStr"/>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Camb-SP-Motorized Desk- B0CPT3Q25C- Exact</t>
+          <t>Camb-SP-Lshape-Multiple Asins- Exact/Phrase</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>B0CPT3Q25C</t>
+          <t>B0BFW59TRG</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>471.98</v>
+        <v>3062.51</v>
       </c>
       <c r="E33" t="n">
-        <v>14</v>
+        <v>127</v>
       </c>
       <c r="F33" t="n">
-        <v>2212</v>
+        <v>40004</v>
       </c>
       <c r="G33" t="n">
         <v>0</v>
@@ -1360,22 +1360,22 @@
       <c r="A34" t="inlineStr"/>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Camb-SP-Motorized Desk-B0CPT3Q25C - PT01</t>
+          <t>Camb-SP-Lshape-Multiple Asins- Exact/Phrase</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>B0CPT3Q25C</t>
+          <t>B0BFWD6SNF</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>330.83</v>
+        <v>184</v>
       </c>
       <c r="E34" t="n">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="F34" t="n">
-        <v>1421</v>
+        <v>3868</v>
       </c>
       <c r="G34" t="n">
         <v>0</v>
@@ -1388,22 +1388,22 @@
       <c r="A35" t="inlineStr"/>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Camb-SP-Motorized Desk-B0CPT3Q25C- Exact</t>
+          <t>Camb-SP-Lshape-Multiple Asins- PT</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>B0CPT3Q25C</t>
+          <t>B0BFVMDJ2K</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>648.99</v>
+        <v>0</v>
       </c>
       <c r="E35" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="F35" t="n">
-        <v>7264</v>
+        <v>0</v>
       </c>
       <c r="G35" t="n">
         <v>0</v>
@@ -1416,22 +1416,22 @@
       <c r="A36" t="inlineStr"/>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Camb-SP-Zshape-B0CPFS24ML- CT ref</t>
+          <t>Camb-SP-Lshape-Multiple Asins- PT</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>B0CPFS24ML</t>
+          <t>B0BFW59TRG</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>242.34</v>
+        <v>0</v>
       </c>
       <c r="E36" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="F36" t="n">
-        <v>5845</v>
+        <v>2</v>
       </c>
       <c r="G36" t="n">
         <v>0</v>
@@ -1444,22 +1444,22 @@
       <c r="A37" t="inlineStr"/>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Camb-SP-Zshape-B0CPFS24ML- PT</t>
+          <t>Camb-SP-Lshape-Multiple Asins- PT</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>B0CPFS24ML</t>
+          <t>B0BFWD6SNF</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>24.47</v>
+        <v>0</v>
       </c>
       <c r="E37" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F37" t="n">
-        <v>119</v>
+        <v>2</v>
       </c>
       <c r="G37" t="n">
         <v>0</v>
@@ -1472,50 +1472,50 @@
       <c r="A38" t="inlineStr"/>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Camb-SP-Zshape-B0CPFS24ML- Phrase</t>
+          <t>Camb-SP-Motorized Desk- B0CPT3Q25C- Exact</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>B0CPFS24ML</t>
+          <t>B0CPT3Q25C</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>221.09</v>
+        <v>1107.41</v>
       </c>
       <c r="E38" t="n">
-        <v>22</v>
+        <v>34</v>
       </c>
       <c r="F38" t="n">
-        <v>1798</v>
+        <v>6461</v>
       </c>
       <c r="G38" t="n">
-        <v>0</v>
+        <v>12712.71</v>
       </c>
       <c r="H38" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr"/>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Camb-SP-Zshape-B0CPFS24ML-PT01</t>
+          <t>Camb-SP-Motorized Desk- B0CPT3Q25C- Phrase/Exact</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>B0CPFS24ML</t>
+          <t>B0CPT3Q25C</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>69.8</v>
+        <v>543.76</v>
       </c>
       <c r="E39" t="n">
-        <v>5</v>
+        <v>18</v>
       </c>
       <c r="F39" t="n">
-        <v>438</v>
+        <v>4854</v>
       </c>
       <c r="G39" t="n">
         <v>0</v>
@@ -1528,7 +1528,7 @@
       <c r="A40" t="inlineStr"/>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Camb-SP-stand desk- B0DQ1NV8D2- PT</t>
+          <t>Camb-SP-Motorized Desk-B0CPT3Q25C - PT01</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -1537,69 +1537,69 @@
         </is>
       </c>
       <c r="D40" t="n">
-        <v>867.75</v>
+        <v>1179.48</v>
       </c>
       <c r="E40" t="n">
-        <v>29</v>
+        <v>54</v>
       </c>
       <c r="F40" t="n">
-        <v>3481</v>
+        <v>7559</v>
       </c>
       <c r="G40" t="n">
-        <v>0</v>
+        <v>12712.71</v>
       </c>
       <c r="H40" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr"/>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Camb-Zshape-Gaming- B0CPFS24ML-Phrase/Exact</t>
+          <t>Camb-SP-Motorized Desk-B0CPT3Q25C- Exact</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>B0CPFS24ML</t>
+          <t>B0CPT3Q25C</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>513.62</v>
+        <v>648.99</v>
       </c>
       <c r="E41" t="n">
-        <v>50</v>
+        <v>30</v>
       </c>
       <c r="F41" t="n">
-        <v>5203</v>
+        <v>7264</v>
       </c>
       <c r="G41" t="n">
-        <v>7202.54</v>
+        <v>0</v>
       </c>
       <c r="H41" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr"/>
       <c r="B42" t="inlineStr">
         <is>
-          <t>SP CT PT_B0CPFS24ML_Gaming</t>
+          <t>Camb-SP-Stand Desk- B0DQ1PKNSP- Broad</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>B0CPFS24ML</t>
+          <t>B0DQ1PKNSP</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>246.57</v>
+        <v>545.9300000000001</v>
       </c>
       <c r="E42" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="F42" t="n">
-        <v>3505</v>
+        <v>13230</v>
       </c>
       <c r="G42" t="n">
         <v>0</v>
@@ -1612,50 +1612,50 @@
       <c r="A43" t="inlineStr"/>
       <c r="B43" t="inlineStr">
         <is>
-          <t>SP KT_B0CPFS24ML_Manual_Gaming</t>
+          <t>Camb-SP-Stand Desk-B0DQ1NV8D2- PT</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>B0CPFS24ML</t>
+          <t>B0DQ1NV8D2</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>385.67</v>
+        <v>261.6</v>
       </c>
       <c r="E43" t="n">
-        <v>27</v>
+        <v>11</v>
       </c>
       <c r="F43" t="n">
-        <v>2280</v>
+        <v>1363</v>
       </c>
       <c r="G43" t="n">
-        <v>0</v>
+        <v>11677.12</v>
       </c>
       <c r="H43" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr"/>
       <c r="B44" t="inlineStr">
         <is>
-          <t>SP_KT_L shape Non Performing Ex</t>
+          <t>Camb-SP-Zshape-B0CPFS24ML- CT ref</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>B0BFVMDJ2K</t>
+          <t>B0CPFS24ML</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>56.82</v>
+        <v>943.2</v>
       </c>
       <c r="E44" t="n">
-        <v>2</v>
+        <v>69</v>
       </c>
       <c r="F44" t="n">
-        <v>877</v>
+        <v>12371</v>
       </c>
       <c r="G44" t="n">
         <v>0</v>
@@ -1668,22 +1668,22 @@
       <c r="A45" t="inlineStr"/>
       <c r="B45" t="inlineStr">
         <is>
-          <t>SP_KT_L shape Non Performing Ex</t>
+          <t>Camb-SP-Zshape-B0CPFS24ML- PT</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>B0BFW59TRG</t>
+          <t>B0CPFS24ML</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>0</v>
+        <v>688.99</v>
       </c>
       <c r="E45" t="n">
-        <v>0</v>
+        <v>51</v>
       </c>
       <c r="F45" t="n">
-        <v>395</v>
+        <v>2641</v>
       </c>
       <c r="G45" t="n">
         <v>0</v>
@@ -1696,50 +1696,50 @@
       <c r="A46" t="inlineStr"/>
       <c r="B46" t="inlineStr">
         <is>
-          <t>SP_KT_L shape Non Performing Ex</t>
+          <t>Camb-SP-Zshape-B0CPFS24ML- Phrase</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>B0BFWD6SNF</t>
+          <t>B0CPFS24ML</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>118.88</v>
+        <v>792.47</v>
       </c>
       <c r="E46" t="n">
-        <v>4</v>
+        <v>74</v>
       </c>
       <c r="F46" t="n">
-        <v>436</v>
+        <v>4607</v>
       </c>
       <c r="G46" t="n">
-        <v>0</v>
+        <v>14066.1</v>
       </c>
       <c r="H46" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr"/>
       <c r="B47" t="inlineStr">
         <is>
-          <t>SP_PT_L shape Non Performing PT</t>
+          <t>Camb-SP-Zshape-B0CPFS24ML-PT01</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>B0BFVMDJ2K</t>
+          <t>B0CPFS24ML</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>204.27</v>
+        <v>488.48</v>
       </c>
       <c r="E47" t="n">
-        <v>8</v>
+        <v>30</v>
       </c>
       <c r="F47" t="n">
-        <v>392</v>
+        <v>2279</v>
       </c>
       <c r="G47" t="n">
         <v>0</v>
@@ -1752,50 +1752,50 @@
       <c r="A48" t="inlineStr"/>
       <c r="B48" t="inlineStr">
         <is>
-          <t>SP_PT_L shape Non Performing PT</t>
+          <t>Camb-SP-stand desk- B0DQ1NV8D2- PT</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>B0BFWD6SNF</t>
+          <t>B0CPT3Q25C</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>141.79</v>
+        <v>2183.64</v>
       </c>
       <c r="E48" t="n">
-        <v>4</v>
+        <v>73</v>
       </c>
       <c r="F48" t="n">
-        <v>500</v>
+        <v>8371</v>
       </c>
       <c r="G48" t="n">
-        <v>0</v>
+        <v>12712.72</v>
       </c>
       <c r="H48" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr"/>
       <c r="B49" t="inlineStr">
         <is>
-          <t>WB- SP- B0DB5VG39T - PT</t>
+          <t>Camb-SP-stand desk- B0DQ1NV8D2- PT</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>B0DB5VG39T</t>
+          <t>B0DQ1NV8D2</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>490.05</v>
+        <v>553.2</v>
       </c>
       <c r="E49" t="n">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="F49" t="n">
-        <v>3994</v>
+        <v>2774</v>
       </c>
       <c r="G49" t="n">
         <v>0</v>
@@ -1808,22 +1808,22 @@
       <c r="A50" t="inlineStr"/>
       <c r="B50" t="inlineStr">
         <is>
-          <t>WB- SP- B0DB5YTQZV-B0DB5VVPSB- PT</t>
+          <t>Camb-Stand Desk- B0DQ1NV8D2/ B0DQ1PKNSP - PT</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>B0DB5YTQZV</t>
+          <t>B0DQ1NV8D2</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>0</v>
+        <v>351.92</v>
       </c>
       <c r="E50" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="F50" t="n">
-        <v>0</v>
+        <v>1882</v>
       </c>
       <c r="G50" t="n">
         <v>0</v>
@@ -1836,22 +1836,22 @@
       <c r="A51" t="inlineStr"/>
       <c r="B51" t="inlineStr">
         <is>
-          <t>WB- SP- B0DP2VVRND - PT</t>
+          <t>Camb-Stand Desk- B0DQ1NV8D2/ B0DQ1PKNSP - PT</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>B0DP2VVRND</t>
+          <t>B0DQ1PKNSP</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>0</v>
+        <v>83.54000000000001</v>
       </c>
       <c r="E51" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F51" t="n">
-        <v>2</v>
+        <v>269</v>
       </c>
       <c r="G51" t="n">
         <v>0</v>
@@ -1864,22 +1864,22 @@
       <c r="A52" t="inlineStr"/>
       <c r="B52" t="inlineStr">
         <is>
-          <t>WB- SP- B0DP2WC5VW - PT</t>
+          <t>Camb-Stand Desk- B0DQ1NV8D2/ B0DQ1PKNSP - Phrase</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>B0DP2WC5VW</t>
+          <t>B0DQ1NV8D2</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>112.99</v>
+        <v>1006.94</v>
       </c>
       <c r="E52" t="n">
-        <v>8</v>
+        <v>38</v>
       </c>
       <c r="F52" t="n">
-        <v>251</v>
+        <v>33958</v>
       </c>
       <c r="G52" t="n">
         <v>0</v>
@@ -1892,78 +1892,78 @@
       <c r="A53" t="inlineStr"/>
       <c r="B53" t="inlineStr">
         <is>
-          <t>WB- SP- B0DP32F346 - PT</t>
+          <t>Camb-Stand Desk- B0DQ1NV8D2/ B0DQ1PKNSP - Phrase</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>B0DP32F346</t>
+          <t>B0DQ1PKNSP</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>412.9100000000001</v>
+        <v>213.79</v>
       </c>
       <c r="E53" t="n">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="F53" t="n">
-        <v>3396</v>
+        <v>2724</v>
       </c>
       <c r="G53" t="n">
-        <v>2626.28</v>
+        <v>0</v>
       </c>
       <c r="H53" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr"/>
       <c r="B54" t="inlineStr">
         <is>
-          <t>WB- SP-B0DB5W4TCP-PT</t>
+          <t>Camb-Zshape-Gaming- B0CPFS24ML-Phrase/Exact</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>B0DB5W4TCP</t>
+          <t>B0CPFS24ML</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>0</v>
+        <v>1926.05</v>
       </c>
       <c r="E54" t="n">
-        <v>0</v>
+        <v>153</v>
       </c>
       <c r="F54" t="n">
-        <v>0</v>
+        <v>19170</v>
       </c>
       <c r="G54" t="n">
-        <v>0</v>
+        <v>14405.08</v>
       </c>
       <c r="H54" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr"/>
       <c r="B55" t="inlineStr">
         <is>
-          <t>WB- SP-B0DP3194QN-PT</t>
+          <t>SP CT PT_B0CPFS24ML_Gaming</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>B0DP3194QN</t>
+          <t>B0CPFS24ML</t>
         </is>
       </c>
       <c r="D55" t="n">
-        <v>385.14</v>
+        <v>246.57</v>
       </c>
       <c r="E55" t="n">
-        <v>13</v>
+        <v>32</v>
       </c>
       <c r="F55" t="n">
-        <v>949</v>
+        <v>3505</v>
       </c>
       <c r="G55" t="n">
         <v>0</v>
@@ -1976,22 +1976,22 @@
       <c r="A56" t="inlineStr"/>
       <c r="B56" t="inlineStr">
         <is>
-          <t>WM- Adj Metal desk- B0DB5W4TCP-SP-KT-Phrase</t>
+          <t>SP KT_B0CPFS24ML_Manual_Gaming</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>B0DB5W4TCP</t>
+          <t>B0CPFS24ML</t>
         </is>
       </c>
       <c r="D56" t="n">
-        <v>356.94</v>
+        <v>385.67</v>
       </c>
       <c r="E56" t="n">
-        <v>10</v>
+        <v>27</v>
       </c>
       <c r="F56" t="n">
-        <v>2037</v>
+        <v>2280</v>
       </c>
       <c r="G56" t="n">
         <v>0</v>
@@ -2004,22 +2004,22 @@
       <c r="A57" t="inlineStr"/>
       <c r="B57" t="inlineStr">
         <is>
-          <t>WM- Heavy-Duty Mechanical- B0DP3194QN - SP-KT-Phrase/BM</t>
+          <t>SP_KT_L shape Non Performing Ex</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>B0DP3194QN</t>
+          <t>B0BFVMDJ2K</t>
         </is>
       </c>
       <c r="D57" t="n">
-        <v>0</v>
+        <v>217.11</v>
       </c>
       <c r="E57" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="F57" t="n">
-        <v>0</v>
+        <v>2520</v>
       </c>
       <c r="G57" t="n">
         <v>0</v>
@@ -2032,50 +2032,50 @@
       <c r="A58" t="inlineStr"/>
       <c r="B58" t="inlineStr">
         <is>
-          <t>WM- Height Adj stand Dual-B0DB5YTQZV-SP-KT-Phrase/BM</t>
+          <t>SP_KT_L shape Non Performing Ex</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>B0DB5YTQZV</t>
+          <t>B0BFW59TRG</t>
         </is>
       </c>
       <c r="D58" t="n">
-        <v>824.95</v>
+        <v>0</v>
       </c>
       <c r="E58" t="n">
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="F58" t="n">
-        <v>4118</v>
+        <v>566</v>
       </c>
       <c r="G58" t="n">
-        <v>5082.2</v>
+        <v>0</v>
       </c>
       <c r="H58" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr"/>
       <c r="B59" t="inlineStr">
         <is>
-          <t>WM- Height Adjustable stand- Dual-B0DB5YTQZV- PT</t>
+          <t>SP_KT_L shape Non Performing Ex</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>B0DB5YTQZV</t>
+          <t>B0BFWD6SNF</t>
         </is>
       </c>
       <c r="D59" t="n">
-        <v>507.47</v>
+        <v>123.9</v>
       </c>
       <c r="E59" t="n">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="F59" t="n">
-        <v>672</v>
+        <v>1390</v>
       </c>
       <c r="G59" t="n">
         <v>0</v>
@@ -2088,22 +2088,22 @@
       <c r="A60" t="inlineStr"/>
       <c r="B60" t="inlineStr">
         <is>
-          <t>WM- SP- Adj Metal desk- Multi Asins- PT</t>
+          <t>SP_PT_L shape Non Performing PT</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>B0DB5W4TCP</t>
+          <t>B0BFVMDJ2K</t>
         </is>
       </c>
       <c r="D60" t="n">
-        <v>420.1</v>
+        <v>1085.58</v>
       </c>
       <c r="E60" t="n">
-        <v>14</v>
+        <v>48</v>
       </c>
       <c r="F60" t="n">
-        <v>1980</v>
+        <v>3026</v>
       </c>
       <c r="G60" t="n">
         <v>0</v>
@@ -2116,175 +2116,175 @@
       <c r="A61" t="inlineStr"/>
       <c r="B61" t="inlineStr">
         <is>
-          <t>WM- SP- Height Adjustable stand- Dual-B0DB5YTQZV- Broad</t>
+          <t>SP_PT_L shape Non Performing PT</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>B0DB5YTQZV</t>
+          <t>B0BFWD6SNF</t>
         </is>
       </c>
       <c r="D61" t="n">
-        <v>412.41</v>
+        <v>575.12</v>
       </c>
       <c r="E61" t="n">
-        <v>33</v>
+        <v>19</v>
       </c>
       <c r="F61" t="n">
-        <v>3992</v>
+        <v>3546</v>
       </c>
       <c r="G61" t="n">
-        <v>1694.07</v>
+        <v>0</v>
       </c>
       <c r="H61" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr"/>
       <c r="B62" t="inlineStr">
         <is>
-          <t>WM- SP- Wall Mounted Stand- B0DP2WC5VW- Broad</t>
+          <t>WB- SP- B0DB5VG39T - CT ref</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>B0DP2WC5VW</t>
+          <t>B0DB5VG39T</t>
         </is>
       </c>
       <c r="D62" t="n">
-        <v>383.96</v>
+        <v>0</v>
       </c>
       <c r="E62" t="n">
-        <v>61</v>
+        <v>0</v>
       </c>
       <c r="F62" t="n">
-        <v>2325</v>
+        <v>0</v>
       </c>
       <c r="G62" t="n">
-        <v>5477.12</v>
+        <v>0</v>
       </c>
       <c r="H62" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr"/>
       <c r="B63" t="inlineStr">
         <is>
-          <t>WM- SP- Wooden Arm- B0DP32F346- PT</t>
+          <t>WB- SP- B0DB5VG39T - PT</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>B0DP32F346</t>
+          <t>B0DB5VG39T</t>
         </is>
       </c>
       <c r="D63" t="n">
-        <v>784.9400000000001</v>
+        <v>1687.55</v>
       </c>
       <c r="E63" t="n">
-        <v>26</v>
+        <v>94</v>
       </c>
       <c r="F63" t="n">
-        <v>3056</v>
+        <v>12108</v>
       </c>
       <c r="G63" t="n">
-        <v>0</v>
+        <v>2329.66</v>
       </c>
       <c r="H63" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr"/>
       <c r="B64" t="inlineStr">
         <is>
-          <t>WM- SP-Wall Mounted Stand- B0DP2WC5VW- Exact &amp; Phrase</t>
+          <t>WB- SP- B0DB5YTQZV-B0DB5VVPSB- PT</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>B0DP2WC5VW</t>
+          <t>B0DB5VVPSB</t>
         </is>
       </c>
       <c r="D64" t="n">
-        <v>1148.29</v>
+        <v>326.34</v>
       </c>
       <c r="E64" t="n">
-        <v>69</v>
+        <v>16</v>
       </c>
       <c r="F64" t="n">
-        <v>2866</v>
+        <v>2071</v>
       </c>
       <c r="G64" t="n">
-        <v>8487.280000000001</v>
+        <v>0</v>
       </c>
       <c r="H64" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr"/>
       <c r="B65" t="inlineStr">
         <is>
-          <t>WM- Wall Mounted Stand- B0DP2WC5VW- PT</t>
+          <t>WB- SP- B0DB5YTQZV-B0DB5VVPSB- PT</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>B0DP2WC5VW</t>
+          <t>B0DB5YTQZV</t>
         </is>
       </c>
       <c r="D65" t="n">
-        <v>685.29</v>
+        <v>1233.56</v>
       </c>
       <c r="E65" t="n">
-        <v>39</v>
+        <v>58</v>
       </c>
       <c r="F65" t="n">
-        <v>1287</v>
+        <v>3308</v>
       </c>
       <c r="G65" t="n">
-        <v>13931.36</v>
+        <v>1694.07</v>
       </c>
       <c r="H65" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr"/>
       <c r="B66" t="inlineStr">
         <is>
-          <t>WM- Wall Mounted Stand- B0DP2WC5VW- Phrase &amp; exact</t>
+          <t>WB- SP- B0DP2VVRND - PT</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>B0DP2WC5VW</t>
+          <t>B0DP2VVRND</t>
         </is>
       </c>
       <c r="D66" t="n">
-        <v>1744.44</v>
+        <v>510.75</v>
       </c>
       <c r="E66" t="n">
-        <v>77</v>
+        <v>27</v>
       </c>
       <c r="F66" t="n">
-        <v>9528</v>
+        <v>996</v>
       </c>
       <c r="G66" t="n">
-        <v>11352.53</v>
+        <v>5387.28</v>
       </c>
       <c r="H66" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr"/>
       <c r="B67" t="inlineStr">
         <is>
-          <t>WM- Wall Mounted Stand- B0DP2WC5VW- SP-KT-Phrase/BM</t>
+          <t>WB- SP- B0DP2WC5VW - PT</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -2293,13 +2293,13 @@
         </is>
       </c>
       <c r="D67" t="n">
-        <v>0</v>
+        <v>541.51</v>
       </c>
       <c r="E67" t="n">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="F67" t="n">
-        <v>0</v>
+        <v>612</v>
       </c>
       <c r="G67" t="n">
         <v>0</v>
@@ -2312,50 +2312,50 @@
       <c r="A68" t="inlineStr"/>
       <c r="B68" t="inlineStr">
         <is>
-          <t>WM-Gas Spring MA- B0DB5VG39T-SP-KT-Phrase/BM</t>
+          <t>WB- SP- B0DP32F346 - PT</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>B0DB5VG39T</t>
+          <t>B0DP32F346</t>
         </is>
       </c>
       <c r="D68" t="n">
-        <v>572.27</v>
+        <v>1428.23</v>
       </c>
       <c r="E68" t="n">
-        <v>22</v>
+        <v>61</v>
       </c>
       <c r="F68" t="n">
-        <v>2680</v>
+        <v>10719</v>
       </c>
       <c r="G68" t="n">
-        <v>0</v>
+        <v>5252.55</v>
       </c>
       <c r="H68" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr"/>
       <c r="B69" t="inlineStr">
         <is>
-          <t>WM-Gas Spring MA- Dual - B0DB5VVPSB-SP-KT-Phrase/BM</t>
+          <t>WB- SP-B0DB5W4TCP-PT</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>B0DB5VVPSB</t>
+          <t>B0DB5W4TCP</t>
         </is>
       </c>
       <c r="D69" t="n">
-        <v>0</v>
+        <v>286.72</v>
       </c>
       <c r="E69" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="F69" t="n">
-        <v>0</v>
+        <v>1732</v>
       </c>
       <c r="G69" t="n">
         <v>0</v>
@@ -2368,35 +2368,35 @@
       <c r="A70" t="inlineStr"/>
       <c r="B70" t="inlineStr">
         <is>
-          <t>WM-SP- Monitor Arms- Multi Asins - AT</t>
+          <t>WB- SP-B0DP3194QN-PT</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>B0DB5VVPSB</t>
+          <t>B0DP3194QN</t>
         </is>
       </c>
       <c r="D70" t="n">
-        <v>298.38</v>
+        <v>1207.5</v>
       </c>
       <c r="E70" t="n">
-        <v>15</v>
+        <v>44</v>
       </c>
       <c r="F70" t="n">
-        <v>914</v>
+        <v>3646</v>
       </c>
       <c r="G70" t="n">
-        <v>0</v>
+        <v>2965.26</v>
       </c>
       <c r="H70" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr"/>
       <c r="B71" t="inlineStr">
         <is>
-          <t>WM-SP- Monitor Arms- Multi Asins - AT</t>
+          <t>WM- Adj Metal desk- B0DB5W4TCP-SP-KT-Phrase</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -2405,13 +2405,13 @@
         </is>
       </c>
       <c r="D71" t="n">
-        <v>212.01</v>
+        <v>1089.28</v>
       </c>
       <c r="E71" t="n">
-        <v>9</v>
+        <v>38</v>
       </c>
       <c r="F71" t="n">
-        <v>985</v>
+        <v>7781</v>
       </c>
       <c r="G71" t="n">
         <v>0</v>
@@ -2424,22 +2424,22 @@
       <c r="A72" t="inlineStr"/>
       <c r="B72" t="inlineStr">
         <is>
-          <t>WM-SP- Monitor Arms- Multi Asins - AT</t>
+          <t>WM- Heavy-Duty Mechanical- B0DP3194QN - SP-KT-Phrase/BM</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>B0DP2WC5VW</t>
+          <t>B0DP3194QN</t>
         </is>
       </c>
       <c r="D72" t="n">
-        <v>197.5</v>
+        <v>622.13</v>
       </c>
       <c r="E72" t="n">
-        <v>11</v>
+        <v>30</v>
       </c>
       <c r="F72" t="n">
-        <v>1555</v>
+        <v>23498</v>
       </c>
       <c r="G72" t="n">
         <v>0</v>
@@ -2452,22 +2452,22 @@
       <c r="A73" t="inlineStr"/>
       <c r="B73" t="inlineStr">
         <is>
-          <t>WM-SP- Monitor Arms- Multi Asins - AT</t>
+          <t>WM- Height Adj stand - B0DP2VVRND-SP-KT-Phrase</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>B0DP2Z5DQ9</t>
+          <t>B0DP2VVRND</t>
         </is>
       </c>
       <c r="D73" t="n">
-        <v>75.86</v>
+        <v>902.6800000000001</v>
       </c>
       <c r="E73" t="n">
-        <v>4</v>
+        <v>36</v>
       </c>
       <c r="F73" t="n">
-        <v>595</v>
+        <v>9205</v>
       </c>
       <c r="G73" t="n">
         <v>0</v>
@@ -2480,106 +2480,106 @@
       <c r="A74" t="inlineStr"/>
       <c r="B74" t="inlineStr">
         <is>
-          <t>WM-SP- Monitor Arms- Multi Asins - AT</t>
+          <t>WM- Height Adj stand Dual-B0DB5YTQZV-SP-KT-Phrase/BM</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>B0DP32F346</t>
+          <t>B0DB5YTQZV</t>
         </is>
       </c>
       <c r="D74" t="n">
-        <v>48.66</v>
+        <v>3619.94</v>
       </c>
       <c r="E74" t="n">
+        <v>194</v>
+      </c>
+      <c r="F74" t="n">
+        <v>25250</v>
+      </c>
+      <c r="G74" t="n">
+        <v>5082.2</v>
+      </c>
+      <c r="H74" t="n">
         <v>3</v>
-      </c>
-      <c r="F74" t="n">
-        <v>1063</v>
-      </c>
-      <c r="G74" t="n">
-        <v>0</v>
-      </c>
-      <c r="H74" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr"/>
       <c r="B75" t="inlineStr">
         <is>
-          <t>WM-SP- Monitor Arms- Multi Asins - CT</t>
+          <t>WM- Height Adjustable stand- Dual-B0DB5YTQZV- PT</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>B0DB5W4TCP</t>
+          <t>B0DB5YTQZV</t>
         </is>
       </c>
       <c r="D75" t="n">
-        <v>180.43</v>
+        <v>1363.73</v>
       </c>
       <c r="E75" t="n">
-        <v>9</v>
+        <v>38</v>
       </c>
       <c r="F75" t="n">
-        <v>944</v>
+        <v>1653</v>
       </c>
       <c r="G75" t="n">
-        <v>1355.08</v>
+        <v>5922.04</v>
       </c>
       <c r="H75" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr"/>
       <c r="B76" t="inlineStr">
         <is>
-          <t>WM-SP- Monitor Arms- Multi Asins - CT</t>
+          <t>WM- SP- Adj Metal desk- Multi Asins- PT</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>B0DB5YTQZV</t>
+          <t>B0DB5W4TCP</t>
         </is>
       </c>
       <c r="D76" t="n">
-        <v>140.97</v>
+        <v>1447.91</v>
       </c>
       <c r="E76" t="n">
-        <v>7</v>
+        <v>56</v>
       </c>
       <c r="F76" t="n">
-        <v>1478</v>
+        <v>7686</v>
       </c>
       <c r="G76" t="n">
-        <v>0</v>
+        <v>1355.08</v>
       </c>
       <c r="H76" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr"/>
       <c r="B77" t="inlineStr">
         <is>
-          <t>WM-SP- Monitor Arms- Multi Asins - CT</t>
+          <t>WM- SP- Adj Metal desk- Multi Asins- PT</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>B0DP2WC5VW</t>
+          <t>B0DB5YTQZV</t>
         </is>
       </c>
       <c r="D77" t="n">
-        <v>131.61</v>
+        <v>613.95</v>
       </c>
       <c r="E77" t="n">
-        <v>6</v>
+        <v>25</v>
       </c>
       <c r="F77" t="n">
-        <v>1781</v>
+        <v>2167</v>
       </c>
       <c r="G77" t="n">
         <v>0</v>
@@ -2592,91 +2592,91 @@
       <c r="A78" t="inlineStr"/>
       <c r="B78" t="inlineStr">
         <is>
-          <t>WM-SP- Monitor Arms- Multi Asins - CT</t>
+          <t>WM- SP- Height Adjustable stand- Dual-B0DB5YTQZV- Broad</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>B0DP2Z5DQ9</t>
+          <t>B0DB5YTQZV</t>
         </is>
       </c>
       <c r="D78" t="n">
-        <v>163.39</v>
+        <v>906.83</v>
       </c>
       <c r="E78" t="n">
-        <v>8</v>
+        <v>78</v>
       </c>
       <c r="F78" t="n">
-        <v>1352</v>
+        <v>9390</v>
       </c>
       <c r="G78" t="n">
-        <v>0</v>
+        <v>3388.14</v>
       </c>
       <c r="H78" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr"/>
       <c r="B79" t="inlineStr">
         <is>
-          <t>WM-SP- Monitor Arms- Multi Asins - CT</t>
+          <t>WM- SP- Wall Mounted Stand- B0DP2WC5VW- Broad</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>B0DP32F346</t>
+          <t>B0DP2WC5VW</t>
         </is>
       </c>
       <c r="D79" t="n">
-        <v>49.57</v>
+        <v>645.58</v>
       </c>
       <c r="E79" t="n">
-        <v>3</v>
+        <v>114</v>
       </c>
       <c r="F79" t="n">
-        <v>327</v>
+        <v>4347</v>
       </c>
       <c r="G79" t="n">
-        <v>0</v>
+        <v>10729.66</v>
       </c>
       <c r="H79" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr"/>
       <c r="B80" t="inlineStr">
         <is>
-          <t>WM-SP- Monitor Arms- Multi Asins - exact</t>
+          <t>WM- SP- Wooden Arm- B0DP32F346- PT</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>B0DB5W4TCP</t>
+          <t>B0DP32F346</t>
         </is>
       </c>
       <c r="D80" t="n">
-        <v>185.09</v>
+        <v>2234.79</v>
       </c>
       <c r="E80" t="n">
-        <v>12</v>
+        <v>76</v>
       </c>
       <c r="F80" t="n">
-        <v>6746</v>
+        <v>8428</v>
       </c>
       <c r="G80" t="n">
-        <v>0</v>
+        <v>7582.200000000001</v>
       </c>
       <c r="H80" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr"/>
       <c r="B81" t="inlineStr">
         <is>
-          <t>WM-SP- Monitor Arms- Multi Asins - exact</t>
+          <t>WM- SP-Wall Mounted Stand- B0DP2WC5VW- Exact &amp; Phrase</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
@@ -2685,138 +2685,138 @@
         </is>
       </c>
       <c r="D81" t="n">
-        <v>587.3</v>
+        <v>3734.61</v>
       </c>
       <c r="E81" t="n">
-        <v>36</v>
+        <v>211</v>
       </c>
       <c r="F81" t="n">
-        <v>17577</v>
+        <v>10800</v>
       </c>
       <c r="G81" t="n">
-        <v>2626.27</v>
+        <v>22277.1</v>
       </c>
       <c r="H81" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr"/>
       <c r="B82" t="inlineStr">
         <is>
-          <t>WM-SP- Premium Monitor Arms- Multi Asins -Phrase</t>
+          <t>WM- Wall Mounted Stand- B0DP2WC5VW- PT</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>B0DP3194QN</t>
+          <t>B0DP2WC5VW</t>
         </is>
       </c>
       <c r="D82" t="n">
-        <v>0</v>
+        <v>2349.88</v>
       </c>
       <c r="E82" t="n">
-        <v>0</v>
+        <v>131</v>
       </c>
       <c r="F82" t="n">
-        <v>0</v>
+        <v>5450</v>
       </c>
       <c r="G82" t="n">
-        <v>0</v>
+        <v>5422.030000000001</v>
       </c>
       <c r="H82" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr"/>
       <c r="B83" t="inlineStr">
         <is>
-          <t>WM-SP- Premium Monitor Arms- Multi Asins -Phrase</t>
+          <t>WM- Wall Mounted Stand- B0DP2WC5VW- Phrase &amp; exact</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>B0DP32F346</t>
+          <t>B0DP2WC5VW</t>
         </is>
       </c>
       <c r="D83" t="n">
-        <v>716.2</v>
+        <v>6062.22</v>
       </c>
       <c r="E83" t="n">
-        <v>34</v>
+        <v>278</v>
       </c>
       <c r="F83" t="n">
-        <v>15278</v>
+        <v>32234</v>
       </c>
       <c r="G83" t="n">
-        <v>5422.030000000001</v>
+        <v>19400.83</v>
       </c>
       <c r="H83" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr"/>
       <c r="B84" t="inlineStr">
         <is>
-          <t>WM-SP-Gas Spring -Multi Asins- Phrase &amp; Exact</t>
+          <t>WM- Wall Mounted Stand- B0DP2WC5VW- SP-KT-Phrase/BM</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>B0DB5VG39T</t>
+          <t>B0DP2WC5VW</t>
         </is>
       </c>
       <c r="D84" t="n">
-        <v>787.4400000000001</v>
+        <v>1656.76</v>
       </c>
       <c r="E84" t="n">
-        <v>37</v>
+        <v>101</v>
       </c>
       <c r="F84" t="n">
-        <v>14645</v>
+        <v>24901</v>
       </c>
       <c r="G84" t="n">
-        <v>0</v>
+        <v>2626.27</v>
       </c>
       <c r="H84" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr"/>
       <c r="B85" t="inlineStr">
         <is>
-          <t>WM-SP-Gas Spring -Multi Asins- Phrase &amp; Exact</t>
+          <t>WM- Wooden Arm- B0DP32F346-SP-KT-Phrase</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>B0DB5VVPSB</t>
+          <t>B0DP32F346</t>
         </is>
       </c>
       <c r="D85" t="n">
-        <v>181.76</v>
+        <v>690.05</v>
       </c>
       <c r="E85" t="n">
-        <v>7</v>
+        <v>27</v>
       </c>
       <c r="F85" t="n">
-        <v>1253</v>
+        <v>15147</v>
       </c>
       <c r="G85" t="n">
-        <v>0</v>
+        <v>2626.27</v>
       </c>
       <c r="H85" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr"/>
       <c r="B86" t="inlineStr">
         <is>
-          <t>WM-SP-Gas Spring MA- B0DB5VG39T- Broad</t>
+          <t>WM-Gas Spring MA- B0DB5VG39T-SP-KT-Phrase/BM</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
@@ -2825,41 +2825,41 @@
         </is>
       </c>
       <c r="D86" t="n">
-        <v>582.28</v>
+        <v>2516.66</v>
       </c>
       <c r="E86" t="n">
-        <v>42</v>
+        <v>94</v>
       </c>
       <c r="F86" t="n">
-        <v>6109</v>
+        <v>8975</v>
       </c>
       <c r="G86" t="n">
-        <v>4659.32</v>
+        <v>6988.98</v>
       </c>
       <c r="H86" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr"/>
       <c r="B87" t="inlineStr">
         <is>
-          <t>WM-SP-Gas Spring MA- B0DB5VG39T- Exact &amp; Phrase</t>
+          <t>WM-Gas Spring MA- Dual - B0DB5VVPSB-SP-KT-Phrase/BM</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>B0DB5VG39T</t>
+          <t>B0DB5VVPSB</t>
         </is>
       </c>
       <c r="D87" t="n">
-        <v>0</v>
+        <v>976.26</v>
       </c>
       <c r="E87" t="n">
-        <v>0</v>
+        <v>62</v>
       </c>
       <c r="F87" t="n">
-        <v>0</v>
+        <v>12322</v>
       </c>
       <c r="G87" t="n">
         <v>0</v>
@@ -2872,7 +2872,7 @@
       <c r="A88" t="inlineStr"/>
       <c r="B88" t="inlineStr">
         <is>
-          <t>WM-SP-Gas Spring MA- B0DB5VG39T/B0DB5VVPSB- PT</t>
+          <t>WM-SP- Monitor Arms- Multi Asins - AT</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
@@ -2881,13 +2881,13 @@
         </is>
       </c>
       <c r="D88" t="n">
-        <v>620.51</v>
+        <v>312.29</v>
       </c>
       <c r="E88" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="F88" t="n">
-        <v>1775</v>
+        <v>7788</v>
       </c>
       <c r="G88" t="n">
         <v>0</v>
@@ -2900,7 +2900,7 @@
       <c r="A89" t="inlineStr"/>
       <c r="B89" t="inlineStr">
         <is>
-          <t>WM-SP-Gas Spring MA- B0DB5VG39T/B0DB5VVPSB- PT</t>
+          <t>WM-SP- Monitor Arms- Multi Asins - AT</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
@@ -2909,13 +2909,13 @@
         </is>
       </c>
       <c r="D89" t="n">
-        <v>192.88</v>
+        <v>797.27</v>
       </c>
       <c r="E89" t="n">
-        <v>7</v>
+        <v>39</v>
       </c>
       <c r="F89" t="n">
-        <v>418</v>
+        <v>3575</v>
       </c>
       <c r="G89" t="n">
         <v>0</v>
@@ -2928,22 +2928,22 @@
       <c r="A90" t="inlineStr"/>
       <c r="B90" t="inlineStr">
         <is>
-          <t>WM-SP-Monitor Arms- Branded</t>
+          <t>WM-SP- Monitor Arms- Multi Asins - AT</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>B0DB5VG39T</t>
+          <t>B0DB5W4TCP</t>
         </is>
       </c>
       <c r="D90" t="n">
-        <v>10.64</v>
+        <v>432.73</v>
       </c>
       <c r="E90" t="n">
-        <v>1</v>
+        <v>21</v>
       </c>
       <c r="F90" t="n">
-        <v>182</v>
+        <v>3973</v>
       </c>
       <c r="G90" t="n">
         <v>0</v>
@@ -2956,12 +2956,12 @@
       <c r="A91" t="inlineStr"/>
       <c r="B91" t="inlineStr">
         <is>
-          <t>WM-SP-Monitor Arms- Branded</t>
+          <t>WM-SP- Monitor Arms- Multi Asins - AT</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>B0DB5VVPSB</t>
+          <t>B0DB5YTQZV</t>
         </is>
       </c>
       <c r="D91" t="n">
@@ -2971,7 +2971,7 @@
         <v>0</v>
       </c>
       <c r="F91" t="n">
-        <v>162</v>
+        <v>0</v>
       </c>
       <c r="G91" t="n">
         <v>0</v>
@@ -2984,22 +2984,22 @@
       <c r="A92" t="inlineStr"/>
       <c r="B92" t="inlineStr">
         <is>
-          <t>WM-SP-Monitor Arms- Branded</t>
+          <t>WM-SP- Monitor Arms- Multi Asins - AT</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>B0DB5W4TCP</t>
+          <t>B0DP2WC5VW</t>
         </is>
       </c>
       <c r="D92" t="n">
-        <v>0</v>
+        <v>733.4200000000001</v>
       </c>
       <c r="E92" t="n">
-        <v>0</v>
+        <v>46</v>
       </c>
       <c r="F92" t="n">
-        <v>367</v>
+        <v>13786</v>
       </c>
       <c r="G92" t="n">
         <v>0</v>
@@ -3012,22 +3012,22 @@
       <c r="A93" t="inlineStr"/>
       <c r="B93" t="inlineStr">
         <is>
-          <t>WM-SP-Monitor Arms- Branded</t>
+          <t>WM-SP- Monitor Arms- Multi Asins - AT</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>B0DB5YTQZV</t>
+          <t>B0DP2Z5DQ9</t>
         </is>
       </c>
       <c r="D93" t="n">
-        <v>0</v>
+        <v>136.04</v>
       </c>
       <c r="E93" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="F93" t="n">
-        <v>144</v>
+        <v>1849</v>
       </c>
       <c r="G93" t="n">
         <v>0</v>
@@ -3040,22 +3040,22 @@
       <c r="A94" t="inlineStr"/>
       <c r="B94" t="inlineStr">
         <is>
-          <t>WM-SP-Monitor Arms- Branded</t>
+          <t>WM-SP- Monitor Arms- Multi Asins - AT</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>B0DP2Z5DQ9</t>
+          <t>B0DP32F346</t>
         </is>
       </c>
       <c r="D94" t="n">
-        <v>0</v>
+        <v>121.44</v>
       </c>
       <c r="E94" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="F94" t="n">
-        <v>532</v>
+        <v>5615</v>
       </c>
       <c r="G94" t="n">
         <v>0</v>
@@ -3068,50 +3068,50 @@
       <c r="A95" t="inlineStr"/>
       <c r="B95" t="inlineStr">
         <is>
-          <t>WM-SP-Monitor Arms- Branded</t>
+          <t>WM-SP- Monitor Arms- Multi Asins - CT</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>B0DP32F346</t>
+          <t>B0DB5W4TCP</t>
         </is>
       </c>
       <c r="D95" t="n">
-        <v>10</v>
+        <v>285.01</v>
       </c>
       <c r="E95" t="n">
+        <v>14</v>
+      </c>
+      <c r="F95" t="n">
+        <v>1903</v>
+      </c>
+      <c r="G95" t="n">
+        <v>1355.08</v>
+      </c>
+      <c r="H95" t="n">
         <v>1</v>
-      </c>
-      <c r="F95" t="n">
-        <v>848</v>
-      </c>
-      <c r="G95" t="n">
-        <v>0</v>
-      </c>
-      <c r="H95" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr"/>
       <c r="B96" t="inlineStr">
         <is>
-          <t>WM-SP-Monitor Arms- Defensive</t>
+          <t>WM-SP- Monitor Arms- Multi Asins - CT</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>B0DB5VG39T</t>
+          <t>B0DB5YTQZV</t>
         </is>
       </c>
       <c r="D96" t="n">
-        <v>39.66</v>
+        <v>320.24</v>
       </c>
       <c r="E96" t="n">
-        <v>3</v>
+        <v>16</v>
       </c>
       <c r="F96" t="n">
-        <v>342</v>
+        <v>3288</v>
       </c>
       <c r="G96" t="n">
         <v>0</v>
@@ -3124,50 +3124,50 @@
       <c r="A97" t="inlineStr"/>
       <c r="B97" t="inlineStr">
         <is>
-          <t>WM-SP-Monitor Arms- Defensive</t>
+          <t>WM-SP- Monitor Arms- Multi Asins - CT</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>B0DB5VVPSB</t>
+          <t>B0DP2WC5VW</t>
         </is>
       </c>
       <c r="D97" t="n">
-        <v>105</v>
+        <v>557.08</v>
       </c>
       <c r="E97" t="n">
-        <v>8</v>
+        <v>30</v>
       </c>
       <c r="F97" t="n">
-        <v>796</v>
+        <v>5829</v>
       </c>
       <c r="G97" t="n">
-        <v>3812.72</v>
+        <v>0</v>
       </c>
       <c r="H97" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr"/>
       <c r="B98" t="inlineStr">
         <is>
-          <t>WM-SP-Monitor Arms- Defensive</t>
+          <t>WM-SP- Monitor Arms- Multi Asins - CT</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>B0DB5W4TCP</t>
+          <t>B0DP2Z5DQ9</t>
         </is>
       </c>
       <c r="D98" t="n">
-        <v>11.55</v>
+        <v>291.08</v>
       </c>
       <c r="E98" t="n">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="F98" t="n">
-        <v>337</v>
+        <v>1997</v>
       </c>
       <c r="G98" t="n">
         <v>0</v>
@@ -3180,22 +3180,22 @@
       <c r="A99" t="inlineStr"/>
       <c r="B99" t="inlineStr">
         <is>
-          <t>WM-SP-Monitor Arms- Defensive</t>
+          <t>WM-SP- Monitor Arms- Multi Asins - CT</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>B0DB5YTQZV</t>
+          <t>B0DP32F346</t>
         </is>
       </c>
       <c r="D99" t="n">
-        <v>111.53</v>
+        <v>197.49</v>
       </c>
       <c r="E99" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="F99" t="n">
-        <v>1770</v>
+        <v>1176</v>
       </c>
       <c r="G99" t="n">
         <v>0</v>
@@ -3208,25 +3208,25 @@
       <c r="A100" t="inlineStr"/>
       <c r="B100" t="inlineStr">
         <is>
-          <t>WM-SP-Monitor Arms- Defensive</t>
+          <t>WM-SP- Monitor Arms- Multi Asins - exact</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>B0DP2Z5DQ9</t>
+          <t>B0DB5W4TCP</t>
         </is>
       </c>
       <c r="D100" t="n">
-        <v>125.95</v>
+        <v>946.8</v>
       </c>
       <c r="E100" t="n">
-        <v>12</v>
+        <v>51</v>
       </c>
       <c r="F100" t="n">
-        <v>1035</v>
+        <v>35447</v>
       </c>
       <c r="G100" t="n">
-        <v>2514.41</v>
+        <v>1355.08</v>
       </c>
       <c r="H100" t="n">
         <v>1</v>
@@ -3236,109 +3236,109 @@
       <c r="A101" t="inlineStr"/>
       <c r="B101" t="inlineStr">
         <is>
-          <t>WM-SP-Monitor Arms- Defensive</t>
+          <t>WM-SP- Monitor Arms- Multi Asins - exact</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>B0DP32F346</t>
+          <t>B0DP2WC5VW</t>
         </is>
       </c>
       <c r="D101" t="n">
-        <v>38.99</v>
+        <v>2012.71</v>
       </c>
       <c r="E101" t="n">
-        <v>3</v>
+        <v>111</v>
       </c>
       <c r="F101" t="n">
-        <v>243</v>
+        <v>47805</v>
       </c>
       <c r="G101" t="n">
-        <v>0</v>
+        <v>5252.54</v>
       </c>
       <c r="H101" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr"/>
       <c r="B102" t="inlineStr">
         <is>
-          <t>WM-SP-Monitor Stand-B0DP2Z5DQ9 - PT</t>
+          <t>WM-SP- Premium Monitor Arms- Multi Asins -Phrase</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>B0DP2Z5DQ9</t>
+          <t>B0DP3194QN</t>
         </is>
       </c>
       <c r="D102" t="n">
-        <v>350.04</v>
+        <v>81.05</v>
       </c>
       <c r="E102" t="n">
-        <v>28</v>
+        <v>3</v>
       </c>
       <c r="F102" t="n">
-        <v>1945</v>
+        <v>571</v>
       </c>
       <c r="G102" t="n">
-        <v>2514.41</v>
+        <v>0</v>
       </c>
       <c r="H102" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr"/>
       <c r="B103" t="inlineStr">
         <is>
-          <t>WM-SP-Monitor Stand-B0DP2Z5DQ9 - Phrase</t>
+          <t>WM-SP- Premium Monitor Arms- Multi Asins -Phrase</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>B0DP2Z5DQ9</t>
+          <t>B0DP32F346</t>
         </is>
       </c>
       <c r="D103" t="n">
-        <v>587.6900000000001</v>
+        <v>2078.3</v>
       </c>
       <c r="E103" t="n">
-        <v>41</v>
+        <v>96</v>
       </c>
       <c r="F103" t="n">
-        <v>3530</v>
+        <v>33533</v>
       </c>
       <c r="G103" t="n">
-        <v>2514.4</v>
+        <v>13004.23</v>
       </c>
       <c r="H103" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr"/>
       <c r="B104" t="inlineStr">
         <is>
-          <t>WM-SP-Monitor Stand-B0DP2Z5DQ9 -Phrase</t>
+          <t>WM-SP-Gas Spring -Multi Asins- Phrase &amp; Exact</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>B0DP2Z5DQ9</t>
+          <t>B0DB5VG39T</t>
         </is>
       </c>
       <c r="D104" t="n">
-        <v>524.45</v>
+        <v>2666.81</v>
       </c>
       <c r="E104" t="n">
-        <v>25</v>
+        <v>124</v>
       </c>
       <c r="F104" t="n">
-        <v>5434</v>
+        <v>67250</v>
       </c>
       <c r="G104" t="n">
-        <v>15508.48</v>
+        <v>9532.200000000001</v>
       </c>
       <c r="H104" t="n">
         <v>2</v>
@@ -3348,134 +3348,134 @@
       <c r="A105" t="inlineStr"/>
       <c r="B105" t="inlineStr">
         <is>
-          <t>WM-SP-POS stand- Multi - PT</t>
+          <t>WM-SP-Gas Spring -Multi Asins- Phrase &amp; Exact</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>B0FN4FPJ83</t>
+          <t>B0DB5VVPSB</t>
         </is>
       </c>
       <c r="D105" t="n">
-        <v>0</v>
+        <v>339.67</v>
       </c>
       <c r="E105" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="F105" t="n">
-        <v>3</v>
+        <v>3186</v>
       </c>
       <c r="G105" t="n">
-        <v>0</v>
+        <v>3812.71</v>
       </c>
       <c r="H105" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr"/>
       <c r="B106" t="inlineStr">
         <is>
-          <t>WM-SP-TV Brackets- Multi Asins- CT</t>
+          <t>WM-SP-Gas Spring MA- B0DB5VG39T- Broad</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>B0FN4D3C89</t>
+          <t>B0DB5VG39T</t>
         </is>
       </c>
       <c r="D106" t="n">
-        <v>245.74</v>
+        <v>2198.05</v>
       </c>
       <c r="E106" t="n">
-        <v>14</v>
+        <v>160</v>
       </c>
       <c r="F106" t="n">
-        <v>1122</v>
+        <v>23021</v>
       </c>
       <c r="G106" t="n">
-        <v>0</v>
+        <v>15629.65</v>
       </c>
       <c r="H106" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr"/>
       <c r="B107" t="inlineStr">
         <is>
-          <t>WM-SP-TV Brackets- Multi Asins- CT</t>
+          <t>WM-SP-Gas Spring MA- B0DB5VG39T- Exact &amp; Phrase</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>B0FN4DSQ6P</t>
+          <t>B0DB5VG39T</t>
         </is>
       </c>
       <c r="D107" t="n">
-        <v>42.18</v>
+        <v>1055.61</v>
       </c>
       <c r="E107" t="n">
-        <v>2</v>
+        <v>31</v>
       </c>
       <c r="F107" t="n">
-        <v>540</v>
+        <v>4475</v>
       </c>
       <c r="G107" t="n">
-        <v>0</v>
+        <v>4955.93</v>
       </c>
       <c r="H107" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr"/>
       <c r="B108" t="inlineStr">
         <is>
-          <t>WM-SP-TV Brackets- Multi Asins- CT</t>
+          <t>WM-SP-Gas Spring MA- B0DB5VG39T/B0DB5VVPSB- PT</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>B0FN4HDM6Z</t>
+          <t>B0DB5VG39T</t>
         </is>
       </c>
       <c r="D108" t="n">
-        <v>0</v>
+        <v>1676.92</v>
       </c>
       <c r="E108" t="n">
-        <v>0</v>
+        <v>52</v>
       </c>
       <c r="F108" t="n">
-        <v>369</v>
+        <v>5400</v>
       </c>
       <c r="G108" t="n">
-        <v>0</v>
+        <v>5083.05</v>
       </c>
       <c r="H108" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr"/>
       <c r="B109" t="inlineStr">
         <is>
-          <t>WM-SP-TV Brackets- Multi Asins- Exact</t>
+          <t>WM-SP-Gas Spring MA- B0DB5VG39T/B0DB5VVPSB- PT</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>B0FHVWHQHR</t>
+          <t>B0DB5VVPSB</t>
         </is>
       </c>
       <c r="D109" t="n">
-        <v>0</v>
+        <v>792.1799999999999</v>
       </c>
       <c r="E109" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="F109" t="n">
-        <v>127</v>
+        <v>2005</v>
       </c>
       <c r="G109" t="n">
         <v>0</v>
@@ -3488,78 +3488,78 @@
       <c r="A110" t="inlineStr"/>
       <c r="B110" t="inlineStr">
         <is>
-          <t>WM-SP-TV Brackets- Multi Asins- Exact</t>
+          <t>WM-SP-Monitor Arms- Branded</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>B0FN4D3C89</t>
+          <t>B0DB5VG39T</t>
         </is>
       </c>
       <c r="D110" t="n">
-        <v>243.75</v>
+        <v>10.64</v>
       </c>
       <c r="E110" t="n">
-        <v>31</v>
+        <v>1</v>
       </c>
       <c r="F110" t="n">
-        <v>5775</v>
+        <v>233</v>
       </c>
       <c r="G110" t="n">
-        <v>854.24</v>
+        <v>0</v>
       </c>
       <c r="H110" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr"/>
       <c r="B111" t="inlineStr">
         <is>
-          <t>WM-SP-TV Brackets- Multi Asins- Exact</t>
+          <t>WM-SP-Monitor Arms- Branded</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>B0FN4DSQ6P</t>
+          <t>B0DB5VVPSB</t>
         </is>
       </c>
       <c r="D111" t="n">
-        <v>64.23</v>
+        <v>10.49</v>
       </c>
       <c r="E111" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="F111" t="n">
-        <v>941</v>
+        <v>201</v>
       </c>
       <c r="G111" t="n">
-        <v>1708.48</v>
+        <v>0</v>
       </c>
       <c r="H111" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr"/>
       <c r="B112" t="inlineStr">
         <is>
-          <t>WM-SP-TV Brackets- Multi Asins- PT</t>
+          <t>WM-SP-Monitor Arms- Branded</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>B0FHVWHQHR</t>
+          <t>B0DB5W4TCP</t>
         </is>
       </c>
       <c r="D112" t="n">
-        <v>28.42</v>
+        <v>0</v>
       </c>
       <c r="E112" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F112" t="n">
-        <v>161</v>
+        <v>498</v>
       </c>
       <c r="G112" t="n">
         <v>0</v>
@@ -3572,50 +3572,50 @@
       <c r="A113" t="inlineStr"/>
       <c r="B113" t="inlineStr">
         <is>
-          <t>WM-SP-TV Brackets- Multi Asins- PT</t>
+          <t>WM-SP-Monitor Arms- Branded</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>B0FN4D3C89</t>
+          <t>B0DB5YTQZV</t>
         </is>
       </c>
       <c r="D113" t="n">
-        <v>267.21</v>
+        <v>0</v>
       </c>
       <c r="E113" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="F113" t="n">
-        <v>1132</v>
+        <v>166</v>
       </c>
       <c r="G113" t="n">
-        <v>854.24</v>
+        <v>0</v>
       </c>
       <c r="H113" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr"/>
       <c r="B114" t="inlineStr">
         <is>
-          <t>WM-SP-TV Brackets- Multi Asins- PT</t>
+          <t>WM-SP-Monitor Arms- Branded</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>B0FN4DSQ6P</t>
+          <t>B0DP2Z5DQ9</t>
         </is>
       </c>
       <c r="D114" t="n">
-        <v>47.88</v>
+        <v>0</v>
       </c>
       <c r="E114" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F114" t="n">
-        <v>181</v>
+        <v>573</v>
       </c>
       <c r="G114" t="n">
         <v>0</v>
@@ -3628,22 +3628,22 @@
       <c r="A115" t="inlineStr"/>
       <c r="B115" t="inlineStr">
         <is>
-          <t>WM-SP-TV Brackets- Multi Asins- PT</t>
+          <t>WM-SP-Monitor Arms- Branded</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>B0FN4HDM6Z</t>
+          <t>B0DP32F346</t>
         </is>
       </c>
       <c r="D115" t="n">
-        <v>246.22</v>
+        <v>10</v>
       </c>
       <c r="E115" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="F115" t="n">
-        <v>467</v>
+        <v>893</v>
       </c>
       <c r="G115" t="n">
         <v>0</v>
@@ -3656,83 +3656,699 @@
       <c r="A116" t="inlineStr"/>
       <c r="B116" t="inlineStr">
         <is>
-          <t>WM-SP-TV Brackets- Multi Asins- PT01</t>
+          <t>WM-SP-Monitor Arms- Defensive</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>B0FN4D3C89</t>
+          <t>B0DB5VG39T</t>
         </is>
       </c>
       <c r="D116" t="n">
-        <v>368.04</v>
+        <v>65.27</v>
       </c>
       <c r="E116" t="n">
-        <v>28</v>
+        <v>5</v>
       </c>
       <c r="F116" t="n">
-        <v>3425</v>
+        <v>407</v>
       </c>
       <c r="G116" t="n">
-        <v>1708.48</v>
+        <v>0</v>
       </c>
       <c r="H116" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr"/>
       <c r="B117" t="inlineStr">
         <is>
-          <t>WM-SP-TV Brackets- Multi Asins- PT01</t>
+          <t>WM-SP-Monitor Arms- Defensive</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>B0FN4DSQ6P</t>
+          <t>B0DB5VVPSB</t>
         </is>
       </c>
       <c r="D117" t="n">
-        <v>67.11</v>
+        <v>140.73</v>
       </c>
       <c r="E117" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="F117" t="n">
-        <v>753</v>
+        <v>1108</v>
       </c>
       <c r="G117" t="n">
-        <v>0</v>
+        <v>3812.72</v>
       </c>
       <c r="H117" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr"/>
       <c r="B118" t="inlineStr">
         <is>
+          <t>WM-SP-Monitor Arms- Defensive</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>B0DB5W4TCP</t>
+        </is>
+      </c>
+      <c r="D118" t="n">
+        <v>23.96</v>
+      </c>
+      <c r="E118" t="n">
+        <v>2</v>
+      </c>
+      <c r="F118" t="n">
+        <v>453</v>
+      </c>
+      <c r="G118" t="n">
+        <v>0</v>
+      </c>
+      <c r="H118" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr"/>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>WM-SP-Monitor Arms- Defensive</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>B0DB5YTQZV</t>
+        </is>
+      </c>
+      <c r="D119" t="n">
+        <v>163.73</v>
+      </c>
+      <c r="E119" t="n">
+        <v>15</v>
+      </c>
+      <c r="F119" t="n">
+        <v>2406</v>
+      </c>
+      <c r="G119" t="n">
+        <v>0</v>
+      </c>
+      <c r="H119" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr"/>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>WM-SP-Monitor Arms- Defensive</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>B0DP2Z5DQ9</t>
+        </is>
+      </c>
+      <c r="D120" t="n">
+        <v>150.22</v>
+      </c>
+      <c r="E120" t="n">
+        <v>14</v>
+      </c>
+      <c r="F120" t="n">
+        <v>1200</v>
+      </c>
+      <c r="G120" t="n">
+        <v>2514.41</v>
+      </c>
+      <c r="H120" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr"/>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>WM-SP-Monitor Arms- Defensive</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>B0DP32F346</t>
+        </is>
+      </c>
+      <c r="D121" t="n">
+        <v>38.99</v>
+      </c>
+      <c r="E121" t="n">
+        <v>3</v>
+      </c>
+      <c r="F121" t="n">
+        <v>312</v>
+      </c>
+      <c r="G121" t="n">
+        <v>0</v>
+      </c>
+      <c r="H121" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr"/>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>WM-SP-Monitor Stand-B0DP2Z5DQ9 - PT</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>B0DP2Z5DQ9</t>
+        </is>
+      </c>
+      <c r="D122" t="n">
+        <v>847.8299999999999</v>
+      </c>
+      <c r="E122" t="n">
+        <v>53</v>
+      </c>
+      <c r="F122" t="n">
+        <v>4129</v>
+      </c>
+      <c r="G122" t="n">
+        <v>7543.219999999999</v>
+      </c>
+      <c r="H122" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr"/>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>WM-SP-Monitor Stand-B0DP2Z5DQ9 - Phrase</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>B0DP2Z5DQ9</t>
+        </is>
+      </c>
+      <c r="D123" t="n">
+        <v>1538.27</v>
+      </c>
+      <c r="E123" t="n">
+        <v>97</v>
+      </c>
+      <c r="F123" t="n">
+        <v>10082</v>
+      </c>
+      <c r="G123" t="n">
+        <v>7363.549999999999</v>
+      </c>
+      <c r="H123" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr"/>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>WM-SP-Monitor Stand-B0DP2Z5DQ9 -Phrase</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>B0DP2Z5DQ9</t>
+        </is>
+      </c>
+      <c r="D124" t="n">
+        <v>1136.88</v>
+      </c>
+      <c r="E124" t="n">
+        <v>54</v>
+      </c>
+      <c r="F124" t="n">
+        <v>13754</v>
+      </c>
+      <c r="G124" t="n">
+        <v>15508.48</v>
+      </c>
+      <c r="H124" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr"/>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>WM-SP-POS stand- Multi - PT</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>B0FN4FPJ83</t>
+        </is>
+      </c>
+      <c r="D125" t="n">
+        <v>0</v>
+      </c>
+      <c r="E125" t="n">
+        <v>0</v>
+      </c>
+      <c r="F125" t="n">
+        <v>10</v>
+      </c>
+      <c r="G125" t="n">
+        <v>0</v>
+      </c>
+      <c r="H125" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr"/>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>WM-SP-TV Brackets- Multi Asins- CT</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>B0FHVWHQHR</t>
+        </is>
+      </c>
+      <c r="D126" t="n">
+        <v>81.40000000000001</v>
+      </c>
+      <c r="E126" t="n">
+        <v>4</v>
+      </c>
+      <c r="F126" t="n">
+        <v>787</v>
+      </c>
+      <c r="G126" t="n">
+        <v>0</v>
+      </c>
+      <c r="H126" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr"/>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>WM-SP-TV Brackets- Multi Asins- CT</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>B0FN4D3C89</t>
+        </is>
+      </c>
+      <c r="D127" t="n">
+        <v>941.95</v>
+      </c>
+      <c r="E127" t="n">
+        <v>52</v>
+      </c>
+      <c r="F127" t="n">
+        <v>7699</v>
+      </c>
+      <c r="G127" t="n">
+        <v>363.56</v>
+      </c>
+      <c r="H127" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr"/>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>WM-SP-TV Brackets- Multi Asins- CT</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>B0FN4DSQ6P</t>
+        </is>
+      </c>
+      <c r="D128" t="n">
+        <v>248.82</v>
+      </c>
+      <c r="E128" t="n">
+        <v>18</v>
+      </c>
+      <c r="F128" t="n">
+        <v>3030</v>
+      </c>
+      <c r="G128" t="n">
+        <v>490.68</v>
+      </c>
+      <c r="H128" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr"/>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>WM-SP-TV Brackets- Multi Asins- CT</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>B0FN4HDM6Z</t>
+        </is>
+      </c>
+      <c r="D129" t="n">
+        <v>456.11</v>
+      </c>
+      <c r="E129" t="n">
+        <v>25</v>
+      </c>
+      <c r="F129" t="n">
+        <v>2999</v>
+      </c>
+      <c r="G129" t="n">
+        <v>0</v>
+      </c>
+      <c r="H129" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr"/>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>WM-SP-TV Brackets- Multi Asins- Exact</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>B0FHVWHQHR</t>
+        </is>
+      </c>
+      <c r="D130" t="n">
+        <v>7.55</v>
+      </c>
+      <c r="E130" t="n">
+        <v>1</v>
+      </c>
+      <c r="F130" t="n">
+        <v>405</v>
+      </c>
+      <c r="G130" t="n">
+        <v>0</v>
+      </c>
+      <c r="H130" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr"/>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>WM-SP-TV Brackets- Multi Asins- Exact</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>B0FN4D3C89</t>
+        </is>
+      </c>
+      <c r="D131" t="n">
+        <v>893.4300000000001</v>
+      </c>
+      <c r="E131" t="n">
+        <v>108</v>
+      </c>
+      <c r="F131" t="n">
+        <v>26055</v>
+      </c>
+      <c r="G131" t="n">
+        <v>3544.08</v>
+      </c>
+      <c r="H131" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr"/>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>WM-SP-TV Brackets- Multi Asins- Exact</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>B0FN4DSQ6P</t>
+        </is>
+      </c>
+      <c r="D132" t="n">
+        <v>147.81</v>
+      </c>
+      <c r="E132" t="n">
+        <v>16</v>
+      </c>
+      <c r="F132" t="n">
+        <v>3954</v>
+      </c>
+      <c r="G132" t="n">
+        <v>1708.48</v>
+      </c>
+      <c r="H132" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr"/>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>WM-SP-TV Brackets- Multi Asins- PT</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>B0FHVWHQHR</t>
+        </is>
+      </c>
+      <c r="D133" t="n">
+        <v>98.56</v>
+      </c>
+      <c r="E133" t="n">
+        <v>5</v>
+      </c>
+      <c r="F133" t="n">
+        <v>946</v>
+      </c>
+      <c r="G133" t="n">
+        <v>617.8</v>
+      </c>
+      <c r="H133" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr"/>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>WM-SP-TV Brackets- Multi Asins- PT</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>B0FN4D3C89</t>
+        </is>
+      </c>
+      <c r="D134" t="n">
+        <v>789.8099999999999</v>
+      </c>
+      <c r="E134" t="n">
+        <v>38</v>
+      </c>
+      <c r="F134" t="n">
+        <v>5413</v>
+      </c>
+      <c r="G134" t="n">
+        <v>1581.36</v>
+      </c>
+      <c r="H134" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr"/>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>WM-SP-TV Brackets- Multi Asins- PT</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>B0FN4DSQ6P</t>
+        </is>
+      </c>
+      <c r="D135" t="n">
+        <v>559.3399999999999</v>
+      </c>
+      <c r="E135" t="n">
+        <v>23</v>
+      </c>
+      <c r="F135" t="n">
+        <v>2390</v>
+      </c>
+      <c r="G135" t="n">
+        <v>2453.4</v>
+      </c>
+      <c r="H135" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr"/>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>WM-SP-TV Brackets- Multi Asins- PT</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>B0FN4HDM6Z</t>
+        </is>
+      </c>
+      <c r="D136" t="n">
+        <v>774.63</v>
+      </c>
+      <c r="E136" t="n">
+        <v>31</v>
+      </c>
+      <c r="F136" t="n">
+        <v>2264</v>
+      </c>
+      <c r="G136" t="n">
+        <v>0</v>
+      </c>
+      <c r="H136" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr"/>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>WM-SP-TV Brackets- Multi Asins- PT01</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>B0FN4D3C89</t>
+        </is>
+      </c>
+      <c r="D137" t="n">
+        <v>1267.55</v>
+      </c>
+      <c r="E137" t="n">
+        <v>92</v>
+      </c>
+      <c r="F137" t="n">
+        <v>14276</v>
+      </c>
+      <c r="G137" t="n">
+        <v>2435.6</v>
+      </c>
+      <c r="H137" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr"/>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>WM-SP-TV Brackets- Multi Asins- PT01</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>B0FN4DSQ6P</t>
+        </is>
+      </c>
+      <c r="D138" t="n">
+        <v>488.96</v>
+      </c>
+      <c r="E138" t="n">
+        <v>36</v>
+      </c>
+      <c r="F138" t="n">
+        <v>4486</v>
+      </c>
+      <c r="G138" t="n">
+        <v>2199.16</v>
+      </c>
+      <c r="H138" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr"/>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>WM-SP-TV Brackets- Multi Asins- PT01</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>B0FN4GQ9HT</t>
+        </is>
+      </c>
+      <c r="D139" t="n">
+        <v>126.99</v>
+      </c>
+      <c r="E139" t="n">
+        <v>7</v>
+      </c>
+      <c r="F139" t="n">
+        <v>1263</v>
+      </c>
+      <c r="G139" t="n">
+        <v>0</v>
+      </c>
+      <c r="H139" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr"/>
+      <c r="B140" t="inlineStr">
+        <is>
           <t>WM_SP_KT_Adjustable_Exact_Manual_HV</t>
         </is>
       </c>
-      <c r="C118" t="inlineStr">
+      <c r="C140" t="inlineStr">
         <is>
           <t>B0CPT3Q25C</t>
         </is>
       </c>
-      <c r="D118" t="n">
-        <v>902</v>
-      </c>
-      <c r="E118" t="n">
-        <v>32</v>
-      </c>
-      <c r="F118" t="n">
-        <v>17591</v>
-      </c>
-      <c r="G118" t="n">
-        <v>0</v>
-      </c>
-      <c r="H118" t="n">
+      <c r="D140" t="n">
+        <v>2597.11</v>
+      </c>
+      <c r="E140" t="n">
+        <v>89</v>
+      </c>
+      <c r="F140" t="n">
+        <v>54480</v>
+      </c>
+      <c r="G140" t="n">
+        <v>0</v>
+      </c>
+      <c r="H140" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4029,13 +4645,13 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>200.51</v>
+        <v>892.91</v>
       </c>
       <c r="E10" t="n">
-        <v>15</v>
+        <v>67</v>
       </c>
       <c r="F10" t="n">
-        <v>6378</v>
+        <v>31217</v>
       </c>
       <c r="G10" t="n">
         <v>0</v>
@@ -4057,19 +4673,19 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>232.84</v>
+        <v>837.21</v>
       </c>
       <c r="E11" t="n">
-        <v>24</v>
+        <v>96</v>
       </c>
       <c r="F11" t="n">
-        <v>9520</v>
+        <v>29741</v>
       </c>
       <c r="G11" t="n">
-        <v>2626.27</v>
+        <v>2989.83</v>
       </c>
       <c r="H11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="12">
@@ -4141,13 +4757,13 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>233.23</v>
+        <v>645.85</v>
       </c>
       <c r="E14" t="n">
-        <v>23</v>
+        <v>53</v>
       </c>
       <c r="F14" t="n">
-        <v>9367</v>
+        <v>22726</v>
       </c>
       <c r="G14" t="n">
         <v>0</v>
@@ -4169,19 +4785,19 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>221.81</v>
+        <v>732.74</v>
       </c>
       <c r="E15" t="n">
-        <v>34</v>
+        <v>99</v>
       </c>
       <c r="F15" t="n">
-        <v>7289</v>
+        <v>25323</v>
       </c>
       <c r="G15" t="n">
-        <v>7878.82</v>
+        <v>2626.27</v>
       </c>
       <c r="H15" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="16">
@@ -4279,7 +4895,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I27"/>
+  <dimension ref="A1:I28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4342,7 +4958,7 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E2" t="n">
         <v>0</v>
@@ -4375,7 +4991,7 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E3" t="n">
         <v>0</v>
@@ -4408,7 +5024,7 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E4" t="n">
         <v>0</v>
@@ -4441,7 +5057,7 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E5" t="n">
         <v>0</v>
@@ -4474,7 +5090,7 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E6" t="n">
         <v>0</v>
@@ -4507,7 +5123,7 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E7" t="n">
         <v>0</v>
@@ -4738,19 +5354,19 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>2320</v>
+        <v>4542</v>
       </c>
       <c r="E14" t="n">
-        <v>90</v>
+        <v>195</v>
       </c>
       <c r="F14" t="n">
-        <v>211.525</v>
+        <v>421.0197143358128</v>
       </c>
       <c r="G14" t="n">
-        <v>6573.73</v>
+        <v>22054.36554985014</v>
       </c>
       <c r="H14" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
@@ -4767,23 +5383,23 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>B0CPFS24ML</t>
+          <t>B0BFVNS8HS</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>2320</v>
+        <v>4815</v>
       </c>
       <c r="E15" t="n">
-        <v>90</v>
+        <v>207</v>
       </c>
       <c r="F15" t="n">
-        <v>211.525</v>
+        <v>446.2841580455429</v>
       </c>
       <c r="G15" t="n">
-        <v>6573.73</v>
+        <v>23377.79829662071</v>
       </c>
       <c r="H15" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
@@ -4795,28 +5411,28 @@
       <c r="A16" t="inlineStr"/>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Camb-SB-Multiple Asin- product collection- Reach</t>
+          <t>Camb-SB-Multiple Asin- Product collection- exact /Reach</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>B0CPT3Q25C</t>
+          <t>B0BFWD6SNF</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>1116</v>
+        <v>2285</v>
       </c>
       <c r="E16" t="n">
-        <v>17</v>
+        <v>98</v>
       </c>
       <c r="F16" t="n">
-        <v>156.5366666666667</v>
+        <v>211.7707586757711</v>
       </c>
       <c r="G16" t="n">
-        <v>2400.846666666667</v>
+        <v>11093.23284771246</v>
       </c>
       <c r="H16" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
@@ -4828,28 +5444,28 @@
       <c r="A17" t="inlineStr"/>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Camb-SB-Multiple Asin- product collection- Reach</t>
+          <t>Camb-SB-Multiple Asin- Product collection- exact /Reach</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>B0DQ1NV8D2</t>
+          <t>B0CPFS24ML</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>1116</v>
+        <v>2257</v>
       </c>
       <c r="E17" t="n">
-        <v>17</v>
+        <v>97</v>
       </c>
       <c r="F17" t="n">
-        <v>156.5366666666667</v>
+        <v>209.2492531828137</v>
       </c>
       <c r="G17" t="n">
-        <v>2400.846666666667</v>
+        <v>10961.14828733655</v>
       </c>
       <c r="H17" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
@@ -4861,28 +5477,28 @@
       <c r="A18" t="inlineStr"/>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Camb-SB-Multiple Asin- product collection- Reach</t>
+          <t>Camb-SB-Multiple Asin- Product collection- exact /Reach</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>B0DQ4YWSMC</t>
+          <t>B0DQPK7MFH</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>1116</v>
+        <v>1935</v>
       </c>
       <c r="E18" t="n">
-        <v>17</v>
+        <v>83</v>
       </c>
       <c r="F18" t="n">
-        <v>156.5366666666667</v>
+        <v>179.3961157600592</v>
       </c>
       <c r="G18" t="n">
-        <v>2400.846666666667</v>
+        <v>9397.345018480133</v>
       </c>
       <c r="H18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
@@ -4894,28 +5510,28 @@
       <c r="A19" t="inlineStr"/>
       <c r="B19" t="inlineStr">
         <is>
-          <t>WM- SBV- Wooden Arm- B0DP32F346- Phrase</t>
+          <t>Camb-SB-Multiple Asin- product collection- Reach</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>B0DP32F346</t>
+          <t>B0CPFS24ML</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>3090</v>
+        <v>12118</v>
       </c>
       <c r="E19" t="n">
-        <v>37</v>
+        <v>234</v>
       </c>
       <c r="F19" t="n">
-        <v>413.9400000000001</v>
+        <v>1684.82</v>
       </c>
       <c r="G19" t="n">
-        <v>0</v>
+        <v>47537.29</v>
       </c>
       <c r="H19" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
@@ -4927,22 +5543,22 @@
       <c r="A20" t="inlineStr"/>
       <c r="B20" t="inlineStr">
         <is>
-          <t>WM- SBV-Wall Mounted Stand- B0DP2WC5VW- Phrase &amp; exact</t>
+          <t>WM- SBV- Wooden Arm- B0DP32F346- Phrase</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>B0DP2WC5VW</t>
+          <t>B0DP32F346</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>4671</v>
+        <v>9282</v>
       </c>
       <c r="E20" t="n">
-        <v>54</v>
+        <v>116</v>
       </c>
       <c r="F20" t="n">
-        <v>828.5999999999999</v>
+        <v>1354.82</v>
       </c>
       <c r="G20" t="n">
         <v>0</v>
@@ -4960,28 +5576,28 @@
       <c r="A21" t="inlineStr"/>
       <c r="B21" t="inlineStr">
         <is>
-          <t>WM-SB-Monitor Arms-Defensive</t>
+          <t>WM- SBV-Wall Mounted Stand- B0DP2WC5VW- Phrase &amp; exact</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>B0DB5VG39T</t>
+          <t>B0DP2WC5VW</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>409</v>
+        <v>17945</v>
       </c>
       <c r="E21" t="n">
-        <v>7</v>
+        <v>201</v>
       </c>
       <c r="F21" t="n">
-        <v>74.98833333333332</v>
+        <v>2724.67</v>
       </c>
       <c r="G21" t="n">
-        <v>607.2033333333333</v>
+        <v>5422.030000000001</v>
       </c>
       <c r="H21" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
@@ -4998,7 +5614,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>B0DB5VVPSB</t>
+          <t>B0DB5VG39T</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -5011,7 +5627,7 @@
         <v>74.98833333333332</v>
       </c>
       <c r="G22" t="n">
-        <v>607.2033333333333</v>
+        <v>0</v>
       </c>
       <c r="H22" t="n">
         <v>0</v>
@@ -5031,7 +5647,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>B0DB5W4TCP</t>
+          <t>B0DB5VVPSB</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -5044,7 +5660,7 @@
         <v>74.98833333333332</v>
       </c>
       <c r="G23" t="n">
-        <v>607.2033333333333</v>
+        <v>0</v>
       </c>
       <c r="H23" t="n">
         <v>0</v>
@@ -5064,7 +5680,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>B0DB5YTQZV</t>
+          <t>B0DB5W4TCP</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -5077,7 +5693,7 @@
         <v>74.98833333333332</v>
       </c>
       <c r="G24" t="n">
-        <v>607.2033333333333</v>
+        <v>0</v>
       </c>
       <c r="H24" t="n">
         <v>0</v>
@@ -5097,7 +5713,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>B0DP2Z5DQ9</t>
+          <t>B0DB5YTQZV</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -5110,7 +5726,7 @@
         <v>74.98833333333332</v>
       </c>
       <c r="G25" t="n">
-        <v>607.2033333333333</v>
+        <v>0</v>
       </c>
       <c r="H25" t="n">
         <v>0</v>
@@ -5130,7 +5746,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>B0DP32F346</t>
+          <t>B0DP2Z5DQ9</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -5143,7 +5759,7 @@
         <v>74.98833333333332</v>
       </c>
       <c r="G26" t="n">
-        <v>607.2033333333333</v>
+        <v>0</v>
       </c>
       <c r="H26" t="n">
         <v>0</v>
@@ -5158,30 +5774,63 @@
       <c r="A27" t="inlineStr"/>
       <c r="B27" t="inlineStr">
         <is>
+          <t>WM-SB-Monitor Arms-Defensive</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>B0DP32F346</t>
+        </is>
+      </c>
+      <c r="D27" t="n">
+        <v>409</v>
+      </c>
+      <c r="E27" t="n">
+        <v>7</v>
+      </c>
+      <c r="F27" t="n">
+        <v>74.98833333333332</v>
+      </c>
+      <c r="G27" t="n">
+        <v>0</v>
+      </c>
+      <c r="H27" t="n">
+        <v>0</v>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>White Mulberry</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr"/>
+      <c r="B28" t="inlineStr">
+        <is>
           <t>WM-SBV-Gas Spring MA- B0DB5VG39T- Phrase</t>
         </is>
       </c>
-      <c r="C27" t="inlineStr">
+      <c r="C28" t="inlineStr">
         <is>
           <t>B0DB5VG39T</t>
         </is>
       </c>
-      <c r="D27" t="n">
-        <v>4957</v>
-      </c>
-      <c r="E27" t="n">
-        <v>38</v>
-      </c>
-      <c r="F27" t="n">
-        <v>699.6800000000001</v>
-      </c>
-      <c r="G27" t="n">
-        <v>0</v>
-      </c>
-      <c r="H27" t="n">
-        <v>0</v>
-      </c>
-      <c r="I27" t="inlineStr">
+      <c r="D28" t="n">
+        <v>16265</v>
+      </c>
+      <c r="E28" t="n">
+        <v>129</v>
+      </c>
+      <c r="F28" t="n">
+        <v>2247.89</v>
+      </c>
+      <c r="G28" t="n">
+        <v>0</v>
+      </c>
+      <c r="H28" t="n">
+        <v>0</v>
+      </c>
+      <c r="I28" t="inlineStr">
         <is>
           <t>White Mulberry</t>
         </is>
